--- a/input/FEC_VoiceAgent_BRD_2.xlsx
+++ b/input/FEC_VoiceAgent_BRD_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hieunguyen/cursor_project/auto_generate_test_cases/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C149F0-1F94-0F41-B02F-512E2972FBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12288E48-F91A-C54F-87CA-52F63369DA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34020" yWindow="680" windowWidth="29400" windowHeight="17000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'1. Kịch bản'!$A$4:$EH$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'1. Kịch bản_25Nov'!$A$4:$EH$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1. Script_03Mar2026'!$A$1:$EC$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1. Script_03Mar2026'!$A$1:$EC$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'1.1. Kịch bản Lead NTB_30Dec'!$A$4:$EI$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'A1-1. Kịch bản Lead NTB_10Jan'!$A$4:$EI$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'A1-1. NTB_Script_12Feb'!$A$2:$EH$2</definedName>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4399" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4405" uniqueCount="541">
   <si>
     <t>No</t>
   </si>
@@ -7813,60 +7813,6 @@
     <xf numFmtId="0" fontId="66" fillId="28" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -7900,6 +7846,63 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="63" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7909,16 +7912,19 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7930,13 +7936,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -8014,30 +8014,6 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -8078,6 +8054,30 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -8164,14 +8164,14 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8181,18 +8181,6 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8209,7 +8197,19 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9274,8 +9274,8 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="419"/>
-      <c r="J1" s="419"/>
+      <c r="I1" s="435"/>
+      <c r="J1" s="435"/>
       <c r="L1" s="30"/>
       <c r="M1" s="30"/>
     </row>
@@ -9316,13 +9316,13 @@
       </c>
     </row>
     <row r="3" spans="1:138" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="486">
+      <c r="A3" s="500">
         <v>1</v>
       </c>
-      <c r="B3" s="422" t="s">
+      <c r="B3" s="438" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="488" t="s">
+      <c r="C3" s="502" t="s">
         <v>360</v>
       </c>
       <c r="D3" s="73" t="s">
@@ -9350,9 +9350,9 @@
       </c>
     </row>
     <row r="4" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A4" s="487"/>
-      <c r="B4" s="423"/>
-      <c r="C4" s="489"/>
+      <c r="A4" s="501"/>
+      <c r="B4" s="439"/>
+      <c r="C4" s="503"/>
       <c r="D4" s="73" t="s">
         <v>56</v>
       </c>
@@ -9374,9 +9374,9 @@
       <c r="M4" s="76"/>
     </row>
     <row r="5" spans="1:138" ht="75" x14ac:dyDescent="0.2">
-      <c r="A5" s="487"/>
-      <c r="B5" s="423"/>
-      <c r="C5" s="489"/>
+      <c r="A5" s="501"/>
+      <c r="B5" s="439"/>
+      <c r="C5" s="503"/>
       <c r="D5" s="73" t="s">
         <v>55</v>
       </c>
@@ -9401,9 +9401,9 @@
       </c>
     </row>
     <row r="6" spans="1:138" ht="225" x14ac:dyDescent="0.2">
-      <c r="A6" s="487"/>
-      <c r="B6" s="423"/>
-      <c r="C6" s="489"/>
+      <c r="A6" s="501"/>
+      <c r="B6" s="439"/>
+      <c r="C6" s="503"/>
       <c r="D6" s="73" t="s">
         <v>63</v>
       </c>
@@ -9426,9 +9426,9 @@
       <c r="M6" s="76"/>
     </row>
     <row r="7" spans="1:138" ht="165" x14ac:dyDescent="0.2">
-      <c r="A7" s="487"/>
-      <c r="B7" s="423"/>
-      <c r="C7" s="489"/>
+      <c r="A7" s="501"/>
+      <c r="B7" s="439"/>
+      <c r="C7" s="503"/>
       <c r="D7" s="73" t="s">
         <v>68</v>
       </c>
@@ -9450,9 +9450,9 @@
       <c r="M7" s="76"/>
     </row>
     <row r="8" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A8" s="487"/>
-      <c r="B8" s="423"/>
-      <c r="C8" s="489"/>
+      <c r="A8" s="501"/>
+      <c r="B8" s="439"/>
+      <c r="C8" s="503"/>
       <c r="D8" s="73" t="s">
         <v>72</v>
       </c>
@@ -9474,9 +9474,9 @@
       <c r="M8" s="76"/>
     </row>
     <row r="9" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A9" s="487"/>
-      <c r="B9" s="423"/>
-      <c r="C9" s="489"/>
+      <c r="A9" s="501"/>
+      <c r="B9" s="439"/>
+      <c r="C9" s="503"/>
       <c r="D9" s="73" t="s">
         <v>86</v>
       </c>
@@ -9500,9 +9500,9 @@
       <c r="M9" s="76"/>
     </row>
     <row r="10" spans="1:138" s="42" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="487"/>
-      <c r="B10" s="423"/>
-      <c r="C10" s="489"/>
+      <c r="A10" s="501"/>
+      <c r="B10" s="439"/>
+      <c r="C10" s="503"/>
       <c r="D10" s="73" t="s">
         <v>92</v>
       </c>
@@ -9652,9 +9652,9 @@
       <c r="EH10" s="41"/>
     </row>
     <row r="11" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A11" s="487"/>
-      <c r="B11" s="423"/>
-      <c r="C11" s="490"/>
+      <c r="A11" s="501"/>
+      <c r="B11" s="439"/>
+      <c r="C11" s="504"/>
       <c r="D11" s="73" t="s">
         <v>318</v>
       </c>
@@ -9676,13 +9676,13 @@
       <c r="M11" s="76"/>
     </row>
     <row r="12" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="491">
+      <c r="A12" s="505">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B12" s="492" t="s">
+      <c r="B12" s="506" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="429" t="s">
+      <c r="C12" s="443" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="73" t="s">
@@ -9708,9 +9708,9 @@
       <c r="M12" s="76"/>
     </row>
     <row r="13" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A13" s="491"/>
-      <c r="B13" s="492"/>
-      <c r="C13" s="430"/>
+      <c r="A13" s="505"/>
+      <c r="B13" s="506"/>
+      <c r="C13" s="444"/>
       <c r="D13" s="73" t="s">
         <v>56</v>
       </c>
@@ -9736,9 +9736,9 @@
       <c r="M13" s="76"/>
     </row>
     <row r="14" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="491"/>
-      <c r="B14" s="492"/>
-      <c r="C14" s="430"/>
+      <c r="A14" s="505"/>
+      <c r="B14" s="506"/>
+      <c r="C14" s="444"/>
       <c r="D14" s="237" t="s">
         <v>320</v>
       </c>
@@ -9785,9 +9785,9 @@
       <c r="M14" s="76"/>
     </row>
     <row r="15" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="491"/>
-      <c r="B15" s="492"/>
-      <c r="C15" s="430"/>
+      <c r="A15" s="505"/>
+      <c r="B15" s="506"/>
+      <c r="C15" s="444"/>
       <c r="D15" s="237" t="s">
         <v>322</v>
       </c>
@@ -9806,9 +9806,9 @@
       <c r="M15" s="76"/>
     </row>
     <row r="16" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="491"/>
-      <c r="B16" s="492"/>
-      <c r="C16" s="430"/>
+      <c r="A16" s="505"/>
+      <c r="B16" s="506"/>
+      <c r="C16" s="444"/>
       <c r="D16" s="76" t="s">
         <v>106</v>
       </c>
@@ -9969,9 +9969,9 @@
       <c r="EH16" s="36"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A17" s="491"/>
-      <c r="B17" s="492"/>
-      <c r="C17" s="430"/>
+      <c r="A17" s="505"/>
+      <c r="B17" s="506"/>
+      <c r="C17" s="444"/>
       <c r="D17" s="76" t="s">
         <v>92</v>
       </c>
@@ -10132,9 +10132,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A18" s="486"/>
-      <c r="B18" s="493"/>
-      <c r="C18" s="430"/>
+      <c r="A18" s="500"/>
+      <c r="B18" s="507"/>
+      <c r="C18" s="444"/>
       <c r="D18" s="78" t="s">
         <v>318</v>
       </c>
@@ -10156,13 +10156,13 @@
       <c r="M18" s="76"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="494">
+      <c r="A19" s="486">
         <v>2</v>
       </c>
-      <c r="B19" s="495" t="s">
+      <c r="B19" s="487" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="496" t="s">
+      <c r="C19" s="488" t="s">
         <v>361</v>
       </c>
       <c r="D19" s="73" t="s">
@@ -10188,9 +10188,9 @@
       <c r="M19" s="76"/>
     </row>
     <row r="20" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A20" s="494"/>
-      <c r="B20" s="495"/>
-      <c r="C20" s="497"/>
+      <c r="A20" s="486"/>
+      <c r="B20" s="487"/>
+      <c r="C20" s="489"/>
       <c r="D20" s="73" t="s">
         <v>56</v>
       </c>
@@ -10216,9 +10216,9 @@
       <c r="M20" s="76"/>
     </row>
     <row r="21" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A21" s="494"/>
-      <c r="B21" s="495"/>
-      <c r="C21" s="497"/>
+      <c r="A21" s="486"/>
+      <c r="B21" s="487"/>
+      <c r="C21" s="489"/>
       <c r="D21" s="240" t="s">
         <v>320</v>
       </c>
@@ -10249,9 +10249,9 @@
       <c r="M21" s="76"/>
     </row>
     <row r="22" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A22" s="494"/>
-      <c r="B22" s="495"/>
-      <c r="C22" s="498"/>
+      <c r="A22" s="486"/>
+      <c r="B22" s="487"/>
+      <c r="C22" s="490"/>
       <c r="D22" s="237" t="s">
         <v>322</v>
       </c>
@@ -10269,9 +10269,9 @@
       <c r="M22" s="76"/>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A23" s="494"/>
-      <c r="B23" s="495"/>
-      <c r="C23" s="497"/>
+      <c r="A23" s="486"/>
+      <c r="B23" s="487"/>
+      <c r="C23" s="489"/>
       <c r="D23" s="88" t="s">
         <v>114</v>
       </c>
@@ -10428,9 +10428,9 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A24" s="494"/>
-      <c r="B24" s="495"/>
-      <c r="C24" s="497"/>
+      <c r="A24" s="486"/>
+      <c r="B24" s="487"/>
+      <c r="C24" s="489"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
       </c>
@@ -10587,9 +10587,9 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="196.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="494"/>
-      <c r="B25" s="495"/>
-      <c r="C25" s="498"/>
+      <c r="A25" s="486"/>
+      <c r="B25" s="487"/>
+      <c r="C25" s="490"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
       </c>
@@ -10611,13 +10611,13 @@
       <c r="M25" s="76"/>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="499">
+      <c r="A26" s="491">
         <v>2.1</v>
       </c>
-      <c r="B26" s="502" t="s">
+      <c r="B26" s="494" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="505" t="s">
+      <c r="C26" s="497" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="237" t="s">
@@ -10643,9 +10643,9 @@
       <c r="M26" s="76"/>
     </row>
     <row r="27" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A27" s="500"/>
-      <c r="B27" s="503"/>
-      <c r="C27" s="506"/>
+      <c r="A27" s="492"/>
+      <c r="B27" s="495"/>
+      <c r="C27" s="498"/>
       <c r="D27" s="237" t="s">
         <v>122</v>
       </c>
@@ -10665,9 +10665,9 @@
       <c r="M27" s="76"/>
     </row>
     <row r="28" spans="1:138" ht="135" x14ac:dyDescent="0.2">
-      <c r="A28" s="500"/>
-      <c r="B28" s="503"/>
-      <c r="C28" s="506"/>
+      <c r="A28" s="492"/>
+      <c r="B28" s="495"/>
+      <c r="C28" s="498"/>
       <c r="D28" s="76" t="s">
         <v>130</v>
       </c>
@@ -10691,9 +10691,9 @@
       <c r="M28" s="76"/>
     </row>
     <row r="29" spans="1:138" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="500"/>
-      <c r="B29" s="503"/>
-      <c r="C29" s="506"/>
+      <c r="A29" s="492"/>
+      <c r="B29" s="495"/>
+      <c r="C29" s="498"/>
       <c r="D29" s="189" t="s">
         <v>55</v>
       </c>
@@ -10717,9 +10717,9 @@
       <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A30" s="500"/>
-      <c r="B30" s="503"/>
-      <c r="C30" s="506"/>
+      <c r="A30" s="492"/>
+      <c r="B30" s="495"/>
+      <c r="C30" s="498"/>
       <c r="D30" s="37" t="s">
         <v>134</v>
       </c>
@@ -10743,9 +10743,9 @@
       </c>
     </row>
     <row r="31" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A31" s="500"/>
-      <c r="B31" s="503"/>
-      <c r="C31" s="506"/>
+      <c r="A31" s="492"/>
+      <c r="B31" s="495"/>
+      <c r="C31" s="498"/>
       <c r="D31" s="88" t="s">
         <v>114</v>
       </c>
@@ -10769,9 +10769,9 @@
       <c r="M31" s="76"/>
     </row>
     <row r="32" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="500"/>
-      <c r="B32" s="503"/>
-      <c r="C32" s="506"/>
+      <c r="A32" s="492"/>
+      <c r="B32" s="495"/>
+      <c r="C32" s="498"/>
       <c r="D32" s="86" t="s">
         <v>92</v>
       </c>
@@ -10795,9 +10795,9 @@
       <c r="M32" s="76"/>
     </row>
     <row r="33" spans="1:13" ht="45" x14ac:dyDescent="0.2">
-      <c r="A33" s="501"/>
-      <c r="B33" s="504"/>
-      <c r="C33" s="507"/>
+      <c r="A33" s="493"/>
+      <c r="B33" s="496"/>
+      <c r="C33" s="499"/>
       <c r="D33" s="76" t="s">
         <v>94</v>
       </c>
@@ -10824,12 +10824,6 @@
   </sheetData>
   <autoFilter ref="A2:EH33" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="13">
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="B19:B25"/>
-    <mergeCell ref="C19:C25"/>
-    <mergeCell ref="A26:A33"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="C26:C33"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="A3:A11"/>
     <mergeCell ref="B3:B11"/>
@@ -10837,6 +10831,12 @@
     <mergeCell ref="A12:A18"/>
     <mergeCell ref="B12:B18"/>
     <mergeCell ref="C12:C18"/>
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="B19:B25"/>
+    <mergeCell ref="C19:C25"/>
+    <mergeCell ref="A26:A33"/>
+    <mergeCell ref="B26:B33"/>
+    <mergeCell ref="C26:C33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -11635,8 +11635,8 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="419"/>
-      <c r="J1" s="419"/>
+      <c r="I1" s="435"/>
+      <c r="J1" s="435"/>
       <c r="L1" s="30"/>
       <c r="M1" s="30"/>
     </row>
@@ -11677,13 +11677,13 @@
       </c>
     </row>
     <row r="3" spans="1:138" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="486">
+      <c r="A3" s="500">
         <v>1</v>
       </c>
-      <c r="B3" s="422" t="s">
+      <c r="B3" s="438" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="488" t="s">
+      <c r="C3" s="502" t="s">
         <v>375</v>
       </c>
       <c r="D3" s="73" t="s">
@@ -11711,9 +11711,9 @@
       </c>
     </row>
     <row r="4" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A4" s="487"/>
-      <c r="B4" s="423"/>
-      <c r="C4" s="489"/>
+      <c r="A4" s="501"/>
+      <c r="B4" s="439"/>
+      <c r="C4" s="503"/>
       <c r="D4" s="73" t="s">
         <v>56</v>
       </c>
@@ -11735,9 +11735,9 @@
       <c r="M4" s="76"/>
     </row>
     <row r="5" spans="1:138" ht="75" x14ac:dyDescent="0.2">
-      <c r="A5" s="487"/>
-      <c r="B5" s="423"/>
-      <c r="C5" s="489"/>
+      <c r="A5" s="501"/>
+      <c r="B5" s="439"/>
+      <c r="C5" s="503"/>
       <c r="D5" s="73" t="s">
         <v>55</v>
       </c>
@@ -11759,9 +11759,9 @@
       <c r="M5" s="76"/>
     </row>
     <row r="6" spans="1:138" ht="240" x14ac:dyDescent="0.2">
-      <c r="A6" s="487"/>
-      <c r="B6" s="423"/>
-      <c r="C6" s="489"/>
+      <c r="A6" s="501"/>
+      <c r="B6" s="439"/>
+      <c r="C6" s="503"/>
       <c r="D6" s="73" t="s">
         <v>63</v>
       </c>
@@ -11784,9 +11784,9 @@
       <c r="M6" s="76"/>
     </row>
     <row r="7" spans="1:138" ht="180" x14ac:dyDescent="0.2">
-      <c r="A7" s="487"/>
-      <c r="B7" s="423"/>
-      <c r="C7" s="489"/>
+      <c r="A7" s="501"/>
+      <c r="B7" s="439"/>
+      <c r="C7" s="503"/>
       <c r="D7" s="73" t="s">
         <v>68</v>
       </c>
@@ -11808,9 +11808,9 @@
       <c r="M7" s="76"/>
     </row>
     <row r="8" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A8" s="487"/>
-      <c r="B8" s="423"/>
-      <c r="C8" s="489"/>
+      <c r="A8" s="501"/>
+      <c r="B8" s="439"/>
+      <c r="C8" s="503"/>
       <c r="D8" s="73" t="s">
         <v>72</v>
       </c>
@@ -11832,9 +11832,9 @@
       <c r="M8" s="76"/>
     </row>
     <row r="9" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A9" s="487"/>
-      <c r="B9" s="423"/>
-      <c r="C9" s="489"/>
+      <c r="A9" s="501"/>
+      <c r="B9" s="439"/>
+      <c r="C9" s="503"/>
       <c r="D9" s="73" t="s">
         <v>86</v>
       </c>
@@ -11858,9 +11858,9 @@
       <c r="M9" s="76"/>
     </row>
     <row r="10" spans="1:138" s="42" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="487"/>
-      <c r="B10" s="423"/>
-      <c r="C10" s="489"/>
+      <c r="A10" s="501"/>
+      <c r="B10" s="439"/>
+      <c r="C10" s="503"/>
       <c r="D10" s="73" t="s">
         <v>92</v>
       </c>
@@ -12010,9 +12010,9 @@
       <c r="EH10" s="41"/>
     </row>
     <row r="11" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A11" s="487"/>
-      <c r="B11" s="423"/>
-      <c r="C11" s="490"/>
+      <c r="A11" s="501"/>
+      <c r="B11" s="439"/>
+      <c r="C11" s="504"/>
       <c r="D11" s="73" t="s">
         <v>318</v>
       </c>
@@ -12034,13 +12034,13 @@
       <c r="M11" s="76"/>
     </row>
     <row r="12" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="491">
+      <c r="A12" s="505">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B12" s="492" t="s">
+      <c r="B12" s="506" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="429" t="s">
+      <c r="C12" s="443" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="73" t="s">
@@ -12066,9 +12066,9 @@
       <c r="M12" s="76"/>
     </row>
     <row r="13" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A13" s="491"/>
-      <c r="B13" s="492"/>
-      <c r="C13" s="430"/>
+      <c r="A13" s="505"/>
+      <c r="B13" s="506"/>
+      <c r="C13" s="444"/>
       <c r="D13" s="73" t="s">
         <v>56</v>
       </c>
@@ -12094,9 +12094,9 @@
       <c r="M13" s="76"/>
     </row>
     <row r="14" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="491"/>
-      <c r="B14" s="492"/>
-      <c r="C14" s="430"/>
+      <c r="A14" s="505"/>
+      <c r="B14" s="506"/>
+      <c r="C14" s="444"/>
       <c r="D14" s="237" t="s">
         <v>320</v>
       </c>
@@ -12132,9 +12132,9 @@
       <c r="M14" s="76"/>
     </row>
     <row r="15" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="491"/>
-      <c r="B15" s="492"/>
-      <c r="C15" s="430"/>
+      <c r="A15" s="505"/>
+      <c r="B15" s="506"/>
+      <c r="C15" s="444"/>
       <c r="D15" s="237" t="s">
         <v>322</v>
       </c>
@@ -12153,9 +12153,9 @@
       <c r="M15" s="76"/>
     </row>
     <row r="16" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="491"/>
-      <c r="B16" s="492"/>
-      <c r="C16" s="430"/>
+      <c r="A16" s="505"/>
+      <c r="B16" s="506"/>
+      <c r="C16" s="444"/>
       <c r="D16" s="76" t="s">
         <v>106</v>
       </c>
@@ -12316,9 +12316,9 @@
       <c r="EH16" s="36"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A17" s="491"/>
-      <c r="B17" s="492"/>
-      <c r="C17" s="430"/>
+      <c r="A17" s="505"/>
+      <c r="B17" s="506"/>
+      <c r="C17" s="444"/>
       <c r="D17" s="76" t="s">
         <v>92</v>
       </c>
@@ -12479,9 +12479,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A18" s="486"/>
-      <c r="B18" s="493"/>
-      <c r="C18" s="430"/>
+      <c r="A18" s="500"/>
+      <c r="B18" s="507"/>
+      <c r="C18" s="444"/>
       <c r="D18" s="78" t="s">
         <v>318</v>
       </c>
@@ -12503,13 +12503,13 @@
       <c r="M18" s="76"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="494">
+      <c r="A19" s="486">
         <v>2</v>
       </c>
-      <c r="B19" s="495" t="s">
+      <c r="B19" s="487" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="496" t="s">
+      <c r="C19" s="488" t="s">
         <v>361</v>
       </c>
       <c r="D19" s="73" t="s">
@@ -12535,9 +12535,9 @@
       <c r="M19" s="76"/>
     </row>
     <row r="20" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A20" s="494"/>
-      <c r="B20" s="495"/>
-      <c r="C20" s="497"/>
+      <c r="A20" s="486"/>
+      <c r="B20" s="487"/>
+      <c r="C20" s="489"/>
       <c r="D20" s="73" t="s">
         <v>56</v>
       </c>
@@ -12563,9 +12563,9 @@
       <c r="M20" s="76"/>
     </row>
     <row r="21" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A21" s="494"/>
-      <c r="B21" s="495"/>
-      <c r="C21" s="497"/>
+      <c r="A21" s="486"/>
+      <c r="B21" s="487"/>
+      <c r="C21" s="489"/>
       <c r="D21" s="240" t="s">
         <v>320</v>
       </c>
@@ -12596,9 +12596,9 @@
       <c r="M21" s="76"/>
     </row>
     <row r="22" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A22" s="494"/>
-      <c r="B22" s="495"/>
-      <c r="C22" s="498"/>
+      <c r="A22" s="486"/>
+      <c r="B22" s="487"/>
+      <c r="C22" s="490"/>
       <c r="D22" s="237" t="s">
         <v>322</v>
       </c>
@@ -12616,9 +12616,9 @@
       <c r="M22" s="76"/>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A23" s="494"/>
-      <c r="B23" s="495"/>
-      <c r="C23" s="497"/>
+      <c r="A23" s="486"/>
+      <c r="B23" s="487"/>
+      <c r="C23" s="489"/>
       <c r="D23" s="88" t="s">
         <v>114</v>
       </c>
@@ -12775,9 +12775,9 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A24" s="494"/>
-      <c r="B24" s="495"/>
-      <c r="C24" s="497"/>
+      <c r="A24" s="486"/>
+      <c r="B24" s="487"/>
+      <c r="C24" s="489"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
       </c>
@@ -12934,9 +12934,9 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="196.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="494"/>
-      <c r="B25" s="495"/>
-      <c r="C25" s="498"/>
+      <c r="A25" s="486"/>
+      <c r="B25" s="487"/>
+      <c r="C25" s="490"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
       </c>
@@ -12958,13 +12958,13 @@
       <c r="M25" s="76"/>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="499">
+      <c r="A26" s="491">
         <v>2.1</v>
       </c>
-      <c r="B26" s="502" t="s">
+      <c r="B26" s="494" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="505" t="s">
+      <c r="C26" s="497" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="237" t="s">
@@ -12990,9 +12990,9 @@
       <c r="M26" s="76"/>
     </row>
     <row r="27" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A27" s="500"/>
-      <c r="B27" s="503"/>
-      <c r="C27" s="506"/>
+      <c r="A27" s="492"/>
+      <c r="B27" s="495"/>
+      <c r="C27" s="498"/>
       <c r="D27" s="237" t="s">
         <v>122</v>
       </c>
@@ -13012,9 +13012,9 @@
       <c r="M27" s="76"/>
     </row>
     <row r="28" spans="1:138" ht="135" x14ac:dyDescent="0.2">
-      <c r="A28" s="500"/>
-      <c r="B28" s="503"/>
-      <c r="C28" s="506"/>
+      <c r="A28" s="492"/>
+      <c r="B28" s="495"/>
+      <c r="C28" s="498"/>
       <c r="D28" s="76" t="s">
         <v>130</v>
       </c>
@@ -13038,9 +13038,9 @@
       <c r="M28" s="76"/>
     </row>
     <row r="29" spans="1:138" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="500"/>
-      <c r="B29" s="503"/>
-      <c r="C29" s="506"/>
+      <c r="A29" s="492"/>
+      <c r="B29" s="495"/>
+      <c r="C29" s="498"/>
       <c r="D29" s="189" t="s">
         <v>55</v>
       </c>
@@ -13064,9 +13064,9 @@
       <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A30" s="500"/>
-      <c r="B30" s="503"/>
-      <c r="C30" s="506"/>
+      <c r="A30" s="492"/>
+      <c r="B30" s="495"/>
+      <c r="C30" s="498"/>
       <c r="D30" s="37" t="s">
         <v>134</v>
       </c>
@@ -13090,9 +13090,9 @@
       </c>
     </row>
     <row r="31" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A31" s="500"/>
-      <c r="B31" s="503"/>
-      <c r="C31" s="506"/>
+      <c r="A31" s="492"/>
+      <c r="B31" s="495"/>
+      <c r="C31" s="498"/>
       <c r="D31" s="88" t="s">
         <v>114</v>
       </c>
@@ -13116,9 +13116,9 @@
       <c r="M31" s="76"/>
     </row>
     <row r="32" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="500"/>
-      <c r="B32" s="503"/>
-      <c r="C32" s="506"/>
+      <c r="A32" s="492"/>
+      <c r="B32" s="495"/>
+      <c r="C32" s="498"/>
       <c r="D32" s="86" t="s">
         <v>92</v>
       </c>
@@ -13142,9 +13142,9 @@
       <c r="M32" s="76"/>
     </row>
     <row r="33" spans="1:13" ht="45" x14ac:dyDescent="0.2">
-      <c r="A33" s="501"/>
-      <c r="B33" s="504"/>
-      <c r="C33" s="507"/>
+      <c r="A33" s="493"/>
+      <c r="B33" s="496"/>
+      <c r="C33" s="499"/>
       <c r="D33" s="76" t="s">
         <v>94</v>
       </c>
@@ -13303,6 +13303,13 @@
   </sheetData>
   <autoFilter ref="A2:EH34" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="16">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="A12:A18"/>
+    <mergeCell ref="B12:B18"/>
+    <mergeCell ref="C12:C18"/>
     <mergeCell ref="A34:A38"/>
     <mergeCell ref="B34:B38"/>
     <mergeCell ref="C34:C38"/>
@@ -13312,13 +13319,6 @@
     <mergeCell ref="A26:A33"/>
     <mergeCell ref="B26:B33"/>
     <mergeCell ref="C26:C33"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A3:A11"/>
-    <mergeCell ref="B3:B11"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="A12:A18"/>
-    <mergeCell ref="B12:B18"/>
-    <mergeCell ref="C12:C18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -13357,8 +13357,8 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="419"/>
-      <c r="J1" s="419"/>
+      <c r="I1" s="435"/>
+      <c r="J1" s="435"/>
       <c r="L1" s="30"/>
       <c r="M1" s="30"/>
     </row>
@@ -13399,10 +13399,10 @@
       </c>
     </row>
     <row r="3" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A3" s="486">
+      <c r="A3" s="500">
         <v>1</v>
       </c>
-      <c r="B3" s="422" t="s">
+      <c r="B3" s="438" t="s">
         <v>50</v>
       </c>
       <c r="C3" s="482" t="s">
@@ -13433,8 +13433,8 @@
       </c>
     </row>
     <row r="4" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A4" s="487"/>
-      <c r="B4" s="423"/>
+      <c r="A4" s="501"/>
+      <c r="B4" s="439"/>
       <c r="C4" s="483"/>
       <c r="D4" s="73" t="s">
         <v>56</v>
@@ -13457,8 +13457,8 @@
       <c r="M4" s="76"/>
     </row>
     <row r="5" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A5" s="487"/>
-      <c r="B5" s="423"/>
+      <c r="A5" s="501"/>
+      <c r="B5" s="439"/>
       <c r="C5" s="483"/>
       <c r="D5" s="73" t="s">
         <v>55</v>
@@ -13481,8 +13481,8 @@
       <c r="M5" s="76"/>
     </row>
     <row r="6" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A6" s="487"/>
-      <c r="B6" s="423"/>
+      <c r="A6" s="501"/>
+      <c r="B6" s="439"/>
       <c r="C6" s="483"/>
       <c r="D6" s="73" t="s">
         <v>63</v>
@@ -13506,8 +13506,8 @@
       <c r="M6" s="76"/>
     </row>
     <row r="7" spans="1:138" ht="150" x14ac:dyDescent="0.2">
-      <c r="A7" s="487"/>
-      <c r="B7" s="423"/>
+      <c r="A7" s="501"/>
+      <c r="B7" s="439"/>
       <c r="C7" s="483"/>
       <c r="D7" s="73" t="s">
         <v>68</v>
@@ -13530,8 +13530,8 @@
       <c r="M7" s="76"/>
     </row>
     <row r="8" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A8" s="487"/>
-      <c r="B8" s="423"/>
+      <c r="A8" s="501"/>
+      <c r="B8" s="439"/>
       <c r="C8" s="483"/>
       <c r="D8" s="73" t="s">
         <v>72</v>
@@ -13554,8 +13554,8 @@
       <c r="M8" s="76"/>
     </row>
     <row r="9" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A9" s="487"/>
-      <c r="B9" s="423"/>
+      <c r="A9" s="501"/>
+      <c r="B9" s="439"/>
       <c r="C9" s="483"/>
       <c r="D9" s="73" t="s">
         <v>86</v>
@@ -13594,8 +13594,8 @@
       <c r="M9" s="76"/>
     </row>
     <row r="10" spans="1:138" s="42" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A10" s="487"/>
-      <c r="B10" s="423"/>
+      <c r="A10" s="501"/>
+      <c r="B10" s="439"/>
       <c r="C10" s="483"/>
       <c r="D10" s="73" t="s">
         <v>92</v>
@@ -13760,8 +13760,8 @@
       <c r="EH10" s="41"/>
     </row>
     <row r="11" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A11" s="487"/>
-      <c r="B11" s="423"/>
+      <c r="A11" s="501"/>
+      <c r="B11" s="439"/>
       <c r="C11" s="483"/>
       <c r="D11" s="73" t="s">
         <v>318</v>
@@ -13784,13 +13784,13 @@
       <c r="M11" s="76"/>
     </row>
     <row r="12" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="491">
+      <c r="A12" s="505">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B12" s="492" t="s">
+      <c r="B12" s="506" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="429" t="s">
+      <c r="C12" s="443" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="73" t="s">
@@ -13816,9 +13816,9 @@
       <c r="M12" s="76"/>
     </row>
     <row r="13" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A13" s="491"/>
-      <c r="B13" s="492"/>
-      <c r="C13" s="430"/>
+      <c r="A13" s="505"/>
+      <c r="B13" s="506"/>
+      <c r="C13" s="444"/>
       <c r="D13" s="73" t="s">
         <v>56</v>
       </c>
@@ -13844,9 +13844,9 @@
       <c r="M13" s="76"/>
     </row>
     <row r="14" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="491"/>
-      <c r="B14" s="492"/>
-      <c r="C14" s="430"/>
+      <c r="A14" s="505"/>
+      <c r="B14" s="506"/>
+      <c r="C14" s="444"/>
       <c r="D14" s="73" t="s">
         <v>55</v>
       </c>
@@ -13882,9 +13882,9 @@
       <c r="M14" s="76"/>
     </row>
     <row r="15" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A15" s="491"/>
-      <c r="B15" s="492"/>
-      <c r="C15" s="430"/>
+      <c r="A15" s="505"/>
+      <c r="B15" s="506"/>
+      <c r="C15" s="444"/>
       <c r="D15" s="76" t="s">
         <v>106</v>
       </c>
@@ -14045,9 +14045,9 @@
       <c r="EH15" s="36"/>
     </row>
     <row r="16" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="491"/>
-      <c r="B16" s="492"/>
-      <c r="C16" s="430"/>
+      <c r="A16" s="505"/>
+      <c r="B16" s="506"/>
+      <c r="C16" s="444"/>
       <c r="D16" s="76" t="s">
         <v>92</v>
       </c>
@@ -14208,9 +14208,9 @@
       <c r="EH16" s="36"/>
     </row>
     <row r="17" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A17" s="486"/>
-      <c r="B17" s="493"/>
-      <c r="C17" s="430"/>
+      <c r="A17" s="500"/>
+      <c r="B17" s="507"/>
+      <c r="C17" s="444"/>
       <c r="D17" s="78" t="s">
         <v>318</v>
       </c>
@@ -14232,13 +14232,13 @@
       <c r="M17" s="76"/>
     </row>
     <row r="18" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A18" s="494">
+      <c r="A18" s="486">
         <v>2</v>
       </c>
-      <c r="B18" s="495" t="s">
+      <c r="B18" s="487" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="496" t="s">
+      <c r="C18" s="488" t="s">
         <v>387</v>
       </c>
       <c r="D18" s="73" t="s">
@@ -14264,9 +14264,9 @@
       <c r="M18" s="76"/>
     </row>
     <row r="19" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A19" s="494"/>
-      <c r="B19" s="495"/>
-      <c r="C19" s="497"/>
+      <c r="A19" s="486"/>
+      <c r="B19" s="487"/>
+      <c r="C19" s="489"/>
       <c r="D19" s="73" t="s">
         <v>56</v>
       </c>
@@ -14292,9 +14292,9 @@
       <c r="M19" s="76"/>
     </row>
     <row r="20" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A20" s="494"/>
-      <c r="B20" s="495"/>
-      <c r="C20" s="497"/>
+      <c r="A20" s="486"/>
+      <c r="B20" s="487"/>
+      <c r="C20" s="489"/>
       <c r="D20" s="73" t="s">
         <v>55</v>
       </c>
@@ -14325,9 +14325,9 @@
       <c r="M20" s="76"/>
     </row>
     <row r="21" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A21" s="494"/>
-      <c r="B21" s="495"/>
-      <c r="C21" s="497"/>
+      <c r="A21" s="486"/>
+      <c r="B21" s="487"/>
+      <c r="C21" s="489"/>
       <c r="D21" s="61" t="s">
         <v>114</v>
       </c>
@@ -14484,9 +14484,9 @@
       <c r="EH21" s="36"/>
     </row>
     <row r="22" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A22" s="494"/>
-      <c r="B22" s="495"/>
-      <c r="C22" s="497"/>
+      <c r="A22" s="486"/>
+      <c r="B22" s="487"/>
+      <c r="C22" s="489"/>
       <c r="D22" s="86" t="s">
         <v>92</v>
       </c>
@@ -14643,9 +14643,9 @@
       <c r="EH22" s="36"/>
     </row>
     <row r="23" spans="1:138" ht="196.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="494"/>
-      <c r="B23" s="495"/>
-      <c r="C23" s="498"/>
+      <c r="A23" s="486"/>
+      <c r="B23" s="487"/>
+      <c r="C23" s="490"/>
       <c r="D23" s="76" t="s">
         <v>94</v>
       </c>
@@ -14667,13 +14667,13 @@
       <c r="M23" s="76"/>
     </row>
     <row r="24" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A24" s="499">
+      <c r="A24" s="491">
         <v>2.1</v>
       </c>
-      <c r="B24" s="502" t="s">
+      <c r="B24" s="494" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="505" t="s">
+      <c r="C24" s="497" t="s">
         <v>117</v>
       </c>
       <c r="D24" s="76" t="s">
@@ -14699,9 +14699,9 @@
       <c r="M24" s="76"/>
     </row>
     <row r="25" spans="1:138" ht="105" x14ac:dyDescent="0.2">
-      <c r="A25" s="500"/>
-      <c r="B25" s="503"/>
-      <c r="C25" s="506"/>
+      <c r="A25" s="492"/>
+      <c r="B25" s="495"/>
+      <c r="C25" s="498"/>
       <c r="D25" s="76" t="s">
         <v>130</v>
       </c>
@@ -14725,9 +14725,9 @@
       <c r="M25" s="76"/>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="500"/>
-      <c r="B26" s="503"/>
-      <c r="C26" s="506"/>
+      <c r="A26" s="492"/>
+      <c r="B26" s="495"/>
+      <c r="C26" s="498"/>
       <c r="D26" s="189" t="s">
         <v>55</v>
       </c>
@@ -14751,9 +14751,9 @@
       <c r="M26" s="76"/>
     </row>
     <row r="27" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A27" s="500"/>
-      <c r="B27" s="503"/>
-      <c r="C27" s="506"/>
+      <c r="A27" s="492"/>
+      <c r="B27" s="495"/>
+      <c r="C27" s="498"/>
       <c r="D27" s="37" t="s">
         <v>134</v>
       </c>
@@ -14777,9 +14777,9 @@
       </c>
     </row>
     <row r="28" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A28" s="500"/>
-      <c r="B28" s="503"/>
-      <c r="C28" s="506"/>
+      <c r="A28" s="492"/>
+      <c r="B28" s="495"/>
+      <c r="C28" s="498"/>
       <c r="D28" s="88" t="s">
         <v>114</v>
       </c>
@@ -14803,9 +14803,9 @@
       <c r="M28" s="76"/>
     </row>
     <row r="29" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="500"/>
-      <c r="B29" s="503"/>
-      <c r="C29" s="506"/>
+      <c r="A29" s="492"/>
+      <c r="B29" s="495"/>
+      <c r="C29" s="498"/>
       <c r="D29" s="86" t="s">
         <v>92</v>
       </c>
@@ -14829,9 +14829,9 @@
       <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="501"/>
-      <c r="B30" s="504"/>
-      <c r="C30" s="507"/>
+      <c r="A30" s="493"/>
+      <c r="B30" s="496"/>
+      <c r="C30" s="499"/>
       <c r="D30" s="76" t="s">
         <v>94</v>
       </c>
@@ -14990,6 +14990,13 @@
   </sheetData>
   <autoFilter ref="A2:EH31" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="16">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="C12:C17"/>
     <mergeCell ref="A31:A35"/>
     <mergeCell ref="B31:B35"/>
     <mergeCell ref="C31:C35"/>
@@ -14999,13 +15006,6 @@
     <mergeCell ref="A24:A30"/>
     <mergeCell ref="B24:B30"/>
     <mergeCell ref="C24:C30"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A3:A11"/>
-    <mergeCell ref="B3:B11"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="C12:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -15867,10 +15867,10 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="419" t="s">
+      <c r="I1" s="435" t="s">
         <v>416</v>
       </c>
-      <c r="J1" s="419"/>
+      <c r="J1" s="435"/>
     </row>
     <row r="2" spans="1:138" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -15903,13 +15903,13 @@
       </c>
     </row>
     <row r="3" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A3" s="486">
+      <c r="A3" s="500">
         <v>1</v>
       </c>
-      <c r="B3" s="422" t="s">
+      <c r="B3" s="438" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="429" t="s">
+      <c r="C3" s="443" t="s">
         <v>417</v>
       </c>
       <c r="D3" s="73" t="s">
@@ -15931,9 +15931,9 @@
       </c>
     </row>
     <row r="4" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A4" s="487"/>
-      <c r="B4" s="423"/>
-      <c r="C4" s="430"/>
+      <c r="A4" s="501"/>
+      <c r="B4" s="439"/>
+      <c r="C4" s="444"/>
       <c r="D4" s="73" t="s">
         <v>56</v>
       </c>
@@ -15953,9 +15953,9 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A5" s="487"/>
-      <c r="B5" s="423"/>
-      <c r="C5" s="430"/>
+      <c r="A5" s="501"/>
+      <c r="B5" s="439"/>
+      <c r="C5" s="444"/>
       <c r="D5" s="73" t="s">
         <v>55</v>
       </c>
@@ -15975,9 +15975,9 @@
       </c>
     </row>
     <row r="6" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A6" s="487"/>
-      <c r="B6" s="423"/>
-      <c r="C6" s="430"/>
+      <c r="A6" s="501"/>
+      <c r="B6" s="439"/>
+      <c r="C6" s="444"/>
       <c r="D6" s="73" t="s">
         <v>63</v>
       </c>
@@ -15998,9 +15998,9 @@
       <c r="K6" s="38"/>
     </row>
     <row r="7" spans="1:138" ht="150" x14ac:dyDescent="0.2">
-      <c r="A7" s="487"/>
-      <c r="B7" s="423"/>
-      <c r="C7" s="430"/>
+      <c r="A7" s="501"/>
+      <c r="B7" s="439"/>
+      <c r="C7" s="444"/>
       <c r="D7" s="73" t="s">
         <v>68</v>
       </c>
@@ -16020,9 +16020,9 @@
       </c>
     </row>
     <row r="8" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A8" s="487"/>
-      <c r="B8" s="423"/>
-      <c r="C8" s="430"/>
+      <c r="A8" s="501"/>
+      <c r="B8" s="439"/>
+      <c r="C8" s="444"/>
       <c r="D8" s="73" t="s">
         <v>72</v>
       </c>
@@ -16042,9 +16042,9 @@
       </c>
     </row>
     <row r="9" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A9" s="487"/>
-      <c r="B9" s="423"/>
-      <c r="C9" s="430"/>
+      <c r="A9" s="501"/>
+      <c r="B9" s="439"/>
+      <c r="C9" s="444"/>
       <c r="D9" s="73" t="s">
         <v>86</v>
       </c>
@@ -16078,9 +16078,9 @@
       </c>
     </row>
     <row r="10" spans="1:138" s="42" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A10" s="487"/>
-      <c r="B10" s="423"/>
-      <c r="C10" s="430"/>
+      <c r="A10" s="501"/>
+      <c r="B10" s="439"/>
+      <c r="C10" s="444"/>
       <c r="D10" s="73" t="s">
         <v>92</v>
       </c>
@@ -16242,9 +16242,9 @@
       <c r="EH10" s="41"/>
     </row>
     <row r="11" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A11" s="487"/>
-      <c r="B11" s="423"/>
-      <c r="C11" s="430"/>
+      <c r="A11" s="501"/>
+      <c r="B11" s="439"/>
+      <c r="C11" s="444"/>
       <c r="D11" s="73" t="s">
         <v>318</v>
       </c>
@@ -16264,13 +16264,13 @@
       </c>
     </row>
     <row r="12" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="491">
+      <c r="A12" s="505">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B12" s="492" t="s">
+      <c r="B12" s="506" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="429" t="s">
+      <c r="C12" s="443" t="s">
         <v>418</v>
       </c>
       <c r="D12" s="73" t="s">
@@ -16292,9 +16292,9 @@
       </c>
     </row>
     <row r="13" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="491"/>
-      <c r="B13" s="492"/>
-      <c r="C13" s="430"/>
+      <c r="A13" s="505"/>
+      <c r="B13" s="506"/>
+      <c r="C13" s="444"/>
       <c r="D13" s="73" t="s">
         <v>56</v>
       </c>
@@ -16316,9 +16316,9 @@
       </c>
     </row>
     <row r="14" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="491"/>
-      <c r="B14" s="492"/>
-      <c r="C14" s="430"/>
+      <c r="A14" s="505"/>
+      <c r="B14" s="506"/>
+      <c r="C14" s="444"/>
       <c r="D14" s="73" t="s">
         <v>55</v>
       </c>
@@ -16353,9 +16353,9 @@
       <c r="K14" s="38"/>
     </row>
     <row r="15" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A15" s="491"/>
-      <c r="B15" s="492"/>
-      <c r="C15" s="430"/>
+      <c r="A15" s="505"/>
+      <c r="B15" s="506"/>
+      <c r="C15" s="444"/>
       <c r="D15" s="76" t="s">
         <v>106</v>
       </c>
@@ -16517,9 +16517,9 @@
       <c r="EH15" s="36"/>
     </row>
     <row r="16" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="491"/>
-      <c r="B16" s="492"/>
-      <c r="C16" s="430"/>
+      <c r="A16" s="505"/>
+      <c r="B16" s="506"/>
+      <c r="C16" s="444"/>
       <c r="D16" s="76" t="s">
         <v>92</v>
       </c>
@@ -16681,9 +16681,9 @@
       <c r="EH16" s="36"/>
     </row>
     <row r="17" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A17" s="486"/>
-      <c r="B17" s="493"/>
-      <c r="C17" s="430"/>
+      <c r="A17" s="500"/>
+      <c r="B17" s="507"/>
+      <c r="C17" s="444"/>
       <c r="D17" s="78" t="s">
         <v>318</v>
       </c>
@@ -16703,10 +16703,10 @@
       </c>
     </row>
     <row r="18" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A18" s="494">
+      <c r="A18" s="486">
         <v>2</v>
       </c>
-      <c r="B18" s="495" t="s">
+      <c r="B18" s="487" t="s">
         <v>109</v>
       </c>
       <c r="C18" s="480" t="s">
@@ -16731,8 +16731,8 @@
       </c>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="494"/>
-      <c r="B19" s="495"/>
+      <c r="A19" s="486"/>
+      <c r="B19" s="487"/>
       <c r="C19" s="528"/>
       <c r="D19" s="73" t="s">
         <v>56</v>
@@ -16755,8 +16755,8 @@
       </c>
     </row>
     <row r="20" spans="1:138" ht="90" x14ac:dyDescent="0.2">
-      <c r="A20" s="494"/>
-      <c r="B20" s="495"/>
+      <c r="A20" s="486"/>
+      <c r="B20" s="487"/>
       <c r="C20" s="528"/>
       <c r="D20" s="73" t="s">
         <v>55</v>
@@ -16779,8 +16779,8 @@
       </c>
     </row>
     <row r="21" spans="1:138" s="47" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A21" s="494"/>
-      <c r="B21" s="495"/>
+      <c r="A21" s="486"/>
+      <c r="B21" s="487"/>
       <c r="C21" s="528"/>
       <c r="D21" s="61" t="s">
         <v>114</v>
@@ -16931,8 +16931,8 @@
       <c r="EH21" s="36"/>
     </row>
     <row r="22" spans="1:138" s="47" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A22" s="494"/>
-      <c r="B22" s="495"/>
+      <c r="A22" s="486"/>
+      <c r="B22" s="487"/>
       <c r="C22" s="528"/>
       <c r="D22" s="86" t="s">
         <v>92</v>
@@ -17083,8 +17083,8 @@
       <c r="EH22" s="36"/>
     </row>
     <row r="23" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A23" s="494"/>
-      <c r="B23" s="495"/>
+      <c r="A23" s="486"/>
+      <c r="B23" s="487"/>
       <c r="C23" s="529"/>
       <c r="D23" s="76" t="s">
         <v>94</v>
@@ -17105,13 +17105,13 @@
       </c>
     </row>
     <row r="24" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A24" s="499">
+      <c r="A24" s="491">
         <v>2.1</v>
       </c>
-      <c r="B24" s="502" t="s">
+      <c r="B24" s="494" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="505" t="s">
+      <c r="C24" s="497" t="s">
         <v>117</v>
       </c>
       <c r="D24" s="83" t="s">
@@ -17136,9 +17136,9 @@
       </c>
     </row>
     <row r="25" spans="1:138" ht="105" x14ac:dyDescent="0.2">
-      <c r="A25" s="500"/>
-      <c r="B25" s="503"/>
-      <c r="C25" s="506"/>
+      <c r="A25" s="492"/>
+      <c r="B25" s="495"/>
+      <c r="C25" s="498"/>
       <c r="D25" s="83" t="s">
         <v>130</v>
       </c>
@@ -17161,9 +17161,9 @@
       </c>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="500"/>
-      <c r="B26" s="503"/>
-      <c r="C26" s="506"/>
+      <c r="A26" s="492"/>
+      <c r="B26" s="495"/>
+      <c r="C26" s="498"/>
       <c r="D26" s="73" t="s">
         <v>55</v>
       </c>
@@ -17188,9 +17188,9 @@
       </c>
     </row>
     <row r="27" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A27" s="500"/>
-      <c r="B27" s="503"/>
-      <c r="C27" s="506"/>
+      <c r="A27" s="492"/>
+      <c r="B27" s="495"/>
+      <c r="C27" s="498"/>
       <c r="D27" s="61" t="s">
         <v>114</v>
       </c>
@@ -17212,9 +17212,9 @@
       </c>
     </row>
     <row r="28" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" s="500"/>
-      <c r="B28" s="503"/>
-      <c r="C28" s="506"/>
+      <c r="A28" s="492"/>
+      <c r="B28" s="495"/>
+      <c r="C28" s="498"/>
       <c r="D28" s="86" t="s">
         <v>92</v>
       </c>
@@ -17236,9 +17236,9 @@
       </c>
     </row>
     <row r="29" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="501"/>
-      <c r="B29" s="504"/>
-      <c r="C29" s="507"/>
+      <c r="A29" s="493"/>
+      <c r="B29" s="496"/>
+      <c r="C29" s="499"/>
       <c r="D29" s="76" t="s">
         <v>94</v>
       </c>
@@ -17380,13 +17380,6 @@
   </sheetData>
   <autoFilter ref="A2:EH30" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="16">
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A3:A11"/>
-    <mergeCell ref="B3:B11"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="C12:C17"/>
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="B30:B34"/>
     <mergeCell ref="A30:A34"/>
@@ -17396,6 +17389,13 @@
     <mergeCell ref="A24:A29"/>
     <mergeCell ref="B24:B29"/>
     <mergeCell ref="C24:C29"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="C12:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -17421,18 +17421,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:133" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="435" t="s">
+      <c r="A1" s="447" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="435"/>
-      <c r="C1" s="435"/>
-      <c r="D1" s="435"/>
-      <c r="E1" s="435"/>
-      <c r="F1" s="435"/>
-      <c r="G1" s="435"/>
+      <c r="B1" s="447"/>
+      <c r="C1" s="447"/>
+      <c r="D1" s="447"/>
+      <c r="E1" s="447"/>
+      <c r="F1" s="447"/>
+      <c r="G1" s="447"/>
       <c r="H1" s="300"/>
-      <c r="I1" s="419"/>
-      <c r="J1" s="419"/>
+      <c r="I1" s="435"/>
+      <c r="J1" s="435"/>
     </row>
     <row r="2" spans="1:133" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -17604,13 +17604,13 @@
       <c r="EC3" s="36"/>
     </row>
     <row r="4" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A4" s="420">
+      <c r="A4" s="436">
         <v>1</v>
       </c>
-      <c r="B4" s="422" t="s">
+      <c r="B4" s="438" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="424" t="s">
+      <c r="C4" s="440" t="s">
         <v>51</v>
       </c>
       <c r="D4" s="73" t="s">
@@ -17632,9 +17632,9 @@
       </c>
     </row>
     <row r="5" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A5" s="421"/>
-      <c r="B5" s="423"/>
-      <c r="C5" s="425"/>
+      <c r="A5" s="437"/>
+      <c r="B5" s="439"/>
+      <c r="C5" s="441"/>
       <c r="D5" s="73" t="s">
         <v>56</v>
       </c>
@@ -17654,9 +17654,9 @@
       </c>
     </row>
     <row r="6" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A6" s="421"/>
-      <c r="B6" s="423"/>
-      <c r="C6" s="425"/>
+      <c r="A6" s="437"/>
+      <c r="B6" s="439"/>
+      <c r="C6" s="441"/>
       <c r="D6" s="237" t="s">
         <v>61</v>
       </c>
@@ -17676,9 +17676,9 @@
       </c>
     </row>
     <row r="7" spans="1:133" ht="144" x14ac:dyDescent="0.2">
-      <c r="A7" s="421"/>
-      <c r="B7" s="423"/>
-      <c r="C7" s="425"/>
+      <c r="A7" s="437"/>
+      <c r="B7" s="439"/>
+      <c r="C7" s="441"/>
       <c r="D7" s="73" t="s">
         <v>63</v>
       </c>
@@ -17698,9 +17698,9 @@
       </c>
     </row>
     <row r="8" spans="1:133" ht="108" x14ac:dyDescent="0.2">
-      <c r="A8" s="421"/>
-      <c r="B8" s="423"/>
-      <c r="C8" s="425"/>
+      <c r="A8" s="437"/>
+      <c r="B8" s="439"/>
+      <c r="C8" s="441"/>
       <c r="D8" s="73" t="s">
         <v>68</v>
       </c>
@@ -17720,9 +17720,9 @@
       </c>
     </row>
     <row r="9" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A9" s="421"/>
-      <c r="B9" s="423"/>
-      <c r="C9" s="425"/>
+      <c r="A9" s="437"/>
+      <c r="B9" s="439"/>
+      <c r="C9" s="441"/>
       <c r="D9" s="73" t="s">
         <v>72</v>
       </c>
@@ -17742,9 +17742,9 @@
       </c>
     </row>
     <row r="10" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="421"/>
-      <c r="B10" s="423"/>
-      <c r="C10" s="425"/>
+      <c r="A10" s="437"/>
+      <c r="B10" s="439"/>
+      <c r="C10" s="441"/>
       <c r="D10" s="237" t="s">
         <v>76</v>
       </c>
@@ -17764,9 +17764,9 @@
       </c>
     </row>
     <row r="11" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A11" s="421"/>
-      <c r="B11" s="423"/>
-      <c r="C11" s="425"/>
+      <c r="A11" s="437"/>
+      <c r="B11" s="439"/>
+      <c r="C11" s="441"/>
       <c r="D11" s="237" t="s">
         <v>79</v>
       </c>
@@ -17788,9 +17788,9 @@
       </c>
     </row>
     <row r="12" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A12" s="421"/>
-      <c r="B12" s="423"/>
-      <c r="C12" s="425"/>
+      <c r="A12" s="437"/>
+      <c r="B12" s="439"/>
+      <c r="C12" s="441"/>
       <c r="D12" s="237" t="s">
         <v>83</v>
       </c>
@@ -17812,9 +17812,9 @@
       </c>
     </row>
     <row r="13" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" s="421"/>
-      <c r="B13" s="423"/>
-      <c r="C13" s="425"/>
+      <c r="A13" s="437"/>
+      <c r="B13" s="439"/>
+      <c r="C13" s="441"/>
       <c r="D13" s="73" t="s">
         <v>86</v>
       </c>
@@ -17836,9 +17836,9 @@
       </c>
     </row>
     <row r="14" spans="1:133" s="42" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A14" s="421"/>
-      <c r="B14" s="423"/>
-      <c r="C14" s="425"/>
+      <c r="A14" s="437"/>
+      <c r="B14" s="439"/>
+      <c r="C14" s="441"/>
       <c r="D14" s="73" t="s">
         <v>92</v>
       </c>
@@ -17983,9 +17983,9 @@
       <c r="EC14" s="41"/>
     </row>
     <row r="15" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="421"/>
-      <c r="B15" s="423"/>
-      <c r="C15" s="426"/>
+      <c r="A15" s="437"/>
+      <c r="B15" s="439"/>
+      <c r="C15" s="442"/>
       <c r="D15" s="73" t="s">
         <v>94</v>
       </c>
@@ -18005,13 +18005,13 @@
       </c>
     </row>
     <row r="16" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A16" s="427" t="s">
+      <c r="A16" s="432" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="428" t="s">
+      <c r="B16" s="433" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="429" t="s">
+      <c r="C16" s="443" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="73" t="s">
@@ -18033,9 +18033,9 @@
       </c>
     </row>
     <row r="17" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="427"/>
-      <c r="B17" s="428"/>
-      <c r="C17" s="430"/>
+      <c r="A17" s="432"/>
+      <c r="B17" s="433"/>
+      <c r="C17" s="444"/>
       <c r="D17" s="73" t="s">
         <v>56</v>
       </c>
@@ -18057,9 +18057,9 @@
       </c>
     </row>
     <row r="18" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A18" s="427"/>
-      <c r="B18" s="428"/>
-      <c r="C18" s="430"/>
+      <c r="A18" s="432"/>
+      <c r="B18" s="433"/>
+      <c r="C18" s="444"/>
       <c r="D18" s="237" t="s">
         <v>61</v>
       </c>
@@ -18079,13 +18079,13 @@
       </c>
     </row>
     <row r="19" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="427"/>
-      <c r="B19" s="428"/>
-      <c r="C19" s="430"/>
-      <c r="D19" s="431" t="s">
+      <c r="A19" s="432"/>
+      <c r="B19" s="433"/>
+      <c r="C19" s="444"/>
+      <c r="D19" s="445" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="433" t="s">
+      <c r="E19" s="430" t="s">
         <v>77</v>
       </c>
       <c r="F19" s="73" t="s">
@@ -18101,11 +18101,11 @@
       </c>
     </row>
     <row r="20" spans="1:133" s="47" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="427"/>
-      <c r="B20" s="428"/>
-      <c r="C20" s="430"/>
-      <c r="D20" s="432"/>
-      <c r="E20" s="434"/>
+      <c r="A20" s="432"/>
+      <c r="B20" s="433"/>
+      <c r="C20" s="444"/>
+      <c r="D20" s="446"/>
+      <c r="E20" s="431"/>
       <c r="F20" s="73" t="s">
         <v>103</v>
       </c>
@@ -18242,9 +18242,9 @@
       <c r="EC20" s="36"/>
     </row>
     <row r="21" spans="1:133" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A21" s="427"/>
-      <c r="B21" s="428"/>
-      <c r="C21" s="430"/>
+      <c r="A21" s="432"/>
+      <c r="B21" s="433"/>
+      <c r="C21" s="444"/>
       <c r="D21" s="237" t="s">
         <v>79</v>
       </c>
@@ -18389,9 +18389,9 @@
       <c r="EC21" s="36"/>
     </row>
     <row r="22" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A22" s="427"/>
-      <c r="B22" s="428"/>
-      <c r="C22" s="430"/>
+      <c r="A22" s="432"/>
+      <c r="B22" s="433"/>
+      <c r="C22" s="444"/>
       <c r="D22" s="237" t="s">
         <v>83</v>
       </c>
@@ -18413,9 +18413,9 @@
       </c>
     </row>
     <row r="23" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A23" s="427"/>
-      <c r="B23" s="428"/>
-      <c r="C23" s="430"/>
+      <c r="A23" s="432"/>
+      <c r="B23" s="433"/>
+      <c r="C23" s="444"/>
       <c r="D23" s="73" t="s">
         <v>106</v>
       </c>
@@ -18437,9 +18437,9 @@
       </c>
     </row>
     <row r="24" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A24" s="427"/>
-      <c r="B24" s="428"/>
-      <c r="C24" s="430"/>
+      <c r="A24" s="432"/>
+      <c r="B24" s="433"/>
+      <c r="C24" s="444"/>
       <c r="D24" s="73" t="s">
         <v>92</v>
       </c>
@@ -18461,9 +18461,9 @@
       </c>
     </row>
     <row r="25" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A25" s="420"/>
-      <c r="B25" s="422"/>
-      <c r="C25" s="430"/>
+      <c r="A25" s="436"/>
+      <c r="B25" s="438"/>
+      <c r="C25" s="444"/>
       <c r="D25" s="73" t="s">
         <v>94</v>
       </c>
@@ -18483,13 +18483,13 @@
       </c>
     </row>
     <row r="26" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A26" s="437" t="s">
+      <c r="A26" s="419" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="440" t="s">
+      <c r="B26" s="422" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="443" t="s">
+      <c r="C26" s="425" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="73" t="s">
@@ -18511,9 +18511,9 @@
       </c>
     </row>
     <row r="27" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A27" s="438"/>
-      <c r="B27" s="441"/>
-      <c r="C27" s="444"/>
+      <c r="A27" s="420"/>
+      <c r="B27" s="423"/>
+      <c r="C27" s="426"/>
       <c r="D27" s="73" t="s">
         <v>56</v>
       </c>
@@ -18535,9 +18535,9 @@
       </c>
     </row>
     <row r="28" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" s="438"/>
-      <c r="B28" s="441"/>
-      <c r="C28" s="444"/>
+      <c r="A28" s="420"/>
+      <c r="B28" s="423"/>
+      <c r="C28" s="426"/>
       <c r="D28" s="237" t="s">
         <v>61</v>
       </c>
@@ -18559,13 +18559,13 @@
       </c>
     </row>
     <row r="29" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="438"/>
-      <c r="B29" s="441"/>
-      <c r="C29" s="444"/>
-      <c r="D29" s="446" t="s">
+      <c r="A29" s="420"/>
+      <c r="B29" s="423"/>
+      <c r="C29" s="426"/>
+      <c r="D29" s="428" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="433" t="s">
+      <c r="E29" s="430" t="s">
         <v>77</v>
       </c>
       <c r="F29" s="73" t="s">
@@ -18581,11 +18581,11 @@
       </c>
     </row>
     <row r="30" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="438"/>
-      <c r="B30" s="441"/>
-      <c r="C30" s="444"/>
-      <c r="D30" s="447"/>
-      <c r="E30" s="434"/>
+      <c r="A30" s="420"/>
+      <c r="B30" s="423"/>
+      <c r="C30" s="426"/>
+      <c r="D30" s="429"/>
+      <c r="E30" s="431"/>
       <c r="F30" s="73" t="s">
         <v>113</v>
       </c>
@@ -18601,9 +18601,9 @@
       </c>
     </row>
     <row r="31" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A31" s="438"/>
-      <c r="B31" s="441"/>
-      <c r="C31" s="444"/>
+      <c r="A31" s="420"/>
+      <c r="B31" s="423"/>
+      <c r="C31" s="426"/>
       <c r="D31" s="237" t="s">
         <v>79</v>
       </c>
@@ -18625,9 +18625,9 @@
       </c>
     </row>
     <row r="32" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A32" s="438"/>
-      <c r="B32" s="441"/>
-      <c r="C32" s="444"/>
+      <c r="A32" s="420"/>
+      <c r="B32" s="423"/>
+      <c r="C32" s="426"/>
       <c r="D32" s="237" t="s">
         <v>83</v>
       </c>
@@ -18649,9 +18649,9 @@
       </c>
     </row>
     <row r="33" spans="1:133" s="47" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A33" s="438"/>
-      <c r="B33" s="441"/>
-      <c r="C33" s="444"/>
+      <c r="A33" s="420"/>
+      <c r="B33" s="423"/>
+      <c r="C33" s="426"/>
       <c r="D33" s="261" t="s">
         <v>114</v>
       </c>
@@ -18796,9 +18796,9 @@
       <c r="EC33" s="36"/>
     </row>
     <row r="34" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A34" s="438"/>
-      <c r="B34" s="441"/>
-      <c r="C34" s="444"/>
+      <c r="A34" s="420"/>
+      <c r="B34" s="423"/>
+      <c r="C34" s="426"/>
       <c r="D34" s="268" t="s">
         <v>92</v>
       </c>
@@ -18943,9 +18943,9 @@
       <c r="EC34" s="36"/>
     </row>
     <row r="35" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A35" s="439"/>
-      <c r="B35" s="442"/>
-      <c r="C35" s="445"/>
+      <c r="A35" s="421"/>
+      <c r="B35" s="424"/>
+      <c r="C35" s="427"/>
       <c r="D35" s="73" t="s">
         <v>94</v>
       </c>
@@ -18965,13 +18965,13 @@
       </c>
     </row>
     <row r="36" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A36" s="437" t="s">
+      <c r="A36" s="419" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="440" t="s">
+      <c r="B36" s="422" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="443" t="s">
+      <c r="C36" s="425" t="s">
         <v>117</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -18995,9 +18995,9 @@
       </c>
     </row>
     <row r="37" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A37" s="438"/>
-      <c r="B37" s="441"/>
-      <c r="C37" s="444"/>
+      <c r="A37" s="420"/>
+      <c r="B37" s="423"/>
+      <c r="C37" s="426"/>
       <c r="D37" s="189" t="s">
         <v>122</v>
       </c>
@@ -19019,9 +19019,9 @@
       </c>
     </row>
     <row r="38" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A38" s="438"/>
-      <c r="B38" s="441"/>
-      <c r="C38" s="444"/>
+      <c r="A38" s="420"/>
+      <c r="B38" s="423"/>
+      <c r="C38" s="426"/>
       <c r="D38" s="37" t="s">
         <v>126</v>
       </c>
@@ -19043,9 +19043,9 @@
       </c>
     </row>
     <row r="39" spans="1:133" ht="84" x14ac:dyDescent="0.2">
-      <c r="A39" s="438"/>
-      <c r="B39" s="441"/>
-      <c r="C39" s="444"/>
+      <c r="A39" s="420"/>
+      <c r="B39" s="423"/>
+      <c r="C39" s="426"/>
       <c r="D39" s="73" t="s">
         <v>130</v>
       </c>
@@ -19067,9 +19067,9 @@
       </c>
     </row>
     <row r="40" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A40" s="438"/>
-      <c r="B40" s="441"/>
-      <c r="C40" s="444"/>
+      <c r="A40" s="420"/>
+      <c r="B40" s="423"/>
+      <c r="C40" s="426"/>
       <c r="D40" s="189" t="s">
         <v>134</v>
       </c>
@@ -19089,9 +19089,9 @@
       </c>
     </row>
     <row r="41" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A41" s="438"/>
-      <c r="B41" s="441"/>
-      <c r="C41" s="444"/>
+      <c r="A41" s="420"/>
+      <c r="B41" s="423"/>
+      <c r="C41" s="426"/>
       <c r="D41" s="237" t="s">
         <v>61</v>
       </c>
@@ -19113,9 +19113,9 @@
       </c>
     </row>
     <row r="42" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A42" s="438"/>
-      <c r="B42" s="441"/>
-      <c r="C42" s="444"/>
+      <c r="A42" s="420"/>
+      <c r="B42" s="423"/>
+      <c r="C42" s="426"/>
       <c r="D42" s="73" t="s">
         <v>76</v>
       </c>
@@ -19137,9 +19137,9 @@
       </c>
     </row>
     <row r="43" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A43" s="438"/>
-      <c r="B43" s="441"/>
-      <c r="C43" s="444"/>
+      <c r="A43" s="420"/>
+      <c r="B43" s="423"/>
+      <c r="C43" s="426"/>
       <c r="D43" s="73" t="s">
         <v>138</v>
       </c>
@@ -19161,9 +19161,9 @@
       </c>
     </row>
     <row r="44" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A44" s="438"/>
-      <c r="B44" s="441"/>
-      <c r="C44" s="444"/>
+      <c r="A44" s="420"/>
+      <c r="B44" s="423"/>
+      <c r="C44" s="426"/>
       <c r="D44" s="321" t="s">
         <v>92</v>
       </c>
@@ -19185,9 +19185,9 @@
       </c>
     </row>
     <row r="45" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A45" s="439"/>
-      <c r="B45" s="442"/>
-      <c r="C45" s="445"/>
+      <c r="A45" s="421"/>
+      <c r="B45" s="424"/>
+      <c r="C45" s="427"/>
       <c r="D45" s="73" t="s">
         <v>94</v>
       </c>
@@ -19223,13 +19223,13 @@
       <c r="J46" s="71"/>
     </row>
     <row r="47" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A47" s="427" t="s">
+      <c r="A47" s="432" t="s">
         <v>141</v>
       </c>
-      <c r="B47" s="428" t="s">
+      <c r="B47" s="433" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="436" t="s">
+      <c r="C47" s="434" t="s">
         <v>142</v>
       </c>
       <c r="D47" s="73" t="s">
@@ -19251,9 +19251,9 @@
       </c>
     </row>
     <row r="48" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A48" s="427"/>
-      <c r="B48" s="428"/>
-      <c r="C48" s="436"/>
+      <c r="A48" s="432"/>
+      <c r="B48" s="433"/>
+      <c r="C48" s="434"/>
       <c r="D48" s="73" t="s">
         <v>56</v>
       </c>
@@ -19273,9 +19273,9 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="24" x14ac:dyDescent="0.2">
-      <c r="A49" s="427"/>
-      <c r="B49" s="428"/>
-      <c r="C49" s="436"/>
+      <c r="A49" s="432"/>
+      <c r="B49" s="433"/>
+      <c r="C49" s="434"/>
       <c r="D49" s="237" t="s">
         <v>61</v>
       </c>
@@ -19295,9 +19295,9 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="427"/>
-      <c r="B50" s="428"/>
-      <c r="C50" s="436"/>
+      <c r="A50" s="432"/>
+      <c r="B50" s="433"/>
+      <c r="C50" s="434"/>
       <c r="D50" s="73" t="s">
         <v>63</v>
       </c>
@@ -19317,9 +19317,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="108" x14ac:dyDescent="0.2">
-      <c r="A51" s="427"/>
-      <c r="B51" s="428"/>
-      <c r="C51" s="436"/>
+      <c r="A51" s="432"/>
+      <c r="B51" s="433"/>
+      <c r="C51" s="434"/>
       <c r="D51" s="73" t="s">
         <v>68</v>
       </c>
@@ -19339,9 +19339,9 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A52" s="427"/>
-      <c r="B52" s="428"/>
-      <c r="C52" s="436"/>
+      <c r="A52" s="432"/>
+      <c r="B52" s="433"/>
+      <c r="C52" s="434"/>
       <c r="D52" s="73" t="s">
         <v>143</v>
       </c>
@@ -19361,9 +19361,9 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A53" s="427"/>
-      <c r="B53" s="428"/>
-      <c r="C53" s="436"/>
+      <c r="A53" s="432"/>
+      <c r="B53" s="433"/>
+      <c r="C53" s="434"/>
       <c r="D53" s="237" t="s">
         <v>76</v>
       </c>
@@ -19383,9 +19383,9 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="75" x14ac:dyDescent="0.2">
-      <c r="A54" s="427"/>
-      <c r="B54" s="428"/>
-      <c r="C54" s="436"/>
+      <c r="A54" s="432"/>
+      <c r="B54" s="433"/>
+      <c r="C54" s="434"/>
       <c r="D54" s="237" t="s">
         <v>79</v>
       </c>
@@ -19407,9 +19407,9 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A55" s="427"/>
-      <c r="B55" s="428"/>
-      <c r="C55" s="436"/>
+      <c r="A55" s="432"/>
+      <c r="B55" s="433"/>
+      <c r="C55" s="434"/>
       <c r="D55" s="237" t="s">
         <v>83</v>
       </c>
@@ -19431,9 +19431,9 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A56" s="427"/>
-      <c r="B56" s="428"/>
-      <c r="C56" s="436"/>
+      <c r="A56" s="432"/>
+      <c r="B56" s="433"/>
+      <c r="C56" s="434"/>
       <c r="D56" s="73" t="s">
         <v>106</v>
       </c>
@@ -19455,9 +19455,9 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A57" s="427"/>
-      <c r="B57" s="428"/>
-      <c r="C57" s="436"/>
+      <c r="A57" s="432"/>
+      <c r="B57" s="433"/>
+      <c r="C57" s="434"/>
       <c r="D57" s="73" t="s">
         <v>92</v>
       </c>
@@ -19479,9 +19479,9 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="45" x14ac:dyDescent="0.2">
-      <c r="A58" s="427"/>
-      <c r="B58" s="428"/>
-      <c r="C58" s="436"/>
+      <c r="A58" s="432"/>
+      <c r="B58" s="433"/>
+      <c r="C58" s="434"/>
       <c r="D58" s="73" t="s">
         <v>94</v>
       </c>
@@ -19503,17 +19503,6 @@
   </sheetData>
   <autoFilter ref="A2:EC43" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="21">
-    <mergeCell ref="A26:A35"/>
-    <mergeCell ref="B26:B35"/>
-    <mergeCell ref="C26:C35"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A47:A58"/>
-    <mergeCell ref="B47:B58"/>
-    <mergeCell ref="C47:C58"/>
-    <mergeCell ref="A36:A45"/>
-    <mergeCell ref="B36:B45"/>
-    <mergeCell ref="C36:C45"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="A4:A15"/>
     <mergeCell ref="B4:B15"/>
@@ -19524,6 +19513,17 @@
     <mergeCell ref="D19:D20"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A47:A58"/>
+    <mergeCell ref="B47:B58"/>
+    <mergeCell ref="C47:C58"/>
+    <mergeCell ref="A36:A45"/>
+    <mergeCell ref="B36:B45"/>
+    <mergeCell ref="C36:C45"/>
+    <mergeCell ref="A26:A35"/>
+    <mergeCell ref="B26:B35"/>
+    <mergeCell ref="C26:C35"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -19983,32 +19983,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:138" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="537"/>
-      <c r="B1" s="537"/>
-      <c r="C1" s="537"/>
-      <c r="D1" s="537"/>
-      <c r="E1" s="537"/>
-      <c r="F1" s="537"/>
-      <c r="G1" s="537"/>
+      <c r="A1" s="536"/>
+      <c r="B1" s="536"/>
+      <c r="C1" s="536"/>
+      <c r="D1" s="536"/>
+      <c r="E1" s="536"/>
+      <c r="F1" s="536"/>
+      <c r="G1" s="536"/>
       <c r="H1" s="104"/>
       <c r="I1" s="101"/>
       <c r="J1" s="102"/>
     </row>
     <row r="2" spans="1:138" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="538" t="s">
+      <c r="A2" s="537" t="s">
         <v>433</v>
       </c>
-      <c r="B2" s="538"/>
-      <c r="C2" s="538"/>
-      <c r="D2" s="538"/>
-      <c r="E2" s="538"/>
-      <c r="F2" s="538"/>
-      <c r="G2" s="538"/>
+      <c r="B2" s="537"/>
+      <c r="C2" s="537"/>
+      <c r="D2" s="537"/>
+      <c r="E2" s="537"/>
+      <c r="F2" s="537"/>
+      <c r="G2" s="537"/>
       <c r="H2" s="105"/>
-      <c r="I2" s="419" t="s">
+      <c r="I2" s="435" t="s">
         <v>416</v>
       </c>
-      <c r="J2" s="419"/>
+      <c r="J2" s="435"/>
     </row>
     <row r="3" spans="1:138" s="31" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="64"/>
@@ -20052,13 +20052,13 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="486">
+      <c r="A5" s="500">
         <v>1</v>
       </c>
-      <c r="B5" s="422" t="s">
+      <c r="B5" s="438" t="s">
         <v>434</v>
       </c>
-      <c r="C5" s="429" t="s">
+      <c r="C5" s="443" t="s">
         <v>435</v>
       </c>
       <c r="D5" s="73" t="s">
@@ -20080,9 +20080,9 @@
       </c>
     </row>
     <row r="6" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="487"/>
-      <c r="B6" s="423"/>
-      <c r="C6" s="430"/>
+      <c r="A6" s="501"/>
+      <c r="B6" s="439"/>
+      <c r="C6" s="444"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
       </c>
@@ -20102,9 +20102,9 @@
       </c>
     </row>
     <row r="7" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="487"/>
-      <c r="B7" s="423"/>
-      <c r="C7" s="430"/>
+      <c r="A7" s="501"/>
+      <c r="B7" s="439"/>
+      <c r="C7" s="444"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
       </c>
@@ -20124,9 +20124,9 @@
       </c>
     </row>
     <row r="8" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="487"/>
-      <c r="B8" s="423"/>
-      <c r="C8" s="430"/>
+      <c r="A8" s="501"/>
+      <c r="B8" s="439"/>
+      <c r="C8" s="444"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
       </c>
@@ -20147,9 +20147,9 @@
       <c r="K8" s="38"/>
     </row>
     <row r="9" spans="1:138" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="487"/>
-      <c r="B9" s="423"/>
-      <c r="C9" s="430"/>
+      <c r="A9" s="501"/>
+      <c r="B9" s="439"/>
+      <c r="C9" s="444"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
       </c>
@@ -20169,9 +20169,9 @@
       </c>
     </row>
     <row r="10" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="487"/>
-      <c r="B10" s="423"/>
-      <c r="C10" s="430"/>
+      <c r="A10" s="501"/>
+      <c r="B10" s="439"/>
+      <c r="C10" s="444"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
       </c>
@@ -20191,9 +20191,9 @@
       </c>
     </row>
     <row r="11" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="487"/>
-      <c r="B11" s="423"/>
-      <c r="C11" s="430"/>
+      <c r="A11" s="501"/>
+      <c r="B11" s="439"/>
+      <c r="C11" s="444"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
       </c>
@@ -20215,9 +20215,9 @@
       </c>
     </row>
     <row r="12" spans="1:138" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="487"/>
-      <c r="B12" s="423"/>
-      <c r="C12" s="430"/>
+      <c r="A12" s="501"/>
+      <c r="B12" s="439"/>
+      <c r="C12" s="444"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
       </c>
@@ -20367,9 +20367,9 @@
       <c r="EH12" s="41"/>
     </row>
     <row r="13" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="487"/>
-      <c r="B13" s="423"/>
-      <c r="C13" s="430"/>
+      <c r="A13" s="501"/>
+      <c r="B13" s="439"/>
+      <c r="C13" s="444"/>
       <c r="D13" s="73" t="s">
         <v>318</v>
       </c>
@@ -20389,13 +20389,13 @@
       </c>
     </row>
     <row r="14" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="491">
+      <c r="A14" s="505">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="492" t="s">
+      <c r="B14" s="506" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="429" t="s">
+      <c r="C14" s="443" t="s">
         <v>436</v>
       </c>
       <c r="D14" s="73" t="s">
@@ -20417,9 +20417,9 @@
       </c>
     </row>
     <row r="15" spans="1:138" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="491"/>
-      <c r="B15" s="492"/>
-      <c r="C15" s="536"/>
+      <c r="A15" s="505"/>
+      <c r="B15" s="506"/>
+      <c r="C15" s="538"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
       </c>
@@ -20441,9 +20441,9 @@
       </c>
     </row>
     <row r="16" spans="1:138" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="491"/>
-      <c r="B16" s="492"/>
-      <c r="C16" s="536"/>
+      <c r="A16" s="505"/>
+      <c r="B16" s="506"/>
+      <c r="C16" s="538"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
       </c>
@@ -20466,9 +20466,9 @@
       <c r="K16" s="38"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="491"/>
-      <c r="B17" s="492"/>
-      <c r="C17" s="536"/>
+      <c r="A17" s="505"/>
+      <c r="B17" s="506"/>
+      <c r="C17" s="538"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
       </c>
@@ -20618,9 +20618,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="491"/>
-      <c r="B18" s="492"/>
-      <c r="C18" s="536"/>
+      <c r="A18" s="505"/>
+      <c r="B18" s="506"/>
+      <c r="C18" s="538"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
       </c>
@@ -20770,9 +20770,9 @@
       <c r="EH18" s="36"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="486"/>
-      <c r="B19" s="493"/>
-      <c r="C19" s="536"/>
+      <c r="A19" s="500"/>
+      <c r="B19" s="507"/>
+      <c r="C19" s="538"/>
       <c r="D19" s="78" t="s">
         <v>318</v>
       </c>
@@ -20792,10 +20792,10 @@
       </c>
     </row>
     <row r="20" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="494">
+      <c r="A20" s="486">
         <v>2</v>
       </c>
-      <c r="B20" s="495" t="s">
+      <c r="B20" s="487" t="s">
         <v>109</v>
       </c>
       <c r="C20" s="480" t="s">
@@ -20820,8 +20820,8 @@
       </c>
     </row>
     <row r="21" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="494"/>
-      <c r="B21" s="495"/>
+      <c r="A21" s="486"/>
+      <c r="B21" s="487"/>
       <c r="C21" s="528"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
@@ -20844,8 +20844,8 @@
       </c>
     </row>
     <row r="22" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A22" s="494"/>
-      <c r="B22" s="495"/>
+      <c r="A22" s="486"/>
+      <c r="B22" s="487"/>
       <c r="C22" s="528"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
@@ -20868,8 +20868,8 @@
       </c>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A23" s="494"/>
-      <c r="B23" s="495"/>
+      <c r="A23" s="486"/>
+      <c r="B23" s="487"/>
       <c r="C23" s="528"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
@@ -21020,8 +21020,8 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A24" s="494"/>
-      <c r="B24" s="495"/>
+      <c r="A24" s="486"/>
+      <c r="B24" s="487"/>
       <c r="C24" s="528"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
@@ -21172,8 +21172,8 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="494"/>
-      <c r="B25" s="495"/>
+      <c r="A25" s="486"/>
+      <c r="B25" s="487"/>
       <c r="C25" s="529"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
@@ -21194,13 +21194,13 @@
       </c>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="499">
+      <c r="A26" s="491">
         <v>2.1</v>
       </c>
-      <c r="B26" s="502" t="s">
+      <c r="B26" s="494" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="505" t="s">
+      <c r="C26" s="497" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="83" t="s">
@@ -21222,9 +21222,9 @@
       </c>
     </row>
     <row r="27" spans="1:138" ht="105" x14ac:dyDescent="0.2">
-      <c r="A27" s="500"/>
-      <c r="B27" s="503"/>
-      <c r="C27" s="506"/>
+      <c r="A27" s="492"/>
+      <c r="B27" s="495"/>
+      <c r="C27" s="498"/>
       <c r="D27" s="83" t="s">
         <v>130</v>
       </c>
@@ -21244,9 +21244,9 @@
       </c>
     </row>
     <row r="28" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A28" s="500"/>
-      <c r="B28" s="503"/>
-      <c r="C28" s="506"/>
+      <c r="A28" s="492"/>
+      <c r="B28" s="495"/>
+      <c r="C28" s="498"/>
       <c r="D28" s="73" t="s">
         <v>55</v>
       </c>
@@ -21268,9 +21268,9 @@
       </c>
     </row>
     <row r="29" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A29" s="500"/>
-      <c r="B29" s="503"/>
-      <c r="C29" s="506"/>
+      <c r="A29" s="492"/>
+      <c r="B29" s="495"/>
+      <c r="C29" s="498"/>
       <c r="D29" s="61" t="s">
         <v>114</v>
       </c>
@@ -21292,9 +21292,9 @@
       </c>
     </row>
     <row r="30" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="500"/>
-      <c r="B30" s="503"/>
-      <c r="C30" s="506"/>
+      <c r="A30" s="492"/>
+      <c r="B30" s="495"/>
+      <c r="C30" s="498"/>
       <c r="D30" s="86" t="s">
         <v>92</v>
       </c>
@@ -21316,9 +21316,9 @@
       </c>
     </row>
     <row r="31" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="501"/>
-      <c r="B31" s="504"/>
-      <c r="C31" s="507"/>
+      <c r="A31" s="493"/>
+      <c r="B31" s="496"/>
+      <c r="C31" s="499"/>
       <c r="D31" s="76" t="s">
         <v>94</v>
       </c>
@@ -21460,24 +21460,24 @@
   </sheetData>
   <autoFilter ref="A4:EH32" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="18">
+    <mergeCell ref="A26:A31"/>
+    <mergeCell ref="B26:B31"/>
+    <mergeCell ref="C26:C31"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="C14:C19"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="C20:C25"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="A5:A13"/>
     <mergeCell ref="B5:B13"/>
     <mergeCell ref="C5:C13"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="C14:C19"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="C20:C25"/>
-    <mergeCell ref="A26:A31"/>
-    <mergeCell ref="B26:B31"/>
-    <mergeCell ref="C26:C31"/>
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="B32:B36"/>
-    <mergeCell ref="C32:C36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -21505,33 +21505,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:139" s="31" customFormat="1" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="537"/>
-      <c r="B1" s="537"/>
-      <c r="C1" s="537"/>
-      <c r="D1" s="537"/>
-      <c r="E1" s="537"/>
-      <c r="F1" s="537"/>
-      <c r="G1" s="537"/>
+      <c r="A1" s="536"/>
+      <c r="B1" s="536"/>
+      <c r="C1" s="536"/>
+      <c r="D1" s="536"/>
+      <c r="E1" s="536"/>
+      <c r="F1" s="536"/>
+      <c r="G1" s="536"/>
       <c r="H1" s="104"/>
       <c r="I1" s="101"/>
       <c r="J1" s="102"/>
       <c r="K1" s="102"/>
     </row>
     <row r="2" spans="1:139" s="31" customFormat="1" ht="25" x14ac:dyDescent="0.2">
-      <c r="A2" s="538" t="s">
+      <c r="A2" s="537" t="s">
         <v>415</v>
       </c>
-      <c r="B2" s="538"/>
-      <c r="C2" s="538"/>
-      <c r="D2" s="538"/>
-      <c r="E2" s="538"/>
-      <c r="F2" s="538"/>
-      <c r="G2" s="538"/>
+      <c r="B2" s="537"/>
+      <c r="C2" s="537"/>
+      <c r="D2" s="537"/>
+      <c r="E2" s="537"/>
+      <c r="F2" s="537"/>
+      <c r="G2" s="537"/>
       <c r="H2" s="105"/>
-      <c r="I2" s="419" t="s">
+      <c r="I2" s="435" t="s">
         <v>416</v>
       </c>
-      <c r="J2" s="419"/>
+      <c r="J2" s="435"/>
       <c r="K2" s="103"/>
     </row>
     <row r="3" spans="1:139" s="31" customFormat="1" ht="20" x14ac:dyDescent="0.2">
@@ -21580,10 +21580,10 @@
       </c>
     </row>
     <row r="5" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A5" s="486">
+      <c r="A5" s="500">
         <v>1</v>
       </c>
-      <c r="B5" s="422" t="s">
+      <c r="B5" s="438" t="s">
         <v>434</v>
       </c>
       <c r="C5" s="482" t="s">
@@ -21611,8 +21611,8 @@
       </c>
     </row>
     <row r="6" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A6" s="487"/>
-      <c r="B6" s="423"/>
+      <c r="A6" s="501"/>
+      <c r="B6" s="439"/>
       <c r="C6" s="483"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
@@ -21634,8 +21634,8 @@
       <c r="K6" s="35"/>
     </row>
     <row r="7" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="487"/>
-      <c r="B7" s="423"/>
+      <c r="A7" s="501"/>
+      <c r="B7" s="439"/>
       <c r="C7" s="483"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
@@ -21657,8 +21657,8 @@
       <c r="K7" s="35"/>
     </row>
     <row r="8" spans="1:139" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="487"/>
-      <c r="B8" s="423"/>
+      <c r="A8" s="501"/>
+      <c r="B8" s="439"/>
       <c r="C8" s="483"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
@@ -21681,8 +21681,8 @@
       <c r="L8" s="38"/>
     </row>
     <row r="9" spans="1:139" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="487"/>
-      <c r="B9" s="423"/>
+      <c r="A9" s="501"/>
+      <c r="B9" s="439"/>
       <c r="C9" s="483"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
@@ -21704,8 +21704,8 @@
       <c r="K9" s="35"/>
     </row>
     <row r="10" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="487"/>
-      <c r="B10" s="423"/>
+      <c r="A10" s="501"/>
+      <c r="B10" s="439"/>
       <c r="C10" s="483"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
@@ -21727,8 +21727,8 @@
       <c r="K10" s="35"/>
     </row>
     <row r="11" spans="1:139" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="487"/>
-      <c r="B11" s="423"/>
+      <c r="A11" s="501"/>
+      <c r="B11" s="439"/>
       <c r="C11" s="483"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
@@ -21766,8 +21766,8 @@
       </c>
     </row>
     <row r="12" spans="1:139" s="42" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A12" s="487"/>
-      <c r="B12" s="423"/>
+      <c r="A12" s="501"/>
+      <c r="B12" s="439"/>
       <c r="C12" s="483"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
@@ -21933,8 +21933,8 @@
       <c r="EI12" s="41"/>
     </row>
     <row r="13" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="487"/>
-      <c r="B13" s="423"/>
+      <c r="A13" s="501"/>
+      <c r="B13" s="439"/>
       <c r="C13" s="483"/>
       <c r="D13" s="73" t="s">
         <v>318</v>
@@ -21958,10 +21958,10 @@
       </c>
     </row>
     <row r="14" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="491">
+      <c r="A14" s="505">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="492" t="s">
+      <c r="B14" s="506" t="s">
         <v>98</v>
       </c>
       <c r="C14" s="482" t="s">
@@ -21989,8 +21989,8 @@
       </c>
     </row>
     <row r="15" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="491"/>
-      <c r="B15" s="492"/>
+      <c r="A15" s="505"/>
+      <c r="B15" s="506"/>
       <c r="C15" s="539"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
@@ -22014,8 +22014,8 @@
       <c r="K15" s="35"/>
     </row>
     <row r="16" spans="1:139" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="491"/>
-      <c r="B16" s="492"/>
+      <c r="A16" s="505"/>
+      <c r="B16" s="506"/>
       <c r="C16" s="539"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
@@ -22054,8 +22054,8 @@
       <c r="L16" s="38"/>
     </row>
     <row r="17" spans="1:139" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A17" s="491"/>
-      <c r="B17" s="492"/>
+      <c r="A17" s="505"/>
+      <c r="B17" s="506"/>
       <c r="C17" s="539"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
@@ -22221,8 +22221,8 @@
       <c r="EI17" s="36"/>
     </row>
     <row r="18" spans="1:139" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A18" s="491"/>
-      <c r="B18" s="492"/>
+      <c r="A18" s="505"/>
+      <c r="B18" s="506"/>
       <c r="C18" s="539"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
@@ -22386,8 +22386,8 @@
       <c r="EI18" s="36"/>
     </row>
     <row r="19" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="486"/>
-      <c r="B19" s="493"/>
+      <c r="A19" s="500"/>
+      <c r="B19" s="507"/>
       <c r="C19" s="539"/>
       <c r="D19" s="78" t="s">
         <v>318</v>
@@ -22411,10 +22411,10 @@
       </c>
     </row>
     <row r="20" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="494">
+      <c r="A20" s="486">
         <v>2</v>
       </c>
-      <c r="B20" s="495" t="s">
+      <c r="B20" s="487" t="s">
         <v>109</v>
       </c>
       <c r="C20" s="480" t="s">
@@ -22440,8 +22440,8 @@
       <c r="K20" s="54"/>
     </row>
     <row r="21" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="494"/>
-      <c r="B21" s="495"/>
+      <c r="A21" s="486"/>
+      <c r="B21" s="487"/>
       <c r="C21" s="528"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
@@ -22465,8 +22465,8 @@
       <c r="K21" s="54"/>
     </row>
     <row r="22" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A22" s="494"/>
-      <c r="B22" s="495"/>
+      <c r="A22" s="486"/>
+      <c r="B22" s="487"/>
       <c r="C22" s="528"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
@@ -22492,8 +22492,8 @@
       </c>
     </row>
     <row r="23" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A23" s="494"/>
-      <c r="B23" s="495"/>
+      <c r="A23" s="486"/>
+      <c r="B23" s="487"/>
       <c r="C23" s="528"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
@@ -22647,8 +22647,8 @@
       <c r="EI23" s="36"/>
     </row>
     <row r="24" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A24" s="494"/>
-      <c r="B24" s="495"/>
+      <c r="A24" s="486"/>
+      <c r="B24" s="487"/>
       <c r="C24" s="528"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
@@ -22802,8 +22802,8 @@
       <c r="EI24" s="36"/>
     </row>
     <row r="25" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="494"/>
-      <c r="B25" s="495"/>
+      <c r="A25" s="486"/>
+      <c r="B25" s="487"/>
       <c r="C25" s="529"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
@@ -22827,13 +22827,13 @@
       </c>
     </row>
     <row r="26" spans="1:139" ht="90" x14ac:dyDescent="0.2">
-      <c r="A26" s="499">
+      <c r="A26" s="491">
         <v>2.1</v>
       </c>
-      <c r="B26" s="502" t="s">
+      <c r="B26" s="494" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="505" t="s">
+      <c r="C26" s="497" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="76" t="s">
@@ -22856,9 +22856,9 @@
       <c r="K26" s="35"/>
     </row>
     <row r="27" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A27" s="500"/>
-      <c r="B27" s="503"/>
-      <c r="C27" s="506"/>
+      <c r="A27" s="492"/>
+      <c r="B27" s="495"/>
+      <c r="C27" s="498"/>
       <c r="D27" s="73" t="s">
         <v>55</v>
       </c>
@@ -22881,9 +22881,9 @@
       <c r="K27" s="35"/>
     </row>
     <row r="28" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A28" s="500"/>
-      <c r="B28" s="503"/>
-      <c r="C28" s="506"/>
+      <c r="A28" s="492"/>
+      <c r="B28" s="495"/>
+      <c r="C28" s="498"/>
       <c r="D28" s="61" t="s">
         <v>114</v>
       </c>
@@ -22906,9 +22906,9 @@
       <c r="K28" s="35"/>
     </row>
     <row r="29" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="500"/>
-      <c r="B29" s="503"/>
-      <c r="C29" s="506"/>
+      <c r="A29" s="492"/>
+      <c r="B29" s="495"/>
+      <c r="C29" s="498"/>
       <c r="D29" s="86" t="s">
         <v>92</v>
       </c>
@@ -22931,9 +22931,9 @@
       <c r="K29" s="35"/>
     </row>
     <row r="30" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="501"/>
-      <c r="B30" s="504"/>
-      <c r="C30" s="507"/>
+      <c r="A30" s="493"/>
+      <c r="B30" s="496"/>
+      <c r="C30" s="499"/>
       <c r="D30" s="76" t="s">
         <v>94</v>
       </c>
@@ -24146,12 +24146,6 @@
   </sheetData>
   <autoFilter ref="A4:EI31" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="15">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C5:C13"/>
     <mergeCell ref="A26:A30"/>
     <mergeCell ref="B26:B30"/>
     <mergeCell ref="C26:C30"/>
@@ -24161,6 +24155,12 @@
     <mergeCell ref="A20:A25"/>
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="C20:C25"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C5:C13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6:K7 K26" xr:uid="{71B7DFEE-6548-4738-BBF7-B2A60C74FD01}"/>
@@ -24770,33 +24770,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:139" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="537"/>
-      <c r="B1" s="537"/>
-      <c r="C1" s="537"/>
-      <c r="D1" s="537"/>
-      <c r="E1" s="537"/>
-      <c r="F1" s="537"/>
-      <c r="G1" s="537"/>
+      <c r="A1" s="536"/>
+      <c r="B1" s="536"/>
+      <c r="C1" s="536"/>
+      <c r="D1" s="536"/>
+      <c r="E1" s="536"/>
+      <c r="F1" s="536"/>
+      <c r="G1" s="536"/>
       <c r="H1" s="104"/>
       <c r="I1" s="101"/>
       <c r="J1" s="102"/>
       <c r="K1" s="102"/>
     </row>
     <row r="2" spans="1:139" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="538" t="s">
+      <c r="A2" s="537" t="s">
         <v>433</v>
       </c>
-      <c r="B2" s="538"/>
-      <c r="C2" s="538"/>
-      <c r="D2" s="538"/>
-      <c r="E2" s="538"/>
-      <c r="F2" s="538"/>
-      <c r="G2" s="538"/>
+      <c r="B2" s="537"/>
+      <c r="C2" s="537"/>
+      <c r="D2" s="537"/>
+      <c r="E2" s="537"/>
+      <c r="F2" s="537"/>
+      <c r="G2" s="537"/>
       <c r="H2" s="105"/>
-      <c r="I2" s="419" t="s">
+      <c r="I2" s="435" t="s">
         <v>416</v>
       </c>
-      <c r="J2" s="419"/>
+      <c r="J2" s="435"/>
       <c r="K2" s="103"/>
     </row>
     <row r="3" spans="1:139" s="31" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -24845,13 +24845,13 @@
       </c>
     </row>
     <row r="5" spans="1:139" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="486">
+      <c r="A5" s="500">
         <v>1</v>
       </c>
-      <c r="B5" s="422" t="s">
+      <c r="B5" s="438" t="s">
         <v>434</v>
       </c>
-      <c r="C5" s="429" t="s">
+      <c r="C5" s="443" t="s">
         <v>435</v>
       </c>
       <c r="D5" s="73" t="s">
@@ -24876,9 +24876,9 @@
       </c>
     </row>
     <row r="6" spans="1:139" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="487"/>
-      <c r="B6" s="423"/>
-      <c r="C6" s="430"/>
+      <c r="A6" s="501"/>
+      <c r="B6" s="439"/>
+      <c r="C6" s="444"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
       </c>
@@ -24899,9 +24899,9 @@
       <c r="K6" s="35"/>
     </row>
     <row r="7" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="487"/>
-      <c r="B7" s="423"/>
-      <c r="C7" s="430"/>
+      <c r="A7" s="501"/>
+      <c r="B7" s="439"/>
+      <c r="C7" s="444"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
       </c>
@@ -24922,9 +24922,9 @@
       <c r="K7" s="35"/>
     </row>
     <row r="8" spans="1:139" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="487"/>
-      <c r="B8" s="423"/>
-      <c r="C8" s="430"/>
+      <c r="A8" s="501"/>
+      <c r="B8" s="439"/>
+      <c r="C8" s="444"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
       </c>
@@ -24946,9 +24946,9 @@
       <c r="L8" s="38"/>
     </row>
     <row r="9" spans="1:139" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="487"/>
-      <c r="B9" s="423"/>
-      <c r="C9" s="430"/>
+      <c r="A9" s="501"/>
+      <c r="B9" s="439"/>
+      <c r="C9" s="444"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
       </c>
@@ -24969,9 +24969,9 @@
       <c r="K9" s="35"/>
     </row>
     <row r="10" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="487"/>
-      <c r="B10" s="423"/>
-      <c r="C10" s="430"/>
+      <c r="A10" s="501"/>
+      <c r="B10" s="439"/>
+      <c r="C10" s="444"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
       </c>
@@ -24992,9 +24992,9 @@
       <c r="K10" s="35"/>
     </row>
     <row r="11" spans="1:139" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="487"/>
-      <c r="B11" s="423"/>
-      <c r="C11" s="430"/>
+      <c r="A11" s="501"/>
+      <c r="B11" s="439"/>
+      <c r="C11" s="444"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
       </c>
@@ -25019,9 +25019,9 @@
       </c>
     </row>
     <row r="12" spans="1:139" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="487"/>
-      <c r="B12" s="423"/>
-      <c r="C12" s="430"/>
+      <c r="A12" s="501"/>
+      <c r="B12" s="439"/>
+      <c r="C12" s="444"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
       </c>
@@ -25174,9 +25174,9 @@
       <c r="EI12" s="41"/>
     </row>
     <row r="13" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="487"/>
-      <c r="B13" s="423"/>
-      <c r="C13" s="430"/>
+      <c r="A13" s="501"/>
+      <c r="B13" s="439"/>
+      <c r="C13" s="444"/>
       <c r="D13" s="73" t="s">
         <v>318</v>
       </c>
@@ -25199,13 +25199,13 @@
       </c>
     </row>
     <row r="14" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="491">
+      <c r="A14" s="505">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="492" t="s">
+      <c r="B14" s="506" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="429" t="s">
+      <c r="C14" s="443" t="s">
         <v>436</v>
       </c>
       <c r="D14" s="73" t="s">
@@ -25230,9 +25230,9 @@
       </c>
     </row>
     <row r="15" spans="1:139" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="491"/>
-      <c r="B15" s="492"/>
-      <c r="C15" s="536"/>
+      <c r="A15" s="505"/>
+      <c r="B15" s="506"/>
+      <c r="C15" s="538"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
       </c>
@@ -25255,9 +25255,9 @@
       <c r="K15" s="35"/>
     </row>
     <row r="16" spans="1:139" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="491"/>
-      <c r="B16" s="492"/>
-      <c r="C16" s="536"/>
+      <c r="A16" s="505"/>
+      <c r="B16" s="506"/>
+      <c r="C16" s="538"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
       </c>
@@ -25283,9 +25283,9 @@
       <c r="L16" s="38"/>
     </row>
     <row r="17" spans="1:139" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="491"/>
-      <c r="B17" s="492"/>
-      <c r="C17" s="536"/>
+      <c r="A17" s="505"/>
+      <c r="B17" s="506"/>
+      <c r="C17" s="538"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
       </c>
@@ -25438,9 +25438,9 @@
       <c r="EI17" s="36"/>
     </row>
     <row r="18" spans="1:139" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="491"/>
-      <c r="B18" s="492"/>
-      <c r="C18" s="536"/>
+      <c r="A18" s="505"/>
+      <c r="B18" s="506"/>
+      <c r="C18" s="538"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
       </c>
@@ -25591,9 +25591,9 @@
       <c r="EI18" s="36"/>
     </row>
     <row r="19" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="486"/>
-      <c r="B19" s="493"/>
-      <c r="C19" s="536"/>
+      <c r="A19" s="500"/>
+      <c r="B19" s="507"/>
+      <c r="C19" s="538"/>
       <c r="D19" s="78" t="s">
         <v>318</v>
       </c>
@@ -25616,10 +25616,10 @@
       </c>
     </row>
     <row r="20" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="494">
+      <c r="A20" s="486">
         <v>2</v>
       </c>
-      <c r="B20" s="495" t="s">
+      <c r="B20" s="487" t="s">
         <v>109</v>
       </c>
       <c r="C20" s="480" t="s">
@@ -25645,8 +25645,8 @@
       <c r="K20" s="54"/>
     </row>
     <row r="21" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="494"/>
-      <c r="B21" s="495"/>
+      <c r="A21" s="486"/>
+      <c r="B21" s="487"/>
       <c r="C21" s="528"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
@@ -25670,8 +25670,8 @@
       <c r="K21" s="54"/>
     </row>
     <row r="22" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A22" s="494"/>
-      <c r="B22" s="495"/>
+      <c r="A22" s="486"/>
+      <c r="B22" s="487"/>
       <c r="C22" s="528"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
@@ -25697,8 +25697,8 @@
       </c>
     </row>
     <row r="23" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A23" s="494"/>
-      <c r="B23" s="495"/>
+      <c r="A23" s="486"/>
+      <c r="B23" s="487"/>
       <c r="C23" s="528"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
@@ -25852,8 +25852,8 @@
       <c r="EI23" s="36"/>
     </row>
     <row r="24" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A24" s="494"/>
-      <c r="B24" s="495"/>
+      <c r="A24" s="486"/>
+      <c r="B24" s="487"/>
       <c r="C24" s="528"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
@@ -26007,8 +26007,8 @@
       <c r="EI24" s="36"/>
     </row>
     <row r="25" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="494"/>
-      <c r="B25" s="495"/>
+      <c r="A25" s="486"/>
+      <c r="B25" s="487"/>
       <c r="C25" s="529"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
@@ -26032,13 +26032,13 @@
       </c>
     </row>
     <row r="26" spans="1:139" ht="90" x14ac:dyDescent="0.2">
-      <c r="A26" s="499">
+      <c r="A26" s="491">
         <v>2.1</v>
       </c>
-      <c r="B26" s="502" t="s">
+      <c r="B26" s="494" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="505" t="s">
+      <c r="C26" s="497" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="76" t="s">
@@ -26061,9 +26061,9 @@
       <c r="K26" s="35"/>
     </row>
     <row r="27" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A27" s="500"/>
-      <c r="B27" s="503"/>
-      <c r="C27" s="506"/>
+      <c r="A27" s="492"/>
+      <c r="B27" s="495"/>
+      <c r="C27" s="498"/>
       <c r="D27" s="73" t="s">
         <v>55</v>
       </c>
@@ -26086,9 +26086,9 @@
       <c r="K27" s="35"/>
     </row>
     <row r="28" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A28" s="500"/>
-      <c r="B28" s="503"/>
-      <c r="C28" s="506"/>
+      <c r="A28" s="492"/>
+      <c r="B28" s="495"/>
+      <c r="C28" s="498"/>
       <c r="D28" s="61" t="s">
         <v>114</v>
       </c>
@@ -26111,9 +26111,9 @@
       <c r="K28" s="35"/>
     </row>
     <row r="29" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="500"/>
-      <c r="B29" s="503"/>
-      <c r="C29" s="506"/>
+      <c r="A29" s="492"/>
+      <c r="B29" s="495"/>
+      <c r="C29" s="498"/>
       <c r="D29" s="86" t="s">
         <v>92</v>
       </c>
@@ -26136,9 +26136,9 @@
       <c r="K29" s="35"/>
     </row>
     <row r="30" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="501"/>
-      <c r="B30" s="504"/>
-      <c r="C30" s="507"/>
+      <c r="A30" s="493"/>
+      <c r="B30" s="496"/>
+      <c r="C30" s="499"/>
       <c r="D30" s="76" t="s">
         <v>94</v>
       </c>
@@ -27351,12 +27351,6 @@
   </sheetData>
   <autoFilter ref="A4:EI31" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="15">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C5:C13"/>
     <mergeCell ref="A26:A30"/>
     <mergeCell ref="B26:B30"/>
     <mergeCell ref="C26:C30"/>
@@ -27366,6 +27360,12 @@
     <mergeCell ref="A20:A25"/>
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="C20:C25"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C5:C13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6:K7 K26" xr:uid="{EC1EB0C9-7584-409C-B7C9-CE8A33BC2994}"/>
@@ -27955,33 +27955,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:139" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="537"/>
-      <c r="B1" s="537"/>
-      <c r="C1" s="537"/>
-      <c r="D1" s="537"/>
-      <c r="E1" s="537"/>
-      <c r="F1" s="537"/>
-      <c r="G1" s="537"/>
+      <c r="A1" s="536"/>
+      <c r="B1" s="536"/>
+      <c r="C1" s="536"/>
+      <c r="D1" s="536"/>
+      <c r="E1" s="536"/>
+      <c r="F1" s="536"/>
+      <c r="G1" s="536"/>
       <c r="H1" s="104"/>
       <c r="I1" s="101"/>
       <c r="J1" s="102"/>
       <c r="K1" s="102"/>
     </row>
     <row r="2" spans="1:139" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="538" t="s">
+      <c r="A2" s="537" t="s">
         <v>469</v>
       </c>
-      <c r="B2" s="538"/>
-      <c r="C2" s="538"/>
-      <c r="D2" s="538"/>
-      <c r="E2" s="538"/>
-      <c r="F2" s="538"/>
-      <c r="G2" s="538"/>
+      <c r="B2" s="537"/>
+      <c r="C2" s="537"/>
+      <c r="D2" s="537"/>
+      <c r="E2" s="537"/>
+      <c r="F2" s="537"/>
+      <c r="G2" s="537"/>
       <c r="H2" s="105"/>
-      <c r="I2" s="419" t="s">
+      <c r="I2" s="435" t="s">
         <v>416</v>
       </c>
-      <c r="J2" s="419"/>
+      <c r="J2" s="435"/>
       <c r="K2" s="103"/>
     </row>
     <row r="3" spans="1:139" s="31" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28030,10 +28030,10 @@
       </c>
     </row>
     <row r="5" spans="1:139" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="486">
+      <c r="A5" s="500">
         <v>1</v>
       </c>
-      <c r="B5" s="422" t="s">
+      <c r="B5" s="438" t="s">
         <v>434</v>
       </c>
       <c r="C5" s="482" t="s">
@@ -28061,8 +28061,8 @@
       </c>
     </row>
     <row r="6" spans="1:139" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="487"/>
-      <c r="B6" s="423"/>
+      <c r="A6" s="501"/>
+      <c r="B6" s="439"/>
       <c r="C6" s="483"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
@@ -28084,8 +28084,8 @@
       <c r="K6" s="35"/>
     </row>
     <row r="7" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="487"/>
-      <c r="B7" s="423"/>
+      <c r="A7" s="501"/>
+      <c r="B7" s="439"/>
       <c r="C7" s="483"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
@@ -28107,8 +28107,8 @@
       <c r="K7" s="35"/>
     </row>
     <row r="8" spans="1:139" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="487"/>
-      <c r="B8" s="423"/>
+      <c r="A8" s="501"/>
+      <c r="B8" s="439"/>
       <c r="C8" s="483"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
@@ -28131,8 +28131,8 @@
       <c r="L8" s="38"/>
     </row>
     <row r="9" spans="1:139" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="487"/>
-      <c r="B9" s="423"/>
+      <c r="A9" s="501"/>
+      <c r="B9" s="439"/>
       <c r="C9" s="483"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
@@ -28154,8 +28154,8 @@
       <c r="K9" s="35"/>
     </row>
     <row r="10" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="487"/>
-      <c r="B10" s="423"/>
+      <c r="A10" s="501"/>
+      <c r="B10" s="439"/>
       <c r="C10" s="483"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
@@ -28177,8 +28177,8 @@
       <c r="K10" s="35"/>
     </row>
     <row r="11" spans="1:139" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="487"/>
-      <c r="B11" s="423"/>
+      <c r="A11" s="501"/>
+      <c r="B11" s="439"/>
       <c r="C11" s="483"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
@@ -28204,8 +28204,8 @@
       </c>
     </row>
     <row r="12" spans="1:139" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="487"/>
-      <c r="B12" s="423"/>
+      <c r="A12" s="501"/>
+      <c r="B12" s="439"/>
       <c r="C12" s="483"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
@@ -28359,8 +28359,8 @@
       <c r="EI12" s="41"/>
     </row>
     <row r="13" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="487"/>
-      <c r="B13" s="423"/>
+      <c r="A13" s="501"/>
+      <c r="B13" s="439"/>
       <c r="C13" s="483"/>
       <c r="D13" s="73" t="s">
         <v>318</v>
@@ -28384,10 +28384,10 @@
       </c>
     </row>
     <row r="14" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="491">
+      <c r="A14" s="505">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="492" t="s">
+      <c r="B14" s="506" t="s">
         <v>98</v>
       </c>
       <c r="C14" s="482" t="s">
@@ -28415,8 +28415,8 @@
       </c>
     </row>
     <row r="15" spans="1:139" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="491"/>
-      <c r="B15" s="492"/>
+      <c r="A15" s="505"/>
+      <c r="B15" s="506"/>
       <c r="C15" s="539"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
@@ -28440,8 +28440,8 @@
       <c r="K15" s="35"/>
     </row>
     <row r="16" spans="1:139" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="491"/>
-      <c r="B16" s="492"/>
+      <c r="A16" s="505"/>
+      <c r="B16" s="506"/>
       <c r="C16" s="539"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
@@ -28468,8 +28468,8 @@
       <c r="L16" s="38"/>
     </row>
     <row r="17" spans="1:139" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="491"/>
-      <c r="B17" s="492"/>
+      <c r="A17" s="505"/>
+      <c r="B17" s="506"/>
       <c r="C17" s="539"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
@@ -28623,8 +28623,8 @@
       <c r="EI17" s="36"/>
     </row>
     <row r="18" spans="1:139" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="491"/>
-      <c r="B18" s="492"/>
+      <c r="A18" s="505"/>
+      <c r="B18" s="506"/>
       <c r="C18" s="539"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
@@ -28776,8 +28776,8 @@
       <c r="EI18" s="36"/>
     </row>
     <row r="19" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="486"/>
-      <c r="B19" s="493"/>
+      <c r="A19" s="500"/>
+      <c r="B19" s="507"/>
       <c r="C19" s="539"/>
       <c r="D19" s="78" t="s">
         <v>318</v>
@@ -28801,10 +28801,10 @@
       </c>
     </row>
     <row r="20" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="494">
+      <c r="A20" s="486">
         <v>2</v>
       </c>
-      <c r="B20" s="495" t="s">
+      <c r="B20" s="487" t="s">
         <v>109</v>
       </c>
       <c r="C20" s="480" t="s">
@@ -28830,8 +28830,8 @@
       <c r="K20" s="54"/>
     </row>
     <row r="21" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="494"/>
-      <c r="B21" s="495"/>
+      <c r="A21" s="486"/>
+      <c r="B21" s="487"/>
       <c r="C21" s="528"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
@@ -28855,8 +28855,8 @@
       <c r="K21" s="54"/>
     </row>
     <row r="22" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A22" s="494"/>
-      <c r="B22" s="495"/>
+      <c r="A22" s="486"/>
+      <c r="B22" s="487"/>
       <c r="C22" s="528"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
@@ -28882,8 +28882,8 @@
       </c>
     </row>
     <row r="23" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A23" s="494"/>
-      <c r="B23" s="495"/>
+      <c r="A23" s="486"/>
+      <c r="B23" s="487"/>
       <c r="C23" s="528"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
@@ -29037,8 +29037,8 @@
       <c r="EI23" s="36"/>
     </row>
     <row r="24" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A24" s="494"/>
-      <c r="B24" s="495"/>
+      <c r="A24" s="486"/>
+      <c r="B24" s="487"/>
       <c r="C24" s="528"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
@@ -29192,8 +29192,8 @@
       <c r="EI24" s="36"/>
     </row>
     <row r="25" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="494"/>
-      <c r="B25" s="495"/>
+      <c r="A25" s="486"/>
+      <c r="B25" s="487"/>
       <c r="C25" s="529"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
@@ -29217,13 +29217,13 @@
       </c>
     </row>
     <row r="26" spans="1:139" ht="90" x14ac:dyDescent="0.2">
-      <c r="A26" s="499">
+      <c r="A26" s="491">
         <v>2.1</v>
       </c>
-      <c r="B26" s="502" t="s">
+      <c r="B26" s="494" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="505" t="s">
+      <c r="C26" s="497" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="76" t="s">
@@ -29246,9 +29246,9 @@
       <c r="K26" s="35"/>
     </row>
     <row r="27" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A27" s="500"/>
-      <c r="B27" s="503"/>
-      <c r="C27" s="506"/>
+      <c r="A27" s="492"/>
+      <c r="B27" s="495"/>
+      <c r="C27" s="498"/>
       <c r="D27" s="73" t="s">
         <v>55</v>
       </c>
@@ -29271,9 +29271,9 @@
       <c r="K27" s="35"/>
     </row>
     <row r="28" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A28" s="500"/>
-      <c r="B28" s="503"/>
-      <c r="C28" s="506"/>
+      <c r="A28" s="492"/>
+      <c r="B28" s="495"/>
+      <c r="C28" s="498"/>
       <c r="D28" s="61" t="s">
         <v>114</v>
       </c>
@@ -29296,9 +29296,9 @@
       <c r="K28" s="35"/>
     </row>
     <row r="29" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="500"/>
-      <c r="B29" s="503"/>
-      <c r="C29" s="506"/>
+      <c r="A29" s="492"/>
+      <c r="B29" s="495"/>
+      <c r="C29" s="498"/>
       <c r="D29" s="86" t="s">
         <v>92</v>
       </c>
@@ -29321,9 +29321,9 @@
       <c r="K29" s="35"/>
     </row>
     <row r="30" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="501"/>
-      <c r="B30" s="504"/>
-      <c r="C30" s="507"/>
+      <c r="A30" s="493"/>
+      <c r="B30" s="496"/>
+      <c r="C30" s="499"/>
       <c r="D30" s="76" t="s">
         <v>94</v>
       </c>
@@ -30536,12 +30536,6 @@
   </sheetData>
   <autoFilter ref="A4:EI31" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="15">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C5:C13"/>
     <mergeCell ref="A26:A30"/>
     <mergeCell ref="B26:B30"/>
     <mergeCell ref="C26:C30"/>
@@ -30551,6 +30545,12 @@
     <mergeCell ref="A20:A25"/>
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="C20:C25"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C5:C13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6:K7 K26" xr:uid="{F4C3080E-55C9-4ABE-B0CD-E6276EC6EDFB}"/>
@@ -30734,7 +30734,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:EC80"/>
+  <dimension ref="A1:EC81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.6640625" style="361" customWidth="1"/>
@@ -31186,7 +31186,7 @@
       <c r="EB3" s="369"/>
       <c r="EC3" s="369"/>
     </row>
-    <row r="4" spans="1:133" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:133" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="379" t="s">
         <v>153</v>
       </c>
@@ -31195,20 +31195,20 @@
       </c>
       <c r="C4" s="409"/>
       <c r="D4" s="397" t="s">
-        <v>156</v>
+        <v>68</v>
       </c>
       <c r="E4" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F4" s="370" t="s">
-        <v>157</v>
+      <c r="F4" s="399" t="s">
+        <v>108</v>
       </c>
       <c r="G4" s="369"/>
       <c r="H4" s="369"/>
       <c r="I4" s="369"/>
       <c r="J4" s="369"/>
-      <c r="K4" s="366" t="s">
-        <v>154</v>
+      <c r="K4" s="363" t="s">
+        <v>158</v>
       </c>
       <c r="P4" s="369"/>
       <c r="Q4" s="369"/>
@@ -31329,7 +31329,7 @@
       <c r="EB4" s="369"/>
       <c r="EC4" s="369"/>
     </row>
-    <row r="5" spans="1:133" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:133" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="379" t="s">
         <v>153</v>
       </c>
@@ -31338,14 +31338,13 @@
       </c>
       <c r="C5" s="409"/>
       <c r="D5" s="397" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F5" s="370" t="str">
-        <f>A5</f>
-        <v>A1</v>
+      <c r="F5" s="370" t="s">
+        <v>157</v>
       </c>
       <c r="G5" s="369"/>
       <c r="H5" s="369"/>
@@ -31473,7 +31472,7 @@
       <c r="EB5" s="369"/>
       <c r="EC5" s="369"/>
     </row>
-    <row r="6" spans="1:133" ht="32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:133" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="379" t="s">
         <v>153</v>
       </c>
@@ -31482,13 +31481,14 @@
       </c>
       <c r="C6" s="409"/>
       <c r="D6" s="397" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E6" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F6" s="370" t="s">
-        <v>161</v>
+      <c r="F6" s="370" t="str">
+        <f>A6</f>
+        <v>A1</v>
       </c>
       <c r="G6" s="369"/>
       <c r="H6" s="369"/>
@@ -31625,20 +31625,20 @@
       </c>
       <c r="C7" s="409"/>
       <c r="D7" s="397" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E7" s="384" t="s">
         <v>540</v>
       </c>
       <c r="F7" s="370" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G7" s="369"/>
       <c r="H7" s="369"/>
       <c r="I7" s="369"/>
       <c r="J7" s="369"/>
-      <c r="K7" s="363" t="s">
-        <v>163</v>
+      <c r="K7" s="366" t="s">
+        <v>154</v>
       </c>
       <c r="P7" s="369"/>
       <c r="Q7" s="369"/>
@@ -31768,7 +31768,7 @@
       </c>
       <c r="C8" s="409"/>
       <c r="D8" s="397" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E8" s="384" t="s">
         <v>540</v>
@@ -31911,7 +31911,7 @@
       </c>
       <c r="C9" s="409"/>
       <c r="D9" s="397" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E9" s="384" t="s">
         <v>540</v>
@@ -32045,7 +32045,7 @@
       <c r="EB9" s="369"/>
       <c r="EC9" s="369"/>
     </row>
-    <row r="10" spans="1:133" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:133" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="379" t="s">
         <v>153</v>
       </c>
@@ -32054,139 +32054,139 @@
       </c>
       <c r="C10" s="409"/>
       <c r="D10" s="397" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E10" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F10" s="400" t="s">
-        <v>153</v>
-      </c>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="366" t="s">
-        <v>154</v>
-      </c>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="41"/>
-      <c r="S10" s="41"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="41"/>
-      <c r="Y10" s="41"/>
-      <c r="Z10" s="41"/>
-      <c r="AA10" s="41"/>
-      <c r="AB10" s="41"/>
-      <c r="AC10" s="41"/>
-      <c r="AD10" s="41"/>
-      <c r="AE10" s="41"/>
-      <c r="AF10" s="41"/>
-      <c r="AG10" s="41"/>
-      <c r="AH10" s="41"/>
-      <c r="AI10" s="41"/>
-      <c r="AJ10" s="41"/>
-      <c r="AK10" s="41"/>
-      <c r="AL10" s="41"/>
-      <c r="AM10" s="41"/>
-      <c r="AN10" s="41"/>
-      <c r="AO10" s="41"/>
-      <c r="AP10" s="41"/>
-      <c r="AQ10" s="41"/>
-      <c r="AR10" s="41"/>
-      <c r="AS10" s="41"/>
-      <c r="AT10" s="41"/>
-      <c r="AU10" s="41"/>
-      <c r="AV10" s="41"/>
-      <c r="AW10" s="41"/>
-      <c r="AX10" s="41"/>
-      <c r="AY10" s="41"/>
-      <c r="AZ10" s="41"/>
-      <c r="BA10" s="41"/>
-      <c r="BB10" s="41"/>
-      <c r="BC10" s="41"/>
-      <c r="BD10" s="41"/>
-      <c r="BE10" s="41"/>
-      <c r="BF10" s="41"/>
-      <c r="BG10" s="41"/>
-      <c r="BH10" s="41"/>
-      <c r="BI10" s="41"/>
-      <c r="BJ10" s="41"/>
-      <c r="BK10" s="41"/>
-      <c r="BL10" s="41"/>
-      <c r="BM10" s="41"/>
-      <c r="BN10" s="41"/>
-      <c r="BO10" s="41"/>
-      <c r="BP10" s="41"/>
-      <c r="BQ10" s="41"/>
-      <c r="BR10" s="41"/>
-      <c r="BS10" s="41"/>
-      <c r="BT10" s="41"/>
-      <c r="BU10" s="41"/>
-      <c r="BV10" s="41"/>
-      <c r="BW10" s="41"/>
-      <c r="BX10" s="41"/>
-      <c r="BY10" s="41"/>
-      <c r="BZ10" s="41"/>
-      <c r="CA10" s="41"/>
-      <c r="CB10" s="41"/>
-      <c r="CC10" s="41"/>
-      <c r="CD10" s="41"/>
-      <c r="CE10" s="41"/>
-      <c r="CF10" s="41"/>
-      <c r="CG10" s="41"/>
-      <c r="CH10" s="41"/>
-      <c r="CI10" s="41"/>
-      <c r="CJ10" s="41"/>
-      <c r="CK10" s="41"/>
-      <c r="CL10" s="41"/>
-      <c r="CM10" s="41"/>
-      <c r="CN10" s="41"/>
-      <c r="CO10" s="41"/>
-      <c r="CP10" s="41"/>
-      <c r="CQ10" s="41"/>
-      <c r="CR10" s="41"/>
-      <c r="CS10" s="41"/>
-      <c r="CT10" s="41"/>
-      <c r="CU10" s="41"/>
-      <c r="CV10" s="41"/>
-      <c r="CW10" s="41"/>
-      <c r="CX10" s="41"/>
-      <c r="CY10" s="41"/>
-      <c r="CZ10" s="41"/>
-      <c r="DA10" s="41"/>
-      <c r="DB10" s="41"/>
-      <c r="DC10" s="41"/>
-      <c r="DD10" s="41"/>
-      <c r="DE10" s="41"/>
-      <c r="DF10" s="41"/>
-      <c r="DG10" s="41"/>
-      <c r="DH10" s="41"/>
-      <c r="DI10" s="41"/>
-      <c r="DJ10" s="41"/>
-      <c r="DK10" s="41"/>
-      <c r="DL10" s="41"/>
-      <c r="DM10" s="41"/>
-      <c r="DN10" s="41"/>
-      <c r="DO10" s="41"/>
-      <c r="DP10" s="41"/>
-      <c r="DQ10" s="41"/>
-      <c r="DR10" s="41"/>
-      <c r="DS10" s="41"/>
-      <c r="DT10" s="41"/>
-      <c r="DU10" s="41"/>
-      <c r="DV10" s="41"/>
-      <c r="DW10" s="41"/>
-      <c r="DX10" s="41"/>
-      <c r="DY10" s="41"/>
-      <c r="DZ10" s="41"/>
-      <c r="EA10" s="41"/>
-      <c r="EB10" s="41"/>
-      <c r="EC10" s="41"/>
+      <c r="F10" s="370" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="369"/>
+      <c r="H10" s="369"/>
+      <c r="I10" s="369"/>
+      <c r="J10" s="369"/>
+      <c r="K10" s="363" t="s">
+        <v>163</v>
+      </c>
+      <c r="P10" s="369"/>
+      <c r="Q10" s="369"/>
+      <c r="R10" s="369"/>
+      <c r="S10" s="369"/>
+      <c r="T10" s="369"/>
+      <c r="U10" s="369"/>
+      <c r="V10" s="369"/>
+      <c r="W10" s="369"/>
+      <c r="X10" s="369"/>
+      <c r="Y10" s="369"/>
+      <c r="Z10" s="369"/>
+      <c r="AA10" s="369"/>
+      <c r="AB10" s="369"/>
+      <c r="AC10" s="369"/>
+      <c r="AD10" s="369"/>
+      <c r="AE10" s="369"/>
+      <c r="AF10" s="369"/>
+      <c r="AG10" s="369"/>
+      <c r="AH10" s="369"/>
+      <c r="AI10" s="369"/>
+      <c r="AJ10" s="369"/>
+      <c r="AK10" s="369"/>
+      <c r="AL10" s="369"/>
+      <c r="AM10" s="369"/>
+      <c r="AN10" s="369"/>
+      <c r="AO10" s="369"/>
+      <c r="AP10" s="369"/>
+      <c r="AQ10" s="369"/>
+      <c r="AR10" s="369"/>
+      <c r="AS10" s="369"/>
+      <c r="AT10" s="369"/>
+      <c r="AU10" s="369"/>
+      <c r="AV10" s="369"/>
+      <c r="AW10" s="369"/>
+      <c r="AX10" s="369"/>
+      <c r="AY10" s="369"/>
+      <c r="AZ10" s="369"/>
+      <c r="BA10" s="369"/>
+      <c r="BB10" s="369"/>
+      <c r="BC10" s="369"/>
+      <c r="BD10" s="369"/>
+      <c r="BE10" s="369"/>
+      <c r="BF10" s="369"/>
+      <c r="BG10" s="369"/>
+      <c r="BH10" s="369"/>
+      <c r="BI10" s="369"/>
+      <c r="BJ10" s="369"/>
+      <c r="BK10" s="369"/>
+      <c r="BL10" s="369"/>
+      <c r="BM10" s="369"/>
+      <c r="BN10" s="369"/>
+      <c r="BO10" s="369"/>
+      <c r="BP10" s="369"/>
+      <c r="BQ10" s="369"/>
+      <c r="BR10" s="369"/>
+      <c r="BS10" s="369"/>
+      <c r="BT10" s="369"/>
+      <c r="BU10" s="369"/>
+      <c r="BV10" s="369"/>
+      <c r="BW10" s="369"/>
+      <c r="BX10" s="369"/>
+      <c r="BY10" s="369"/>
+      <c r="BZ10" s="369"/>
+      <c r="CA10" s="369"/>
+      <c r="CB10" s="369"/>
+      <c r="CC10" s="369"/>
+      <c r="CD10" s="369"/>
+      <c r="CE10" s="369"/>
+      <c r="CF10" s="369"/>
+      <c r="CG10" s="369"/>
+      <c r="CH10" s="369"/>
+      <c r="CI10" s="369"/>
+      <c r="CJ10" s="369"/>
+      <c r="CK10" s="369"/>
+      <c r="CL10" s="369"/>
+      <c r="CM10" s="369"/>
+      <c r="CN10" s="369"/>
+      <c r="CO10" s="369"/>
+      <c r="CP10" s="369"/>
+      <c r="CQ10" s="369"/>
+      <c r="CR10" s="369"/>
+      <c r="CS10" s="369"/>
+      <c r="CT10" s="369"/>
+      <c r="CU10" s="369"/>
+      <c r="CV10" s="369"/>
+      <c r="CW10" s="369"/>
+      <c r="CX10" s="369"/>
+      <c r="CY10" s="369"/>
+      <c r="CZ10" s="369"/>
+      <c r="DA10" s="369"/>
+      <c r="DB10" s="369"/>
+      <c r="DC10" s="369"/>
+      <c r="DD10" s="369"/>
+      <c r="DE10" s="369"/>
+      <c r="DF10" s="369"/>
+      <c r="DG10" s="369"/>
+      <c r="DH10" s="369"/>
+      <c r="DI10" s="369"/>
+      <c r="DJ10" s="369"/>
+      <c r="DK10" s="369"/>
+      <c r="DL10" s="369"/>
+      <c r="DM10" s="369"/>
+      <c r="DN10" s="369"/>
+      <c r="DO10" s="369"/>
+      <c r="DP10" s="369"/>
+      <c r="DQ10" s="369"/>
+      <c r="DR10" s="369"/>
+      <c r="DS10" s="369"/>
+      <c r="DT10" s="369"/>
+      <c r="DU10" s="369"/>
+      <c r="DV10" s="369"/>
+      <c r="DW10" s="369"/>
+      <c r="DX10" s="369"/>
+      <c r="DY10" s="369"/>
+      <c r="DZ10" s="369"/>
+      <c r="EA10" s="369"/>
+      <c r="EB10" s="369"/>
+      <c r="EC10" s="369"/>
     </row>
     <row r="11" spans="1:133" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="379" t="s">
@@ -32197,7 +32197,7 @@
       </c>
       <c r="C11" s="409"/>
       <c r="D11" s="397" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E11" s="384" t="s">
         <v>540</v>
@@ -32331,22 +32331,22 @@
       <c r="EB11" s="41"/>
       <c r="EC11" s="41"/>
     </row>
-    <row r="12" spans="1:133" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="403" t="s">
+    <row r="12" spans="1:133" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="379" t="s">
         <v>153</v>
       </c>
-      <c r="B12" s="404" t="s">
+      <c r="B12" s="381" t="s">
         <v>155</v>
       </c>
-      <c r="C12" s="408"/>
+      <c r="C12" s="409"/>
       <c r="D12" s="397" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E12" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F12" s="370" t="s">
-        <v>157</v>
+      <c r="F12" s="400" t="s">
+        <v>153</v>
       </c>
       <c r="G12" s="41"/>
       <c r="H12" s="41"/>
@@ -32475,28 +32475,28 @@
       <c r="EC12" s="41"/>
     </row>
     <row r="13" spans="1:133" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="401" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="402" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="410"/>
+      <c r="A13" s="403" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="404" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="408"/>
       <c r="D13" s="397" t="s">
-        <v>52</v>
+        <v>168</v>
       </c>
       <c r="E13" s="384" t="s">
         <v>540</v>
       </c>
       <c r="F13" s="370" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="G13" s="41"/>
       <c r="H13" s="41"/>
       <c r="I13" s="41"/>
       <c r="J13" s="41"/>
-      <c r="K13" s="365" t="s">
-        <v>55</v>
+      <c r="K13" s="366" t="s">
+        <v>154</v>
       </c>
       <c r="P13" s="41"/>
       <c r="Q13" s="41"/>
@@ -32626,21 +32626,20 @@
       </c>
       <c r="C14" s="410"/>
       <c r="D14" s="397" t="s">
-        <v>159</v>
+        <v>52</v>
       </c>
       <c r="E14" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F14" s="370" t="str">
-        <f>A14</f>
-        <v>A2</v>
+      <c r="F14" s="370" t="s">
+        <v>175</v>
       </c>
       <c r="G14" s="41"/>
       <c r="H14" s="41"/>
       <c r="I14" s="41"/>
       <c r="J14" s="41"/>
-      <c r="K14" s="366" t="s">
-        <v>154</v>
+      <c r="K14" s="365" t="s">
+        <v>55</v>
       </c>
       <c r="P14" s="41"/>
       <c r="Q14" s="41"/>
@@ -32770,13 +32769,14 @@
       </c>
       <c r="C15" s="410"/>
       <c r="D15" s="397" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E15" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F15" s="370" t="s">
-        <v>161</v>
+      <c r="F15" s="370" t="str">
+        <f>A15</f>
+        <v>A2</v>
       </c>
       <c r="G15" s="41"/>
       <c r="H15" s="41"/>
@@ -32911,23 +32911,22 @@
       <c r="B16" s="402" t="s">
         <v>169</v>
       </c>
-      <c r="C16" s="411"/>
-      <c r="D16" s="398" t="s">
-        <v>170</v>
+      <c r="C16" s="410"/>
+      <c r="D16" s="397" t="s">
+        <v>160</v>
       </c>
       <c r="E16" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F16" s="400" t="str">
-        <f>A16</f>
-        <v>A2</v>
+      <c r="F16" s="370" t="s">
+        <v>161</v>
       </c>
       <c r="G16" s="41"/>
       <c r="H16" s="41"/>
       <c r="I16" s="41"/>
       <c r="J16" s="41"/>
-      <c r="K16" s="364" t="s">
-        <v>171</v>
+      <c r="K16" s="366" t="s">
+        <v>154</v>
       </c>
       <c r="P16" s="41"/>
       <c r="Q16" s="41"/>
@@ -33049,15 +33048,15 @@
       <c r="EC16" s="41"/>
     </row>
     <row r="17" spans="1:133" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="405" t="s">
+      <c r="A17" s="401" t="s">
         <v>108</v>
       </c>
-      <c r="B17" s="406" t="s">
+      <c r="B17" s="402" t="s">
         <v>169</v>
       </c>
-      <c r="C17" s="412"/>
+      <c r="C17" s="411"/>
       <c r="D17" s="398" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E17" s="384" t="s">
         <v>540</v>
@@ -33070,8 +33069,8 @@
       <c r="H17" s="41"/>
       <c r="I17" s="41"/>
       <c r="J17" s="41"/>
-      <c r="K17" s="365" t="s">
-        <v>55</v>
+      <c r="K17" s="364" t="s">
+        <v>171</v>
       </c>
       <c r="P17" s="41"/>
       <c r="Q17" s="41"/>
@@ -33192,29 +33191,30 @@
       <c r="EB17" s="41"/>
       <c r="EC17" s="41"/>
     </row>
-    <row r="18" spans="1:133" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="401" t="s">
-        <v>175</v>
-      </c>
-      <c r="B18" s="402" t="s">
-        <v>173</v>
-      </c>
-      <c r="C18" s="402"/>
-      <c r="D18" s="407" t="s">
-        <v>174</v>
+    <row r="18" spans="1:133" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="405" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="406" t="s">
+        <v>169</v>
+      </c>
+      <c r="C18" s="412"/>
+      <c r="D18" s="398" t="s">
+        <v>172</v>
       </c>
       <c r="E18" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F18" s="370" t="s">
-        <v>537</v>
+      <c r="F18" s="400" t="str">
+        <f>A18</f>
+        <v>A2</v>
       </c>
       <c r="G18" s="41"/>
       <c r="H18" s="41"/>
       <c r="I18" s="41"/>
       <c r="J18" s="41"/>
-      <c r="K18" s="366" t="s">
-        <v>154</v>
+      <c r="K18" s="365" t="s">
+        <v>55</v>
       </c>
       <c r="P18" s="41"/>
       <c r="Q18" s="41"/>
@@ -33335,29 +33335,29 @@
       <c r="EB18" s="41"/>
       <c r="EC18" s="41"/>
     </row>
-    <row r="19" spans="1:133" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:133" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="401" t="s">
         <v>175</v>
       </c>
       <c r="B19" s="402" t="s">
         <v>173</v>
       </c>
-      <c r="C19" s="410"/>
-      <c r="D19" s="397" t="s">
-        <v>68</v>
+      <c r="C19" s="402"/>
+      <c r="D19" s="407" t="s">
+        <v>174</v>
       </c>
       <c r="E19" s="384" t="s">
         <v>540</v>
       </c>
       <c r="F19" s="370" t="s">
-        <v>157</v>
+        <v>537</v>
       </c>
       <c r="G19" s="41"/>
       <c r="H19" s="41"/>
       <c r="I19" s="41"/>
       <c r="J19" s="41"/>
-      <c r="K19" s="363" t="s">
-        <v>158</v>
+      <c r="K19" s="366" t="s">
+        <v>154</v>
       </c>
       <c r="P19" s="41"/>
       <c r="Q19" s="41"/>
@@ -33485,23 +33485,22 @@
       <c r="B20" s="402" t="s">
         <v>173</v>
       </c>
-      <c r="C20" s="411"/>
-      <c r="D20" s="398" t="s">
-        <v>170</v>
+      <c r="C20" s="410"/>
+      <c r="D20" s="397" t="s">
+        <v>68</v>
       </c>
       <c r="E20" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F20" s="400" t="str">
-        <f>A20</f>
-        <v>A3</v>
+      <c r="F20" s="370" t="s">
+        <v>157</v>
       </c>
       <c r="G20" s="41"/>
       <c r="H20" s="41"/>
       <c r="I20" s="41"/>
       <c r="J20" s="41"/>
-      <c r="K20" s="364" t="s">
-        <v>171</v>
+      <c r="K20" s="363" t="s">
+        <v>158</v>
       </c>
       <c r="P20" s="41"/>
       <c r="Q20" s="41"/>
@@ -33631,7 +33630,7 @@
       </c>
       <c r="C21" s="411"/>
       <c r="D21" s="398" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E21" s="384" t="s">
         <v>540</v>
@@ -33775,13 +33774,14 @@
       </c>
       <c r="C22" s="411"/>
       <c r="D22" s="398" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E22" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F22" s="370" t="s">
-        <v>161</v>
+      <c r="F22" s="400" t="str">
+        <f>A22</f>
+        <v>A3</v>
       </c>
       <c r="G22" s="41"/>
       <c r="H22" s="41"/>
@@ -33918,21 +33918,20 @@
       </c>
       <c r="C23" s="411"/>
       <c r="D23" s="398" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E23" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F23" s="400" t="str">
-        <f>A23</f>
-        <v>A3</v>
+      <c r="F23" s="370" t="s">
+        <v>161</v>
       </c>
       <c r="G23" s="41"/>
       <c r="H23" s="41"/>
       <c r="I23" s="41"/>
       <c r="J23" s="41"/>
-      <c r="K23" s="365" t="s">
-        <v>536</v>
+      <c r="K23" s="364" t="s">
+        <v>171</v>
       </c>
       <c r="P23" s="41"/>
       <c r="Q23" s="41"/>
@@ -34060,22 +34059,23 @@
       <c r="B24" s="402" t="s">
         <v>173</v>
       </c>
-      <c r="C24" s="410"/>
-      <c r="D24" s="397" t="s">
-        <v>68</v>
+      <c r="C24" s="411"/>
+      <c r="D24" s="398" t="s">
+        <v>172</v>
       </c>
       <c r="E24" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F24" s="370" t="s">
-        <v>161</v>
+      <c r="F24" s="400" t="str">
+        <f>A24</f>
+        <v>A3</v>
       </c>
       <c r="G24" s="41"/>
       <c r="H24" s="41"/>
       <c r="I24" s="41"/>
       <c r="J24" s="41"/>
       <c r="K24" s="365" t="s">
-        <v>459</v>
+        <v>536</v>
       </c>
       <c r="P24" s="41"/>
       <c r="Q24" s="41"/>
@@ -34196,148 +34196,148 @@
       <c r="EB24" s="41"/>
       <c r="EC24" s="41"/>
     </row>
-    <row r="25" spans="1:133" s="42" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="371" t="s">
-        <v>537</v>
-      </c>
-      <c r="B25" s="382" t="s">
-        <v>178</v>
-      </c>
-      <c r="C25" s="413"/>
+    <row r="25" spans="1:133" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="401" t="s">
+        <v>175</v>
+      </c>
+      <c r="B25" s="402" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="410"/>
       <c r="D25" s="397" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="E25" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F25" s="399" t="s">
-        <v>538</v>
-      </c>
-      <c r="G25" s="369"/>
-      <c r="H25" s="369"/>
-      <c r="I25" s="369"/>
-      <c r="J25" s="369"/>
-      <c r="K25" s="366" t="s">
-        <v>154</v>
-      </c>
-      <c r="P25" s="369"/>
-      <c r="Q25" s="369"/>
-      <c r="R25" s="369"/>
-      <c r="S25" s="369"/>
-      <c r="T25" s="369"/>
-      <c r="U25" s="369"/>
-      <c r="V25" s="369"/>
-      <c r="W25" s="369"/>
-      <c r="X25" s="369"/>
-      <c r="Y25" s="369"/>
-      <c r="Z25" s="369"/>
-      <c r="AA25" s="369"/>
-      <c r="AB25" s="369"/>
-      <c r="AC25" s="369"/>
-      <c r="AD25" s="369"/>
-      <c r="AE25" s="369"/>
-      <c r="AF25" s="369"/>
-      <c r="AG25" s="369"/>
-      <c r="AH25" s="369"/>
-      <c r="AI25" s="369"/>
-      <c r="AJ25" s="369"/>
-      <c r="AK25" s="369"/>
-      <c r="AL25" s="369"/>
-      <c r="AM25" s="369"/>
-      <c r="AN25" s="369"/>
-      <c r="AO25" s="369"/>
-      <c r="AP25" s="369"/>
-      <c r="AQ25" s="369"/>
-      <c r="AR25" s="369"/>
-      <c r="AS25" s="369"/>
-      <c r="AT25" s="369"/>
-      <c r="AU25" s="369"/>
-      <c r="AV25" s="369"/>
-      <c r="AW25" s="369"/>
-      <c r="AX25" s="369"/>
-      <c r="AY25" s="369"/>
-      <c r="AZ25" s="369"/>
-      <c r="BA25" s="369"/>
-      <c r="BB25" s="369"/>
-      <c r="BC25" s="369"/>
-      <c r="BD25" s="369"/>
-      <c r="BE25" s="369"/>
-      <c r="BF25" s="369"/>
-      <c r="BG25" s="369"/>
-      <c r="BH25" s="369"/>
-      <c r="BI25" s="369"/>
-      <c r="BJ25" s="369"/>
-      <c r="BK25" s="369"/>
-      <c r="BL25" s="369"/>
-      <c r="BM25" s="369"/>
-      <c r="BN25" s="369"/>
-      <c r="BO25" s="369"/>
-      <c r="BP25" s="369"/>
-      <c r="BQ25" s="369"/>
-      <c r="BR25" s="369"/>
-      <c r="BS25" s="369"/>
-      <c r="BT25" s="369"/>
-      <c r="BU25" s="369"/>
-      <c r="BV25" s="369"/>
-      <c r="BW25" s="369"/>
-      <c r="BX25" s="369"/>
-      <c r="BY25" s="369"/>
-      <c r="BZ25" s="369"/>
-      <c r="CA25" s="369"/>
-      <c r="CB25" s="369"/>
-      <c r="CC25" s="369"/>
-      <c r="CD25" s="369"/>
-      <c r="CE25" s="369"/>
-      <c r="CF25" s="369"/>
-      <c r="CG25" s="369"/>
-      <c r="CH25" s="369"/>
-      <c r="CI25" s="369"/>
-      <c r="CJ25" s="369"/>
-      <c r="CK25" s="369"/>
-      <c r="CL25" s="369"/>
-      <c r="CM25" s="369"/>
-      <c r="CN25" s="369"/>
-      <c r="CO25" s="369"/>
-      <c r="CP25" s="369"/>
-      <c r="CQ25" s="369"/>
-      <c r="CR25" s="369"/>
-      <c r="CS25" s="369"/>
-      <c r="CT25" s="369"/>
-      <c r="CU25" s="369"/>
-      <c r="CV25" s="369"/>
-      <c r="CW25" s="369"/>
-      <c r="CX25" s="369"/>
-      <c r="CY25" s="369"/>
-      <c r="CZ25" s="369"/>
-      <c r="DA25" s="369"/>
-      <c r="DB25" s="369"/>
-      <c r="DC25" s="369"/>
-      <c r="DD25" s="369"/>
-      <c r="DE25" s="369"/>
-      <c r="DF25" s="369"/>
-      <c r="DG25" s="369"/>
-      <c r="DH25" s="369"/>
-      <c r="DI25" s="369"/>
-      <c r="DJ25" s="369"/>
-      <c r="DK25" s="369"/>
-      <c r="DL25" s="369"/>
-      <c r="DM25" s="369"/>
-      <c r="DN25" s="369"/>
-      <c r="DO25" s="369"/>
-      <c r="DP25" s="369"/>
-      <c r="DQ25" s="369"/>
-      <c r="DR25" s="369"/>
-      <c r="DS25" s="369"/>
-      <c r="DT25" s="369"/>
-      <c r="DU25" s="369"/>
-      <c r="DV25" s="369"/>
-      <c r="DW25" s="369"/>
-      <c r="DX25" s="369"/>
-      <c r="DY25" s="369"/>
-      <c r="DZ25" s="369"/>
-      <c r="EA25" s="369"/>
-      <c r="EB25" s="369"/>
-      <c r="EC25" s="369"/>
+      <c r="F25" s="370" t="s">
+        <v>161</v>
+      </c>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="365" t="s">
+        <v>459</v>
+      </c>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="41"/>
+      <c r="R25" s="41"/>
+      <c r="S25" s="41"/>
+      <c r="T25" s="41"/>
+      <c r="U25" s="41"/>
+      <c r="V25" s="41"/>
+      <c r="W25" s="41"/>
+      <c r="X25" s="41"/>
+      <c r="Y25" s="41"/>
+      <c r="Z25" s="41"/>
+      <c r="AA25" s="41"/>
+      <c r="AB25" s="41"/>
+      <c r="AC25" s="41"/>
+      <c r="AD25" s="41"/>
+      <c r="AE25" s="41"/>
+      <c r="AF25" s="41"/>
+      <c r="AG25" s="41"/>
+      <c r="AH25" s="41"/>
+      <c r="AI25" s="41"/>
+      <c r="AJ25" s="41"/>
+      <c r="AK25" s="41"/>
+      <c r="AL25" s="41"/>
+      <c r="AM25" s="41"/>
+      <c r="AN25" s="41"/>
+      <c r="AO25" s="41"/>
+      <c r="AP25" s="41"/>
+      <c r="AQ25" s="41"/>
+      <c r="AR25" s="41"/>
+      <c r="AS25" s="41"/>
+      <c r="AT25" s="41"/>
+      <c r="AU25" s="41"/>
+      <c r="AV25" s="41"/>
+      <c r="AW25" s="41"/>
+      <c r="AX25" s="41"/>
+      <c r="AY25" s="41"/>
+      <c r="AZ25" s="41"/>
+      <c r="BA25" s="41"/>
+      <c r="BB25" s="41"/>
+      <c r="BC25" s="41"/>
+      <c r="BD25" s="41"/>
+      <c r="BE25" s="41"/>
+      <c r="BF25" s="41"/>
+      <c r="BG25" s="41"/>
+      <c r="BH25" s="41"/>
+      <c r="BI25" s="41"/>
+      <c r="BJ25" s="41"/>
+      <c r="BK25" s="41"/>
+      <c r="BL25" s="41"/>
+      <c r="BM25" s="41"/>
+      <c r="BN25" s="41"/>
+      <c r="BO25" s="41"/>
+      <c r="BP25" s="41"/>
+      <c r="BQ25" s="41"/>
+      <c r="BR25" s="41"/>
+      <c r="BS25" s="41"/>
+      <c r="BT25" s="41"/>
+      <c r="BU25" s="41"/>
+      <c r="BV25" s="41"/>
+      <c r="BW25" s="41"/>
+      <c r="BX25" s="41"/>
+      <c r="BY25" s="41"/>
+      <c r="BZ25" s="41"/>
+      <c r="CA25" s="41"/>
+      <c r="CB25" s="41"/>
+      <c r="CC25" s="41"/>
+      <c r="CD25" s="41"/>
+      <c r="CE25" s="41"/>
+      <c r="CF25" s="41"/>
+      <c r="CG25" s="41"/>
+      <c r="CH25" s="41"/>
+      <c r="CI25" s="41"/>
+      <c r="CJ25" s="41"/>
+      <c r="CK25" s="41"/>
+      <c r="CL25" s="41"/>
+      <c r="CM25" s="41"/>
+      <c r="CN25" s="41"/>
+      <c r="CO25" s="41"/>
+      <c r="CP25" s="41"/>
+      <c r="CQ25" s="41"/>
+      <c r="CR25" s="41"/>
+      <c r="CS25" s="41"/>
+      <c r="CT25" s="41"/>
+      <c r="CU25" s="41"/>
+      <c r="CV25" s="41"/>
+      <c r="CW25" s="41"/>
+      <c r="CX25" s="41"/>
+      <c r="CY25" s="41"/>
+      <c r="CZ25" s="41"/>
+      <c r="DA25" s="41"/>
+      <c r="DB25" s="41"/>
+      <c r="DC25" s="41"/>
+      <c r="DD25" s="41"/>
+      <c r="DE25" s="41"/>
+      <c r="DF25" s="41"/>
+      <c r="DG25" s="41"/>
+      <c r="DH25" s="41"/>
+      <c r="DI25" s="41"/>
+      <c r="DJ25" s="41"/>
+      <c r="DK25" s="41"/>
+      <c r="DL25" s="41"/>
+      <c r="DM25" s="41"/>
+      <c r="DN25" s="41"/>
+      <c r="DO25" s="41"/>
+      <c r="DP25" s="41"/>
+      <c r="DQ25" s="41"/>
+      <c r="DR25" s="41"/>
+      <c r="DS25" s="41"/>
+      <c r="DT25" s="41"/>
+      <c r="DU25" s="41"/>
+      <c r="DV25" s="41"/>
+      <c r="DW25" s="41"/>
+      <c r="DX25" s="41"/>
+      <c r="DY25" s="41"/>
+      <c r="DZ25" s="41"/>
+      <c r="EA25" s="41"/>
+      <c r="EB25" s="41"/>
+      <c r="EC25" s="41"/>
     </row>
     <row r="26" spans="1:133" s="42" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="371" t="s">
@@ -34346,23 +34346,22 @@
       <c r="B26" s="382" t="s">
         <v>178</v>
       </c>
-      <c r="C26" s="414"/>
-      <c r="D26" s="398" t="s">
-        <v>170</v>
+      <c r="C26" s="413"/>
+      <c r="D26" s="397" t="s">
+        <v>52</v>
       </c>
       <c r="E26" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F26" s="400" t="str">
-        <f>A26</f>
-        <v>A4</v>
+      <c r="F26" s="399" t="s">
+        <v>538</v>
       </c>
       <c r="G26" s="369"/>
       <c r="H26" s="369"/>
       <c r="I26" s="369"/>
       <c r="J26" s="369"/>
-      <c r="K26" s="364" t="s">
-        <v>171</v>
+      <c r="K26" s="366" t="s">
+        <v>154</v>
       </c>
       <c r="P26" s="369"/>
       <c r="Q26" s="369"/>
@@ -34483,7 +34482,7 @@
       <c r="EB26" s="369"/>
       <c r="EC26" s="369"/>
     </row>
-    <row r="27" spans="1:133" ht="86.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:133" s="42" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="371" t="s">
         <v>537</v>
       </c>
@@ -34492,7 +34491,7 @@
       </c>
       <c r="C27" s="414"/>
       <c r="D27" s="398" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E27" s="384" t="s">
         <v>540</v>
@@ -34627,7 +34626,7 @@
       <c r="EB27" s="369"/>
       <c r="EC27" s="369"/>
     </row>
-    <row r="28" spans="1:133" ht="60" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:133" ht="86.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="371" t="s">
         <v>537</v>
       </c>
@@ -34636,13 +34635,14 @@
       </c>
       <c r="C28" s="414"/>
       <c r="D28" s="398" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E28" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F28" s="370" t="s">
-        <v>161</v>
+      <c r="F28" s="400" t="str">
+        <f>A28</f>
+        <v>A4</v>
       </c>
       <c r="G28" s="369"/>
       <c r="H28" s="369"/>
@@ -34779,21 +34779,20 @@
       </c>
       <c r="C29" s="414"/>
       <c r="D29" s="398" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E29" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F29" s="400" t="str">
-        <f>A29</f>
-        <v>A4</v>
+      <c r="F29" s="370" t="s">
+        <v>161</v>
       </c>
       <c r="G29" s="369"/>
       <c r="H29" s="369"/>
       <c r="I29" s="369"/>
       <c r="J29" s="369"/>
-      <c r="K29" s="365" t="s">
-        <v>55</v>
+      <c r="K29" s="364" t="s">
+        <v>171</v>
       </c>
       <c r="P29" s="369"/>
       <c r="Q29" s="369"/>
@@ -34923,7 +34922,7 @@
       </c>
       <c r="C30" s="414"/>
       <c r="D30" s="398" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="E30" s="384" t="s">
         <v>540</v>
@@ -35058,30 +35057,30 @@
       <c r="EB30" s="369"/>
       <c r="EC30" s="369"/>
     </row>
-    <row r="31" spans="1:133" ht="48" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:133" ht="60" x14ac:dyDescent="0.2">
       <c r="A31" s="371" t="s">
-        <v>538</v>
-      </c>
-      <c r="B31" s="383" t="s">
-        <v>180</v>
-      </c>
-      <c r="C31" s="415"/>
-      <c r="D31" s="370" t="s">
-        <v>181</v>
+        <v>537</v>
+      </c>
+      <c r="B31" s="382" t="s">
+        <v>178</v>
+      </c>
+      <c r="C31" s="414"/>
+      <c r="D31" s="398" t="s">
+        <v>179</v>
       </c>
       <c r="E31" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F31" s="261" t="str">
+      <c r="F31" s="400" t="str">
         <f>A31</f>
-        <v>A5</v>
+        <v>A4</v>
       </c>
       <c r="G31" s="369"/>
       <c r="H31" s="369"/>
       <c r="I31" s="369"/>
       <c r="J31" s="369"/>
       <c r="K31" s="365" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="P31" s="369"/>
       <c r="Q31" s="369"/>
@@ -35211,13 +35210,14 @@
       </c>
       <c r="C32" s="415"/>
       <c r="D32" s="370" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E32" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F32" s="261" t="s">
-        <v>157</v>
+      <c r="F32" s="261" t="str">
+        <f>A32</f>
+        <v>A5</v>
       </c>
       <c r="G32" s="369"/>
       <c r="H32" s="369"/>
@@ -35354,7 +35354,7 @@
       </c>
       <c r="C33" s="415"/>
       <c r="D33" s="370" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="E33" s="384" t="s">
         <v>540</v>
@@ -35367,7 +35367,7 @@
       <c r="I33" s="369"/>
       <c r="J33" s="369"/>
       <c r="K33" s="365" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="P33" s="369"/>
       <c r="Q33" s="369"/>
@@ -35497,21 +35497,20 @@
       </c>
       <c r="C34" s="415"/>
       <c r="D34" s="370" t="s">
-        <v>183</v>
+        <v>122</v>
       </c>
       <c r="E34" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F34" s="261" t="str">
-        <f>A34</f>
-        <v>A5</v>
+      <c r="F34" s="261" t="s">
+        <v>157</v>
       </c>
       <c r="G34" s="369"/>
       <c r="H34" s="369"/>
       <c r="I34" s="369"/>
       <c r="J34" s="369"/>
-      <c r="K34" s="363" t="s">
-        <v>158</v>
+      <c r="K34" s="365" t="s">
+        <v>125</v>
       </c>
       <c r="P34" s="369"/>
       <c r="Q34" s="369"/>
@@ -35641,13 +35640,14 @@
       </c>
       <c r="C35" s="415"/>
       <c r="D35" s="370" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E35" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F35" s="261" t="s">
-        <v>157</v>
+      <c r="F35" s="261" t="str">
+        <f>A35</f>
+        <v>A5</v>
       </c>
       <c r="G35" s="369"/>
       <c r="H35" s="369"/>
@@ -35782,23 +35782,22 @@
       <c r="B36" s="383" t="s">
         <v>180</v>
       </c>
-      <c r="C36" s="416"/>
-      <c r="D36" s="372" t="s">
-        <v>185</v>
+      <c r="C36" s="415"/>
+      <c r="D36" s="370" t="s">
+        <v>184</v>
       </c>
       <c r="E36" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F36" s="376" t="str">
-        <f>A36</f>
-        <v>A5</v>
-      </c>
-      <c r="G36" s="378"/>
+      <c r="F36" s="261" t="s">
+        <v>157</v>
+      </c>
+      <c r="G36" s="369"/>
       <c r="H36" s="369"/>
       <c r="I36" s="369"/>
       <c r="J36" s="369"/>
-      <c r="K36" s="377" t="s">
-        <v>133</v>
+      <c r="K36" s="363" t="s">
+        <v>158</v>
       </c>
       <c r="P36" s="369"/>
       <c r="Q36" s="369"/>
@@ -35926,23 +35925,23 @@
       <c r="B37" s="383" t="s">
         <v>180</v>
       </c>
-      <c r="C37" s="417"/>
-      <c r="D37" s="380" t="s">
-        <v>170</v>
+      <c r="C37" s="416"/>
+      <c r="D37" s="372" t="s">
+        <v>185</v>
       </c>
       <c r="E37" s="384" t="s">
         <v>540</v>
       </c>
       <c r="F37" s="376" t="str">
-        <f t="shared" ref="F37:F38" si="0">A37</f>
+        <f>A37</f>
         <v>A5</v>
       </c>
-      <c r="G37" s="369"/>
+      <c r="G37" s="378"/>
       <c r="H37" s="369"/>
       <c r="I37" s="369"/>
       <c r="J37" s="369"/>
-      <c r="K37" s="364" t="s">
-        <v>171</v>
+      <c r="K37" s="377" t="s">
+        <v>133</v>
       </c>
       <c r="P37" s="369"/>
       <c r="Q37" s="369"/>
@@ -36072,13 +36071,13 @@
       </c>
       <c r="C38" s="417"/>
       <c r="D38" s="380" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E38" s="384" t="s">
         <v>540</v>
       </c>
       <c r="F38" s="376" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F38:F39" si="0">A38</f>
         <v>A5</v>
       </c>
       <c r="G38" s="369"/>
@@ -36216,13 +36215,14 @@
       </c>
       <c r="C39" s="417"/>
       <c r="D39" s="380" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E39" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F39" s="261" t="s">
-        <v>161</v>
+      <c r="F39" s="376" t="str">
+        <f t="shared" si="0"/>
+        <v>A5</v>
       </c>
       <c r="G39" s="369"/>
       <c r="H39" s="369"/>
@@ -36359,21 +36359,20 @@
       </c>
       <c r="C40" s="417"/>
       <c r="D40" s="380" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E40" s="384" t="s">
         <v>540</v>
       </c>
-      <c r="F40" s="360" t="str">
-        <f>A40</f>
-        <v>A5</v>
+      <c r="F40" s="261" t="s">
+        <v>161</v>
       </c>
       <c r="G40" s="369"/>
       <c r="H40" s="369"/>
       <c r="I40" s="369"/>
       <c r="J40" s="369"/>
-      <c r="K40" s="365" t="s">
-        <v>55</v>
+      <c r="K40" s="364" t="s">
+        <v>171</v>
       </c>
       <c r="P40" s="369"/>
       <c r="Q40" s="369"/>
@@ -36503,7 +36502,7 @@
       </c>
       <c r="C41" s="417"/>
       <c r="D41" s="380" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="E41" s="384" t="s">
         <v>540</v>
@@ -36638,18 +36637,31 @@
       <c r="EB41" s="369"/>
       <c r="EC41" s="369"/>
     </row>
-    <row r="42" spans="1:133" x14ac:dyDescent="0.2">
-      <c r="A42" s="367"/>
-      <c r="B42" s="373"/>
-      <c r="C42" s="373"/>
-      <c r="D42" s="261"/>
-      <c r="E42" s="261"/>
-      <c r="F42" s="261"/>
+    <row r="42" spans="1:133" ht="48" x14ac:dyDescent="0.2">
+      <c r="A42" s="371" t="s">
+        <v>538</v>
+      </c>
+      <c r="B42" s="383" t="s">
+        <v>180</v>
+      </c>
+      <c r="C42" s="417"/>
+      <c r="D42" s="380" t="s">
+        <v>179</v>
+      </c>
+      <c r="E42" s="384" t="s">
+        <v>540</v>
+      </c>
+      <c r="F42" s="360" t="str">
+        <f>A42</f>
+        <v>A5</v>
+      </c>
       <c r="G42" s="369"/>
       <c r="H42" s="369"/>
       <c r="I42" s="369"/>
       <c r="J42" s="369"/>
-      <c r="K42" s="71"/>
+      <c r="K42" s="365" t="s">
+        <v>55</v>
+      </c>
       <c r="P42" s="369"/>
       <c r="Q42" s="369"/>
       <c r="R42" s="369"/>
@@ -37293,7 +37305,7 @@
       <c r="EB46" s="369"/>
       <c r="EC46" s="369"/>
     </row>
-    <row r="47" spans="1:133" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:133" x14ac:dyDescent="0.2">
       <c r="A47" s="367"/>
       <c r="B47" s="373"/>
       <c r="C47" s="373"/>
@@ -37424,7 +37436,7 @@
       <c r="EB47" s="369"/>
       <c r="EC47" s="369"/>
     </row>
-    <row r="48" spans="1:133" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:133" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="367"/>
       <c r="B48" s="373"/>
       <c r="C48" s="373"/>
@@ -37686,7 +37698,7 @@
       <c r="EB49" s="369"/>
       <c r="EC49" s="369"/>
     </row>
-    <row r="50" spans="1:133" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:133" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="367"/>
       <c r="B50" s="373"/>
       <c r="C50" s="373"/>
@@ -37948,7 +37960,7 @@
       <c r="EB51" s="369"/>
       <c r="EC51" s="369"/>
     </row>
-    <row r="52" spans="1:133" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:133" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="367"/>
       <c r="B52" s="373"/>
       <c r="C52" s="373"/>
@@ -41747,8 +41759,139 @@
       <c r="EB80" s="369"/>
       <c r="EC80" s="369"/>
     </row>
+    <row r="81" spans="1:133" x14ac:dyDescent="0.2">
+      <c r="A81" s="367"/>
+      <c r="B81" s="373"/>
+      <c r="C81" s="373"/>
+      <c r="D81" s="261"/>
+      <c r="E81" s="261"/>
+      <c r="F81" s="261"/>
+      <c r="G81" s="369"/>
+      <c r="H81" s="369"/>
+      <c r="I81" s="369"/>
+      <c r="J81" s="369"/>
+      <c r="K81" s="71"/>
+      <c r="P81" s="369"/>
+      <c r="Q81" s="369"/>
+      <c r="R81" s="369"/>
+      <c r="S81" s="369"/>
+      <c r="T81" s="369"/>
+      <c r="U81" s="369"/>
+      <c r="V81" s="369"/>
+      <c r="W81" s="369"/>
+      <c r="X81" s="369"/>
+      <c r="Y81" s="369"/>
+      <c r="Z81" s="369"/>
+      <c r="AA81" s="369"/>
+      <c r="AB81" s="369"/>
+      <c r="AC81" s="369"/>
+      <c r="AD81" s="369"/>
+      <c r="AE81" s="369"/>
+      <c r="AF81" s="369"/>
+      <c r="AG81" s="369"/>
+      <c r="AH81" s="369"/>
+      <c r="AI81" s="369"/>
+      <c r="AJ81" s="369"/>
+      <c r="AK81" s="369"/>
+      <c r="AL81" s="369"/>
+      <c r="AM81" s="369"/>
+      <c r="AN81" s="369"/>
+      <c r="AO81" s="369"/>
+      <c r="AP81" s="369"/>
+      <c r="AQ81" s="369"/>
+      <c r="AR81" s="369"/>
+      <c r="AS81" s="369"/>
+      <c r="AT81" s="369"/>
+      <c r="AU81" s="369"/>
+      <c r="AV81" s="369"/>
+      <c r="AW81" s="369"/>
+      <c r="AX81" s="369"/>
+      <c r="AY81" s="369"/>
+      <c r="AZ81" s="369"/>
+      <c r="BA81" s="369"/>
+      <c r="BB81" s="369"/>
+      <c r="BC81" s="369"/>
+      <c r="BD81" s="369"/>
+      <c r="BE81" s="369"/>
+      <c r="BF81" s="369"/>
+      <c r="BG81" s="369"/>
+      <c r="BH81" s="369"/>
+      <c r="BI81" s="369"/>
+      <c r="BJ81" s="369"/>
+      <c r="BK81" s="369"/>
+      <c r="BL81" s="369"/>
+      <c r="BM81" s="369"/>
+      <c r="BN81" s="369"/>
+      <c r="BO81" s="369"/>
+      <c r="BP81" s="369"/>
+      <c r="BQ81" s="369"/>
+      <c r="BR81" s="369"/>
+      <c r="BS81" s="369"/>
+      <c r="BT81" s="369"/>
+      <c r="BU81" s="369"/>
+      <c r="BV81" s="369"/>
+      <c r="BW81" s="369"/>
+      <c r="BX81" s="369"/>
+      <c r="BY81" s="369"/>
+      <c r="BZ81" s="369"/>
+      <c r="CA81" s="369"/>
+      <c r="CB81" s="369"/>
+      <c r="CC81" s="369"/>
+      <c r="CD81" s="369"/>
+      <c r="CE81" s="369"/>
+      <c r="CF81" s="369"/>
+      <c r="CG81" s="369"/>
+      <c r="CH81" s="369"/>
+      <c r="CI81" s="369"/>
+      <c r="CJ81" s="369"/>
+      <c r="CK81" s="369"/>
+      <c r="CL81" s="369"/>
+      <c r="CM81" s="369"/>
+      <c r="CN81" s="369"/>
+      <c r="CO81" s="369"/>
+      <c r="CP81" s="369"/>
+      <c r="CQ81" s="369"/>
+      <c r="CR81" s="369"/>
+      <c r="CS81" s="369"/>
+      <c r="CT81" s="369"/>
+      <c r="CU81" s="369"/>
+      <c r="CV81" s="369"/>
+      <c r="CW81" s="369"/>
+      <c r="CX81" s="369"/>
+      <c r="CY81" s="369"/>
+      <c r="CZ81" s="369"/>
+      <c r="DA81" s="369"/>
+      <c r="DB81" s="369"/>
+      <c r="DC81" s="369"/>
+      <c r="DD81" s="369"/>
+      <c r="DE81" s="369"/>
+      <c r="DF81" s="369"/>
+      <c r="DG81" s="369"/>
+      <c r="DH81" s="369"/>
+      <c r="DI81" s="369"/>
+      <c r="DJ81" s="369"/>
+      <c r="DK81" s="369"/>
+      <c r="DL81" s="369"/>
+      <c r="DM81" s="369"/>
+      <c r="DN81" s="369"/>
+      <c r="DO81" s="369"/>
+      <c r="DP81" s="369"/>
+      <c r="DQ81" s="369"/>
+      <c r="DR81" s="369"/>
+      <c r="DS81" s="369"/>
+      <c r="DT81" s="369"/>
+      <c r="DU81" s="369"/>
+      <c r="DV81" s="369"/>
+      <c r="DW81" s="369"/>
+      <c r="DX81" s="369"/>
+      <c r="DY81" s="369"/>
+      <c r="DZ81" s="369"/>
+      <c r="EA81" s="369"/>
+      <c r="EB81" s="369"/>
+      <c r="EC81" s="369"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:EC51" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
+  <autoFilter ref="A1:EC52" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <phoneticPr fontId="65" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -41775,27 +41918,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:138" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="537"/>
-      <c r="B1" s="537"/>
-      <c r="C1" s="537"/>
-      <c r="D1" s="537"/>
-      <c r="E1" s="537"/>
-      <c r="F1" s="537"/>
-      <c r="G1" s="537"/>
+      <c r="A1" s="536"/>
+      <c r="B1" s="536"/>
+      <c r="C1" s="536"/>
+      <c r="D1" s="536"/>
+      <c r="E1" s="536"/>
+      <c r="F1" s="536"/>
+      <c r="G1" s="536"/>
       <c r="H1" s="24"/>
       <c r="I1" s="25"/>
       <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:138" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="538" t="s">
+      <c r="A2" s="537" t="s">
         <v>474</v>
       </c>
-      <c r="B2" s="538"/>
-      <c r="C2" s="538"/>
-      <c r="D2" s="538"/>
-      <c r="E2" s="538"/>
-      <c r="F2" s="538"/>
-      <c r="G2" s="538"/>
+      <c r="B2" s="537"/>
+      <c r="C2" s="537"/>
+      <c r="D2" s="537"/>
+      <c r="E2" s="537"/>
+      <c r="F2" s="537"/>
+      <c r="G2" s="537"/>
       <c r="H2" s="24"/>
       <c r="I2" s="25"/>
       <c r="J2" s="25"/>
@@ -41844,13 +41987,13 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="486">
+      <c r="A5" s="500">
         <v>1</v>
       </c>
-      <c r="B5" s="422" t="s">
+      <c r="B5" s="438" t="s">
         <v>434</v>
       </c>
-      <c r="C5" s="429" t="s">
+      <c r="C5" s="443" t="s">
         <v>475</v>
       </c>
       <c r="D5" s="73" t="s">
@@ -41874,9 +42017,9 @@
       </c>
     </row>
     <row r="6" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="487"/>
-      <c r="B6" s="423"/>
-      <c r="C6" s="430"/>
+      <c r="A6" s="501"/>
+      <c r="B6" s="439"/>
+      <c r="C6" s="444"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
       </c>
@@ -41896,9 +42039,9 @@
       <c r="J6" s="35"/>
     </row>
     <row r="7" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="487"/>
-      <c r="B7" s="423"/>
-      <c r="C7" s="430"/>
+      <c r="A7" s="501"/>
+      <c r="B7" s="439"/>
+      <c r="C7" s="444"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
       </c>
@@ -41918,9 +42061,9 @@
       <c r="J7" s="35"/>
     </row>
     <row r="8" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="487"/>
-      <c r="B8" s="423"/>
-      <c r="C8" s="430"/>
+      <c r="A8" s="501"/>
+      <c r="B8" s="439"/>
+      <c r="C8" s="444"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
       </c>
@@ -41941,9 +42084,9 @@
       <c r="K8" s="38"/>
     </row>
     <row r="9" spans="1:138" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="487"/>
-      <c r="B9" s="423"/>
-      <c r="C9" s="430"/>
+      <c r="A9" s="501"/>
+      <c r="B9" s="439"/>
+      <c r="C9" s="444"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
       </c>
@@ -41963,9 +42106,9 @@
       <c r="J9" s="35"/>
     </row>
     <row r="10" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="487"/>
-      <c r="B10" s="423"/>
-      <c r="C10" s="430"/>
+      <c r="A10" s="501"/>
+      <c r="B10" s="439"/>
+      <c r="C10" s="444"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
       </c>
@@ -41985,9 +42128,9 @@
       <c r="J10" s="35"/>
     </row>
     <row r="11" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="487"/>
-      <c r="B11" s="423"/>
-      <c r="C11" s="430"/>
+      <c r="A11" s="501"/>
+      <c r="B11" s="439"/>
+      <c r="C11" s="444"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
       </c>
@@ -42011,9 +42154,9 @@
       </c>
     </row>
     <row r="12" spans="1:138" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="487"/>
-      <c r="B12" s="423"/>
-      <c r="C12" s="430"/>
+      <c r="A12" s="501"/>
+      <c r="B12" s="439"/>
+      <c r="C12" s="444"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
       </c>
@@ -42163,9 +42306,9 @@
       <c r="EH12" s="41"/>
     </row>
     <row r="13" spans="1:138" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="487"/>
-      <c r="B13" s="423"/>
-      <c r="C13" s="430"/>
+      <c r="A13" s="501"/>
+      <c r="B13" s="439"/>
+      <c r="C13" s="444"/>
       <c r="D13" s="73" t="s">
         <v>318</v>
       </c>
@@ -42185,13 +42328,13 @@
       </c>
     </row>
     <row r="14" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="491">
+      <c r="A14" s="505">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="492" t="s">
+      <c r="B14" s="506" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="429" t="s">
+      <c r="C14" s="443" t="s">
         <v>476</v>
       </c>
       <c r="D14" s="73" t="s">
@@ -42215,9 +42358,9 @@
       </c>
     </row>
     <row r="15" spans="1:138" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="491"/>
-      <c r="B15" s="492"/>
-      <c r="C15" s="536"/>
+      <c r="A15" s="505"/>
+      <c r="B15" s="506"/>
+      <c r="C15" s="538"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
       </c>
@@ -42239,9 +42382,9 @@
       <c r="J15" s="35"/>
     </row>
     <row r="16" spans="1:138" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="491"/>
-      <c r="B16" s="492"/>
-      <c r="C16" s="536"/>
+      <c r="A16" s="505"/>
+      <c r="B16" s="506"/>
+      <c r="C16" s="538"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
       </c>
@@ -42266,9 +42409,9 @@
       <c r="K16" s="38"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="491"/>
-      <c r="B17" s="492"/>
-      <c r="C17" s="536"/>
+      <c r="A17" s="505"/>
+      <c r="B17" s="506"/>
+      <c r="C17" s="538"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
       </c>
@@ -42420,9 +42563,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="491"/>
-      <c r="B18" s="492"/>
-      <c r="C18" s="536"/>
+      <c r="A18" s="505"/>
+      <c r="B18" s="506"/>
+      <c r="C18" s="538"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
       </c>
@@ -42570,9 +42713,9 @@
       <c r="EH18" s="36"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="486"/>
-      <c r="B19" s="493"/>
-      <c r="C19" s="536"/>
+      <c r="A19" s="500"/>
+      <c r="B19" s="507"/>
+      <c r="C19" s="538"/>
       <c r="D19" s="78" t="s">
         <v>318</v>
       </c>
@@ -42592,10 +42735,10 @@
       </c>
     </row>
     <row r="20" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="494">
+      <c r="A20" s="486">
         <v>2</v>
       </c>
-      <c r="B20" s="495" t="s">
+      <c r="B20" s="487" t="s">
         <v>477</v>
       </c>
       <c r="C20" s="480" t="s">
@@ -42620,8 +42763,8 @@
       <c r="J20" s="54"/>
     </row>
     <row r="21" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="494"/>
-      <c r="B21" s="495"/>
+      <c r="A21" s="486"/>
+      <c r="B21" s="487"/>
       <c r="C21" s="528"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
@@ -42644,8 +42787,8 @@
       <c r="J21" s="54"/>
     </row>
     <row r="22" spans="1:138" ht="165" x14ac:dyDescent="0.2">
-      <c r="A22" s="494"/>
-      <c r="B22" s="495"/>
+      <c r="A22" s="486"/>
+      <c r="B22" s="487"/>
       <c r="C22" s="528"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
@@ -42670,8 +42813,8 @@
       </c>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="165" x14ac:dyDescent="0.2">
-      <c r="A23" s="494"/>
-      <c r="B23" s="495"/>
+      <c r="A23" s="486"/>
+      <c r="B23" s="487"/>
       <c r="C23" s="528"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
@@ -42824,8 +42967,8 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="165" x14ac:dyDescent="0.2">
-      <c r="A24" s="494"/>
-      <c r="B24" s="495"/>
+      <c r="A24" s="486"/>
+      <c r="B24" s="487"/>
       <c r="C24" s="528"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
@@ -42976,8 +43119,8 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="494"/>
-      <c r="B25" s="495"/>
+      <c r="A25" s="486"/>
+      <c r="B25" s="487"/>
       <c r="C25" s="529"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
@@ -44483,26 +44626,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:138" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="537"/>
-      <c r="B1" s="537"/>
-      <c r="C1" s="537"/>
-      <c r="D1" s="537"/>
-      <c r="E1" s="537"/>
-      <c r="F1" s="537"/>
+      <c r="A1" s="536"/>
+      <c r="B1" s="536"/>
+      <c r="C1" s="536"/>
+      <c r="D1" s="536"/>
+      <c r="E1" s="536"/>
+      <c r="F1" s="536"/>
       <c r="G1" s="23"/>
       <c r="H1" s="24"/>
       <c r="I1" s="25"/>
       <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:138" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="537" t="s">
+      <c r="A2" s="536" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="537"/>
-      <c r="C2" s="537"/>
-      <c r="D2" s="537"/>
-      <c r="E2" s="537"/>
-      <c r="F2" s="537"/>
+      <c r="B2" s="536"/>
+      <c r="C2" s="536"/>
+      <c r="D2" s="536"/>
+      <c r="E2" s="536"/>
+      <c r="F2" s="536"/>
       <c r="G2" s="23"/>
       <c r="H2" s="24"/>
       <c r="I2" s="25"/>
@@ -44552,13 +44695,13 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="486">
+      <c r="A5" s="500">
         <v>1</v>
       </c>
-      <c r="B5" s="542" t="s">
+      <c r="B5" s="549" t="s">
         <v>434</v>
       </c>
-      <c r="C5" s="544" t="s">
+      <c r="C5" s="547" t="s">
         <v>475</v>
       </c>
       <c r="D5" s="32" t="s">
@@ -44580,9 +44723,9 @@
       <c r="J5" s="35"/>
     </row>
     <row r="6" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="487"/>
-      <c r="B6" s="543"/>
-      <c r="C6" s="545"/>
+      <c r="A6" s="501"/>
+      <c r="B6" s="550"/>
+      <c r="C6" s="551"/>
       <c r="D6" s="32" t="s">
         <v>56</v>
       </c>
@@ -44602,9 +44745,9 @@
       <c r="J6" s="35"/>
     </row>
     <row r="7" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A7" s="487"/>
-      <c r="B7" s="543"/>
-      <c r="C7" s="545"/>
+      <c r="A7" s="501"/>
+      <c r="B7" s="550"/>
+      <c r="C7" s="551"/>
       <c r="D7" s="32" t="s">
         <v>55</v>
       </c>
@@ -44624,9 +44767,9 @@
       <c r="J7" s="35"/>
     </row>
     <row r="8" spans="1:138" ht="120" x14ac:dyDescent="0.2">
-      <c r="A8" s="487"/>
-      <c r="B8" s="543"/>
-      <c r="C8" s="545"/>
+      <c r="A8" s="501"/>
+      <c r="B8" s="550"/>
+      <c r="C8" s="551"/>
       <c r="D8" s="32" t="s">
         <v>63</v>
       </c>
@@ -44647,9 +44790,9 @@
       <c r="K8" s="38"/>
     </row>
     <row r="9" spans="1:138" ht="105" x14ac:dyDescent="0.2">
-      <c r="A9" s="487"/>
-      <c r="B9" s="543"/>
-      <c r="C9" s="545"/>
+      <c r="A9" s="501"/>
+      <c r="B9" s="550"/>
+      <c r="C9" s="551"/>
       <c r="D9" s="32" t="s">
         <v>68</v>
       </c>
@@ -44669,9 +44812,9 @@
       <c r="J9" s="35"/>
     </row>
     <row r="10" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A10" s="487"/>
-      <c r="B10" s="543"/>
-      <c r="C10" s="545"/>
+      <c r="A10" s="501"/>
+      <c r="B10" s="550"/>
+      <c r="C10" s="551"/>
       <c r="D10" s="32" t="s">
         <v>72</v>
       </c>
@@ -44691,9 +44834,9 @@
       <c r="J10" s="35"/>
     </row>
     <row r="11" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="487"/>
-      <c r="B11" s="543"/>
-      <c r="C11" s="545"/>
+      <c r="A11" s="501"/>
+      <c r="B11" s="550"/>
+      <c r="C11" s="551"/>
       <c r="D11" s="32" t="s">
         <v>86</v>
       </c>
@@ -44717,9 +44860,9 @@
       </c>
     </row>
     <row r="12" spans="1:138" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="487"/>
-      <c r="B12" s="543"/>
-      <c r="C12" s="545"/>
+      <c r="A12" s="501"/>
+      <c r="B12" s="550"/>
+      <c r="C12" s="551"/>
       <c r="D12" s="32" t="s">
         <v>92</v>
       </c>
@@ -44869,9 +45012,9 @@
       <c r="EH12" s="41"/>
     </row>
     <row r="13" spans="1:138" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="487"/>
-      <c r="B13" s="543"/>
-      <c r="C13" s="545"/>
+      <c r="A13" s="501"/>
+      <c r="B13" s="550"/>
+      <c r="C13" s="551"/>
       <c r="D13" s="32" t="s">
         <v>318</v>
       </c>
@@ -44891,13 +45034,13 @@
       </c>
     </row>
     <row r="14" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A14" s="491">
+      <c r="A14" s="505">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="549" t="s">
+      <c r="B14" s="545" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="544" t="s">
+      <c r="C14" s="547" t="s">
         <v>476</v>
       </c>
       <c r="D14" s="32" t="s">
@@ -44921,9 +45064,9 @@
       <c r="J14" s="44"/>
     </row>
     <row r="15" spans="1:138" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="491"/>
-      <c r="B15" s="549"/>
-      <c r="C15" s="551"/>
+      <c r="A15" s="505"/>
+      <c r="B15" s="545"/>
+      <c r="C15" s="548"/>
       <c r="D15" s="32" t="s">
         <v>56</v>
       </c>
@@ -44945,9 +45088,9 @@
       <c r="J15" s="35"/>
     </row>
     <row r="16" spans="1:138" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="491"/>
-      <c r="B16" s="549"/>
-      <c r="C16" s="551"/>
+      <c r="A16" s="505"/>
+      <c r="B16" s="545"/>
+      <c r="C16" s="548"/>
       <c r="D16" s="32" t="s">
         <v>55</v>
       </c>
@@ -44972,9 +45115,9 @@
       <c r="K16" s="38"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="491"/>
-      <c r="B17" s="549"/>
-      <c r="C17" s="551"/>
+      <c r="A17" s="505"/>
+      <c r="B17" s="545"/>
+      <c r="C17" s="548"/>
       <c r="D17" s="46" t="s">
         <v>106</v>
       </c>
@@ -45126,9 +45269,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="491"/>
-      <c r="B18" s="549"/>
-      <c r="C18" s="551"/>
+      <c r="A18" s="505"/>
+      <c r="B18" s="545"/>
+      <c r="C18" s="548"/>
       <c r="D18" s="46" t="s">
         <v>92</v>
       </c>
@@ -45276,9 +45419,9 @@
       <c r="EH18" s="36"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="486"/>
-      <c r="B19" s="550"/>
-      <c r="C19" s="551"/>
+      <c r="A19" s="500"/>
+      <c r="B19" s="546"/>
+      <c r="C19" s="548"/>
       <c r="D19" s="49" t="s">
         <v>318</v>
       </c>
@@ -45298,13 +45441,13 @@
       </c>
     </row>
     <row r="20" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="494">
+      <c r="A20" s="486">
         <v>2</v>
       </c>
-      <c r="B20" s="546" t="s">
+      <c r="B20" s="542" t="s">
         <v>477</v>
       </c>
-      <c r="C20" s="547" t="s">
+      <c r="C20" s="543" t="s">
         <v>478</v>
       </c>
       <c r="D20" s="32" t="s">
@@ -45326,9 +45469,9 @@
       <c r="J20" s="54"/>
     </row>
     <row r="21" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A21" s="494"/>
-      <c r="B21" s="546"/>
-      <c r="C21" s="548"/>
+      <c r="A21" s="486"/>
+      <c r="B21" s="542"/>
+      <c r="C21" s="544"/>
       <c r="D21" s="32" t="s">
         <v>56</v>
       </c>
@@ -45350,9 +45493,9 @@
       <c r="J21" s="54"/>
     </row>
     <row r="22" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A22" s="494"/>
-      <c r="B22" s="546"/>
-      <c r="C22" s="548"/>
+      <c r="A22" s="486"/>
+      <c r="B22" s="542"/>
+      <c r="C22" s="544"/>
       <c r="D22" s="32" t="s">
         <v>55</v>
       </c>
@@ -45376,9 +45519,9 @@
       </c>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="210" x14ac:dyDescent="0.2">
-      <c r="A23" s="494"/>
-      <c r="B23" s="546"/>
-      <c r="C23" s="548"/>
+      <c r="A23" s="486"/>
+      <c r="B23" s="542"/>
+      <c r="C23" s="544"/>
       <c r="D23" s="52" t="s">
         <v>114</v>
       </c>
@@ -45530,9 +45673,9 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="210" x14ac:dyDescent="0.2">
-      <c r="A24" s="494"/>
-      <c r="B24" s="546"/>
-      <c r="C24" s="548"/>
+      <c r="A24" s="486"/>
+      <c r="B24" s="542"/>
+      <c r="C24" s="544"/>
       <c r="D24" s="52" t="s">
         <v>92</v>
       </c>
@@ -45682,9 +45825,9 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="494"/>
-      <c r="B25" s="546"/>
-      <c r="C25" s="548"/>
+      <c r="A25" s="486"/>
+      <c r="B25" s="542"/>
+      <c r="C25" s="544"/>
       <c r="D25" s="52" t="s">
         <v>94</v>
       </c>
@@ -46894,17 +47037,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C5:C13"/>
     <mergeCell ref="A20:A25"/>
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="C20:C25"/>
     <mergeCell ref="A14:A19"/>
     <mergeCell ref="B14:B19"/>
     <mergeCell ref="C14:C19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C5:C13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J5:J7" xr:uid="{D5870D16-9B64-40FF-B604-4C6EAE214F81}"/>
@@ -46971,18 +47114,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:133" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="435" t="s">
+      <c r="A1" s="447" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="435"/>
-      <c r="C1" s="435"/>
-      <c r="D1" s="435"/>
-      <c r="E1" s="435"/>
-      <c r="F1" s="435"/>
-      <c r="G1" s="435"/>
+      <c r="B1" s="447"/>
+      <c r="C1" s="447"/>
+      <c r="D1" s="447"/>
+      <c r="E1" s="447"/>
+      <c r="F1" s="447"/>
+      <c r="G1" s="447"/>
       <c r="H1" s="323"/>
-      <c r="I1" s="419"/>
-      <c r="J1" s="419"/>
+      <c r="I1" s="435"/>
+      <c r="J1" s="435"/>
     </row>
     <row r="2" spans="1:133" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -47154,10 +47297,10 @@
       <c r="EC3" s="36"/>
     </row>
     <row r="4" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A4" s="420">
+      <c r="A4" s="436">
         <v>1</v>
       </c>
-      <c r="B4" s="422" t="s">
+      <c r="B4" s="438" t="s">
         <v>50</v>
       </c>
       <c r="C4" s="552" t="s">
@@ -47182,8 +47325,8 @@
       </c>
     </row>
     <row r="5" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A5" s="421"/>
-      <c r="B5" s="423"/>
+      <c r="A5" s="437"/>
+      <c r="B5" s="439"/>
       <c r="C5" s="553"/>
       <c r="D5" s="73" t="s">
         <v>56</v>
@@ -47204,8 +47347,8 @@
       </c>
     </row>
     <row r="6" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A6" s="421"/>
-      <c r="B6" s="423"/>
+      <c r="A6" s="437"/>
+      <c r="B6" s="439"/>
       <c r="C6" s="553"/>
       <c r="D6" s="73" t="s">
         <v>61</v>
@@ -47226,8 +47369,8 @@
       </c>
     </row>
     <row r="7" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A7" s="421"/>
-      <c r="B7" s="423"/>
+      <c r="A7" s="437"/>
+      <c r="B7" s="439"/>
       <c r="C7" s="553"/>
       <c r="D7" s="73" t="s">
         <v>63</v>
@@ -47248,8 +47391,8 @@
       </c>
     </row>
     <row r="8" spans="1:133" ht="108" x14ac:dyDescent="0.2">
-      <c r="A8" s="421"/>
-      <c r="B8" s="423"/>
+      <c r="A8" s="437"/>
+      <c r="B8" s="439"/>
       <c r="C8" s="553"/>
       <c r="D8" s="73" t="s">
         <v>68</v>
@@ -47270,8 +47413,8 @@
       </c>
     </row>
     <row r="9" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A9" s="421"/>
-      <c r="B9" s="423"/>
+      <c r="A9" s="437"/>
+      <c r="B9" s="439"/>
       <c r="C9" s="553"/>
       <c r="D9" s="73" t="s">
         <v>72</v>
@@ -47292,8 +47435,8 @@
       </c>
     </row>
     <row r="10" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="421"/>
-      <c r="B10" s="423"/>
+      <c r="A10" s="437"/>
+      <c r="B10" s="439"/>
       <c r="C10" s="553"/>
       <c r="D10" s="73" t="s">
         <v>76</v>
@@ -47314,8 +47457,8 @@
       </c>
     </row>
     <row r="11" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A11" s="421"/>
-      <c r="B11" s="423"/>
+      <c r="A11" s="437"/>
+      <c r="B11" s="439"/>
       <c r="C11" s="553"/>
       <c r="D11" s="73" t="s">
         <v>79</v>
@@ -47338,8 +47481,8 @@
       </c>
     </row>
     <row r="12" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A12" s="421"/>
-      <c r="B12" s="423"/>
+      <c r="A12" s="437"/>
+      <c r="B12" s="439"/>
       <c r="C12" s="553"/>
       <c r="D12" s="73" t="s">
         <v>83</v>
@@ -47362,8 +47505,8 @@
       </c>
     </row>
     <row r="13" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" s="421"/>
-      <c r="B13" s="423"/>
+      <c r="A13" s="437"/>
+      <c r="B13" s="439"/>
       <c r="C13" s="553"/>
       <c r="D13" s="73" t="s">
         <v>86</v>
@@ -47386,8 +47529,8 @@
       </c>
     </row>
     <row r="14" spans="1:133" s="42" customFormat="1" ht="150" x14ac:dyDescent="0.2">
-      <c r="A14" s="421"/>
-      <c r="B14" s="423"/>
+      <c r="A14" s="437"/>
+      <c r="B14" s="439"/>
       <c r="C14" s="553"/>
       <c r="D14" s="73" t="s">
         <v>92</v>
@@ -47533,8 +47676,8 @@
       <c r="EC14" s="41"/>
     </row>
     <row r="15" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="421"/>
-      <c r="B15" s="423"/>
+      <c r="A15" s="437"/>
+      <c r="B15" s="439"/>
       <c r="C15" s="554"/>
       <c r="D15" s="73" t="s">
         <v>94</v>
@@ -47555,13 +47698,13 @@
       </c>
     </row>
     <row r="16" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A16" s="427" t="s">
+      <c r="A16" s="432" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="428" t="s">
+      <c r="B16" s="433" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="429" t="s">
+      <c r="C16" s="443" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="73" t="s">
@@ -47583,9 +47726,9 @@
       </c>
     </row>
     <row r="17" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="427"/>
-      <c r="B17" s="428"/>
-      <c r="C17" s="430"/>
+      <c r="A17" s="432"/>
+      <c r="B17" s="433"/>
+      <c r="C17" s="444"/>
       <c r="D17" s="73" t="s">
         <v>56</v>
       </c>
@@ -47607,9 +47750,9 @@
       </c>
     </row>
     <row r="18" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A18" s="427"/>
-      <c r="B18" s="428"/>
-      <c r="C18" s="430"/>
+      <c r="A18" s="432"/>
+      <c r="B18" s="433"/>
+      <c r="C18" s="444"/>
       <c r="D18" s="73" t="s">
         <v>61</v>
       </c>
@@ -47629,13 +47772,13 @@
       </c>
     </row>
     <row r="19" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="427"/>
-      <c r="B19" s="428"/>
-      <c r="C19" s="430"/>
-      <c r="D19" s="429" t="s">
+      <c r="A19" s="432"/>
+      <c r="B19" s="433"/>
+      <c r="C19" s="444"/>
+      <c r="D19" s="443" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="456" t="s">
+      <c r="E19" s="458" t="s">
         <v>77</v>
       </c>
       <c r="F19" s="73" t="s">
@@ -47651,11 +47794,11 @@
       </c>
     </row>
     <row r="20" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="427"/>
-      <c r="B20" s="428"/>
-      <c r="C20" s="430"/>
-      <c r="D20" s="455"/>
-      <c r="E20" s="457"/>
+      <c r="A20" s="432"/>
+      <c r="B20" s="433"/>
+      <c r="C20" s="444"/>
+      <c r="D20" s="457"/>
+      <c r="E20" s="459"/>
       <c r="F20" s="73" t="s">
         <v>103</v>
       </c>
@@ -47792,9 +47935,9 @@
       <c r="EC20" s="36"/>
     </row>
     <row r="21" spans="1:133" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A21" s="427"/>
-      <c r="B21" s="428"/>
-      <c r="C21" s="430"/>
+      <c r="A21" s="432"/>
+      <c r="B21" s="433"/>
+      <c r="C21" s="444"/>
       <c r="D21" s="73" t="s">
         <v>79</v>
       </c>
@@ -47939,9 +48082,9 @@
       <c r="EC21" s="36"/>
     </row>
     <row r="22" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A22" s="427"/>
-      <c r="B22" s="428"/>
-      <c r="C22" s="430"/>
+      <c r="A22" s="432"/>
+      <c r="B22" s="433"/>
+      <c r="C22" s="444"/>
       <c r="D22" s="73" t="s">
         <v>83</v>
       </c>
@@ -47963,9 +48106,9 @@
       </c>
     </row>
     <row r="23" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A23" s="427"/>
-      <c r="B23" s="428"/>
-      <c r="C23" s="430"/>
+      <c r="A23" s="432"/>
+      <c r="B23" s="433"/>
+      <c r="C23" s="444"/>
       <c r="D23" s="73" t="s">
         <v>106</v>
       </c>
@@ -47987,9 +48130,9 @@
       </c>
     </row>
     <row r="24" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A24" s="427"/>
-      <c r="B24" s="428"/>
-      <c r="C24" s="430"/>
+      <c r="A24" s="432"/>
+      <c r="B24" s="433"/>
+      <c r="C24" s="444"/>
       <c r="D24" s="73" t="s">
         <v>92</v>
       </c>
@@ -48011,9 +48154,9 @@
       </c>
     </row>
     <row r="25" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="420"/>
-      <c r="B25" s="422"/>
-      <c r="C25" s="430"/>
+      <c r="A25" s="436"/>
+      <c r="B25" s="438"/>
+      <c r="C25" s="444"/>
       <c r="D25" s="189" t="s">
         <v>94</v>
       </c>
@@ -48033,13 +48176,13 @@
       </c>
     </row>
     <row r="26" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A26" s="437" t="s">
+      <c r="A26" s="419" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="448" t="s">
+      <c r="B26" s="449" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="452" t="s">
+      <c r="C26" s="448" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="73" t="s">
@@ -48061,9 +48204,9 @@
       </c>
     </row>
     <row r="27" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A27" s="438"/>
-      <c r="B27" s="449"/>
-      <c r="C27" s="452"/>
+      <c r="A27" s="420"/>
+      <c r="B27" s="450"/>
+      <c r="C27" s="448"/>
       <c r="D27" s="73" t="s">
         <v>56</v>
       </c>
@@ -48085,9 +48228,9 @@
       </c>
     </row>
     <row r="28" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" s="438"/>
-      <c r="B28" s="449"/>
-      <c r="C28" s="452"/>
+      <c r="A28" s="420"/>
+      <c r="B28" s="450"/>
+      <c r="C28" s="448"/>
       <c r="D28" s="73" t="s">
         <v>61</v>
       </c>
@@ -48109,13 +48252,13 @@
       </c>
     </row>
     <row r="29" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="438"/>
-      <c r="B29" s="449"/>
-      <c r="C29" s="452"/>
-      <c r="D29" s="452" t="s">
+      <c r="A29" s="420"/>
+      <c r="B29" s="450"/>
+      <c r="C29" s="448"/>
+      <c r="D29" s="448" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="453" t="s">
+      <c r="E29" s="452" t="s">
         <v>77</v>
       </c>
       <c r="F29" s="73" t="s">
@@ -48131,11 +48274,11 @@
       </c>
     </row>
     <row r="30" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="438"/>
-      <c r="B30" s="449"/>
-      <c r="C30" s="452"/>
-      <c r="D30" s="452"/>
-      <c r="E30" s="454"/>
+      <c r="A30" s="420"/>
+      <c r="B30" s="450"/>
+      <c r="C30" s="448"/>
+      <c r="D30" s="448"/>
+      <c r="E30" s="453"/>
       <c r="F30" s="73" t="s">
         <v>113</v>
       </c>
@@ -48151,9 +48294,9 @@
       </c>
     </row>
     <row r="31" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A31" s="438"/>
-      <c r="B31" s="449"/>
-      <c r="C31" s="452"/>
+      <c r="A31" s="420"/>
+      <c r="B31" s="450"/>
+      <c r="C31" s="448"/>
       <c r="D31" s="73" t="s">
         <v>79</v>
       </c>
@@ -48175,9 +48318,9 @@
       </c>
     </row>
     <row r="32" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A32" s="438"/>
-      <c r="B32" s="449"/>
-      <c r="C32" s="452"/>
+      <c r="A32" s="420"/>
+      <c r="B32" s="450"/>
+      <c r="C32" s="448"/>
       <c r="D32" s="73" t="s">
         <v>83</v>
       </c>
@@ -48199,9 +48342,9 @@
       </c>
     </row>
     <row r="33" spans="1:133" s="47" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A33" s="438"/>
-      <c r="B33" s="449"/>
-      <c r="C33" s="452"/>
+      <c r="A33" s="420"/>
+      <c r="B33" s="450"/>
+      <c r="C33" s="448"/>
       <c r="D33" s="73" t="s">
         <v>114</v>
       </c>
@@ -48346,9 +48489,9 @@
       <c r="EC33" s="36"/>
     </row>
     <row r="34" spans="1:133" s="47" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A34" s="438"/>
-      <c r="B34" s="449"/>
-      <c r="C34" s="452"/>
+      <c r="A34" s="420"/>
+      <c r="B34" s="450"/>
+      <c r="C34" s="448"/>
       <c r="D34" s="73" t="s">
         <v>92</v>
       </c>
@@ -48493,9 +48636,9 @@
       <c r="EC34" s="36"/>
     </row>
     <row r="35" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A35" s="439"/>
-      <c r="B35" s="450"/>
-      <c r="C35" s="452"/>
+      <c r="A35" s="421"/>
+      <c r="B35" s="451"/>
+      <c r="C35" s="448"/>
       <c r="D35" s="73" t="s">
         <v>94</v>
       </c>
@@ -48515,13 +48658,13 @@
       </c>
     </row>
     <row r="36" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A36" s="437" t="s">
+      <c r="A36" s="419" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="440" t="s">
+      <c r="B36" s="422" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="444" t="s">
+      <c r="C36" s="426" t="s">
         <v>117</v>
       </c>
       <c r="D36" s="206" t="s">
@@ -48545,9 +48688,9 @@
       </c>
     </row>
     <row r="37" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A37" s="438"/>
-      <c r="B37" s="441"/>
-      <c r="C37" s="444"/>
+      <c r="A37" s="420"/>
+      <c r="B37" s="423"/>
+      <c r="C37" s="426"/>
       <c r="D37" s="189" t="s">
         <v>122</v>
       </c>
@@ -48569,9 +48712,9 @@
       </c>
     </row>
     <row r="38" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A38" s="438"/>
-      <c r="B38" s="441"/>
-      <c r="C38" s="444"/>
+      <c r="A38" s="420"/>
+      <c r="B38" s="423"/>
+      <c r="C38" s="426"/>
       <c r="D38" s="73" t="s">
         <v>126</v>
       </c>
@@ -48593,9 +48736,9 @@
       </c>
     </row>
     <row r="39" spans="1:133" ht="84" x14ac:dyDescent="0.2">
-      <c r="A39" s="438"/>
-      <c r="B39" s="441"/>
-      <c r="C39" s="444"/>
+      <c r="A39" s="420"/>
+      <c r="B39" s="423"/>
+      <c r="C39" s="426"/>
       <c r="D39" s="73" t="s">
         <v>130</v>
       </c>
@@ -48617,9 +48760,9 @@
       </c>
     </row>
     <row r="40" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A40" s="438"/>
-      <c r="B40" s="441"/>
-      <c r="C40" s="444"/>
+      <c r="A40" s="420"/>
+      <c r="B40" s="423"/>
+      <c r="C40" s="426"/>
       <c r="D40" s="189" t="s">
         <v>134</v>
       </c>
@@ -48639,9 +48782,9 @@
       </c>
     </row>
     <row r="41" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A41" s="438"/>
-      <c r="B41" s="441"/>
-      <c r="C41" s="444"/>
+      <c r="A41" s="420"/>
+      <c r="B41" s="423"/>
+      <c r="C41" s="426"/>
       <c r="D41" s="73" t="s">
         <v>61</v>
       </c>
@@ -48663,9 +48806,9 @@
       </c>
     </row>
     <row r="42" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A42" s="438"/>
-      <c r="B42" s="441"/>
-      <c r="C42" s="444"/>
+      <c r="A42" s="420"/>
+      <c r="B42" s="423"/>
+      <c r="C42" s="426"/>
       <c r="D42" s="73" t="s">
         <v>76</v>
       </c>
@@ -48687,9 +48830,9 @@
       </c>
     </row>
     <row r="43" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A43" s="438"/>
-      <c r="B43" s="441"/>
-      <c r="C43" s="444"/>
+      <c r="A43" s="420"/>
+      <c r="B43" s="423"/>
+      <c r="C43" s="426"/>
       <c r="D43" s="261" t="s">
         <v>114</v>
       </c>
@@ -48711,9 +48854,9 @@
       </c>
     </row>
     <row r="44" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A44" s="438"/>
-      <c r="B44" s="441"/>
-      <c r="C44" s="444"/>
+      <c r="A44" s="420"/>
+      <c r="B44" s="423"/>
+      <c r="C44" s="426"/>
       <c r="D44" s="321" t="s">
         <v>92</v>
       </c>
@@ -48735,9 +48878,9 @@
       </c>
     </row>
     <row r="45" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A45" s="439"/>
-      <c r="B45" s="442"/>
-      <c r="C45" s="445"/>
+      <c r="A45" s="421"/>
+      <c r="B45" s="424"/>
+      <c r="C45" s="427"/>
       <c r="D45" s="73" t="s">
         <v>94</v>
       </c>
@@ -48773,13 +48916,13 @@
       <c r="J46" s="108"/>
     </row>
     <row r="47" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A47" s="427" t="s">
+      <c r="A47" s="432" t="s">
         <v>141</v>
       </c>
-      <c r="B47" s="428" t="s">
+      <c r="B47" s="433" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="452" t="s">
+      <c r="C47" s="448" t="s">
         <v>142</v>
       </c>
       <c r="D47" s="73" t="s">
@@ -48801,9 +48944,9 @@
       </c>
     </row>
     <row r="48" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A48" s="427"/>
-      <c r="B48" s="428"/>
-      <c r="C48" s="452"/>
+      <c r="A48" s="432"/>
+      <c r="B48" s="433"/>
+      <c r="C48" s="448"/>
       <c r="D48" s="73" t="s">
         <v>56</v>
       </c>
@@ -48823,9 +48966,9 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="24" x14ac:dyDescent="0.2">
-      <c r="A49" s="427"/>
-      <c r="B49" s="428"/>
-      <c r="C49" s="452"/>
+      <c r="A49" s="432"/>
+      <c r="B49" s="433"/>
+      <c r="C49" s="448"/>
       <c r="D49" s="73" t="s">
         <v>61</v>
       </c>
@@ -48845,9 +48988,9 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="427"/>
-      <c r="B50" s="428"/>
-      <c r="C50" s="452"/>
+      <c r="A50" s="432"/>
+      <c r="B50" s="433"/>
+      <c r="C50" s="448"/>
       <c r="D50" s="73" t="s">
         <v>63</v>
       </c>
@@ -48867,9 +49010,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="108" x14ac:dyDescent="0.2">
-      <c r="A51" s="427"/>
-      <c r="B51" s="428"/>
-      <c r="C51" s="452"/>
+      <c r="A51" s="432"/>
+      <c r="B51" s="433"/>
+      <c r="C51" s="448"/>
       <c r="D51" s="73" t="s">
         <v>68</v>
       </c>
@@ -48889,9 +49032,9 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A52" s="427"/>
-      <c r="B52" s="428"/>
-      <c r="C52" s="452"/>
+      <c r="A52" s="432"/>
+      <c r="B52" s="433"/>
+      <c r="C52" s="448"/>
       <c r="D52" s="73" t="s">
         <v>143</v>
       </c>
@@ -48911,9 +49054,9 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A53" s="427"/>
-      <c r="B53" s="428"/>
-      <c r="C53" s="452"/>
+      <c r="A53" s="432"/>
+      <c r="B53" s="433"/>
+      <c r="C53" s="448"/>
       <c r="D53" s="73" t="s">
         <v>76</v>
       </c>
@@ -48933,9 +49076,9 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="75" x14ac:dyDescent="0.2">
-      <c r="A54" s="427"/>
-      <c r="B54" s="428"/>
-      <c r="C54" s="452"/>
+      <c r="A54" s="432"/>
+      <c r="B54" s="433"/>
+      <c r="C54" s="448"/>
       <c r="D54" s="73" t="s">
         <v>79</v>
       </c>
@@ -48957,9 +49100,9 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A55" s="427"/>
-      <c r="B55" s="428"/>
-      <c r="C55" s="452"/>
+      <c r="A55" s="432"/>
+      <c r="B55" s="433"/>
+      <c r="C55" s="448"/>
       <c r="D55" s="73" t="s">
         <v>83</v>
       </c>
@@ -48981,9 +49124,9 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A56" s="427"/>
-      <c r="B56" s="428"/>
-      <c r="C56" s="452"/>
+      <c r="A56" s="432"/>
+      <c r="B56" s="433"/>
+      <c r="C56" s="448"/>
       <c r="D56" s="73" t="s">
         <v>106</v>
       </c>
@@ -49005,9 +49148,9 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A57" s="427"/>
-      <c r="B57" s="428"/>
-      <c r="C57" s="452"/>
+      <c r="A57" s="432"/>
+      <c r="B57" s="433"/>
+      <c r="C57" s="448"/>
       <c r="D57" s="73" t="s">
         <v>92</v>
       </c>
@@ -49029,9 +49172,9 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A58" s="427"/>
-      <c r="B58" s="428"/>
-      <c r="C58" s="452"/>
+      <c r="A58" s="432"/>
+      <c r="B58" s="433"/>
+      <c r="C58" s="448"/>
       <c r="D58" s="73" t="s">
         <v>94</v>
       </c>
@@ -49053,27 +49196,27 @@
   </sheetData>
   <autoFilter ref="A2:EC43" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="21">
-    <mergeCell ref="A16:A25"/>
-    <mergeCell ref="B16:B25"/>
-    <mergeCell ref="C16:C25"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A4:A15"/>
-    <mergeCell ref="B4:B15"/>
-    <mergeCell ref="C4:C15"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A36:A45"/>
-    <mergeCell ref="B36:B45"/>
-    <mergeCell ref="C36:C45"/>
     <mergeCell ref="A47:A58"/>
     <mergeCell ref="B47:B58"/>
     <mergeCell ref="C47:C58"/>
     <mergeCell ref="A26:A35"/>
     <mergeCell ref="B26:B35"/>
     <mergeCell ref="C26:C35"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A36:A45"/>
+    <mergeCell ref="B36:B45"/>
+    <mergeCell ref="C36:C45"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A4:A15"/>
+    <mergeCell ref="B4:B15"/>
+    <mergeCell ref="C4:C15"/>
+    <mergeCell ref="A16:A25"/>
+    <mergeCell ref="B16:B25"/>
+    <mergeCell ref="C16:C25"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -49379,18 +49522,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:133" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="435" t="s">
+      <c r="A1" s="447" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="435"/>
-      <c r="C1" s="435"/>
-      <c r="D1" s="435"/>
-      <c r="E1" s="435"/>
-      <c r="F1" s="435"/>
-      <c r="G1" s="435"/>
+      <c r="B1" s="447"/>
+      <c r="C1" s="447"/>
+      <c r="D1" s="447"/>
+      <c r="E1" s="447"/>
+      <c r="F1" s="447"/>
+      <c r="G1" s="447"/>
       <c r="H1" s="323"/>
-      <c r="I1" s="419"/>
-      <c r="J1" s="419"/>
+      <c r="I1" s="435"/>
+      <c r="J1" s="435"/>
     </row>
     <row r="2" spans="1:133" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -49562,13 +49705,13 @@
       <c r="EC3" s="36"/>
     </row>
     <row r="4" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A4" s="420">
+      <c r="A4" s="436">
         <v>1</v>
       </c>
-      <c r="B4" s="422" t="s">
+      <c r="B4" s="438" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="458" t="s">
+      <c r="C4" s="454" t="s">
         <v>186</v>
       </c>
       <c r="D4" s="73" t="s">
@@ -49590,9 +49733,9 @@
       </c>
     </row>
     <row r="5" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A5" s="421"/>
-      <c r="B5" s="423"/>
-      <c r="C5" s="459"/>
+      <c r="A5" s="437"/>
+      <c r="B5" s="439"/>
+      <c r="C5" s="455"/>
       <c r="D5" s="73" t="s">
         <v>56</v>
       </c>
@@ -49612,9 +49755,9 @@
       </c>
     </row>
     <row r="6" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A6" s="421"/>
-      <c r="B6" s="423"/>
-      <c r="C6" s="459"/>
+      <c r="A6" s="437"/>
+      <c r="B6" s="439"/>
+      <c r="C6" s="455"/>
       <c r="D6" s="73" t="s">
         <v>61</v>
       </c>
@@ -49634,9 +49777,9 @@
       </c>
     </row>
     <row r="7" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A7" s="421"/>
-      <c r="B7" s="423"/>
-      <c r="C7" s="459"/>
+      <c r="A7" s="437"/>
+      <c r="B7" s="439"/>
+      <c r="C7" s="455"/>
       <c r="D7" s="73" t="s">
         <v>63</v>
       </c>
@@ -49656,9 +49799,9 @@
       </c>
     </row>
     <row r="8" spans="1:133" ht="108" x14ac:dyDescent="0.2">
-      <c r="A8" s="421"/>
-      <c r="B8" s="423"/>
-      <c r="C8" s="459"/>
+      <c r="A8" s="437"/>
+      <c r="B8" s="439"/>
+      <c r="C8" s="455"/>
       <c r="D8" s="73" t="s">
         <v>68</v>
       </c>
@@ -49678,9 +49821,9 @@
       </c>
     </row>
     <row r="9" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A9" s="421"/>
-      <c r="B9" s="423"/>
-      <c r="C9" s="459"/>
+      <c r="A9" s="437"/>
+      <c r="B9" s="439"/>
+      <c r="C9" s="455"/>
       <c r="D9" s="73" t="s">
         <v>72</v>
       </c>
@@ -49700,9 +49843,9 @@
       </c>
     </row>
     <row r="10" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="421"/>
-      <c r="B10" s="423"/>
-      <c r="C10" s="459"/>
+      <c r="A10" s="437"/>
+      <c r="B10" s="439"/>
+      <c r="C10" s="455"/>
       <c r="D10" s="73" t="s">
         <v>76</v>
       </c>
@@ -49722,9 +49865,9 @@
       </c>
     </row>
     <row r="11" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A11" s="421"/>
-      <c r="B11" s="423"/>
-      <c r="C11" s="459"/>
+      <c r="A11" s="437"/>
+      <c r="B11" s="439"/>
+      <c r="C11" s="455"/>
       <c r="D11" s="73" t="s">
         <v>79</v>
       </c>
@@ -49746,9 +49889,9 @@
       </c>
     </row>
     <row r="12" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A12" s="421"/>
-      <c r="B12" s="423"/>
-      <c r="C12" s="459"/>
+      <c r="A12" s="437"/>
+      <c r="B12" s="439"/>
+      <c r="C12" s="455"/>
       <c r="D12" s="73" t="s">
         <v>83</v>
       </c>
@@ -49770,9 +49913,9 @@
       </c>
     </row>
     <row r="13" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" s="421"/>
-      <c r="B13" s="423"/>
-      <c r="C13" s="459"/>
+      <c r="A13" s="437"/>
+      <c r="B13" s="439"/>
+      <c r="C13" s="455"/>
       <c r="D13" s="73" t="s">
         <v>86</v>
       </c>
@@ -49794,9 +49937,9 @@
       </c>
     </row>
     <row r="14" spans="1:133" s="42" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A14" s="421"/>
-      <c r="B14" s="423"/>
-      <c r="C14" s="459"/>
+      <c r="A14" s="437"/>
+      <c r="B14" s="439"/>
+      <c r="C14" s="455"/>
       <c r="D14" s="73" t="s">
         <v>92</v>
       </c>
@@ -49941,9 +50084,9 @@
       <c r="EC14" s="41"/>
     </row>
     <row r="15" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="421"/>
-      <c r="B15" s="423"/>
-      <c r="C15" s="460"/>
+      <c r="A15" s="437"/>
+      <c r="B15" s="439"/>
+      <c r="C15" s="456"/>
       <c r="D15" s="73" t="s">
         <v>94</v>
       </c>
@@ -49963,13 +50106,13 @@
       </c>
     </row>
     <row r="16" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A16" s="427" t="s">
+      <c r="A16" s="432" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="428" t="s">
+      <c r="B16" s="433" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="429" t="s">
+      <c r="C16" s="443" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="73" t="s">
@@ -49991,9 +50134,9 @@
       </c>
     </row>
     <row r="17" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="427"/>
-      <c r="B17" s="428"/>
-      <c r="C17" s="430"/>
+      <c r="A17" s="432"/>
+      <c r="B17" s="433"/>
+      <c r="C17" s="444"/>
       <c r="D17" s="73" t="s">
         <v>56</v>
       </c>
@@ -50015,9 +50158,9 @@
       </c>
     </row>
     <row r="18" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A18" s="427"/>
-      <c r="B18" s="428"/>
-      <c r="C18" s="430"/>
+      <c r="A18" s="432"/>
+      <c r="B18" s="433"/>
+      <c r="C18" s="444"/>
       <c r="D18" s="73" t="s">
         <v>61</v>
       </c>
@@ -50037,13 +50180,13 @@
       </c>
     </row>
     <row r="19" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="427"/>
-      <c r="B19" s="428"/>
-      <c r="C19" s="430"/>
-      <c r="D19" s="429" t="s">
+      <c r="A19" s="432"/>
+      <c r="B19" s="433"/>
+      <c r="C19" s="444"/>
+      <c r="D19" s="443" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="456" t="s">
+      <c r="E19" s="458" t="s">
         <v>77</v>
       </c>
       <c r="F19" s="73" t="s">
@@ -50059,11 +50202,11 @@
       </c>
     </row>
     <row r="20" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="427"/>
-      <c r="B20" s="428"/>
-      <c r="C20" s="430"/>
-      <c r="D20" s="455"/>
-      <c r="E20" s="457"/>
+      <c r="A20" s="432"/>
+      <c r="B20" s="433"/>
+      <c r="C20" s="444"/>
+      <c r="D20" s="457"/>
+      <c r="E20" s="459"/>
       <c r="F20" s="73" t="s">
         <v>103</v>
       </c>
@@ -50200,9 +50343,9 @@
       <c r="EC20" s="36"/>
     </row>
     <row r="21" spans="1:133" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A21" s="427"/>
-      <c r="B21" s="428"/>
-      <c r="C21" s="430"/>
+      <c r="A21" s="432"/>
+      <c r="B21" s="433"/>
+      <c r="C21" s="444"/>
       <c r="D21" s="73" t="s">
         <v>79</v>
       </c>
@@ -50347,9 +50490,9 @@
       <c r="EC21" s="36"/>
     </row>
     <row r="22" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A22" s="427"/>
-      <c r="B22" s="428"/>
-      <c r="C22" s="430"/>
+      <c r="A22" s="432"/>
+      <c r="B22" s="433"/>
+      <c r="C22" s="444"/>
       <c r="D22" s="73" t="s">
         <v>83</v>
       </c>
@@ -50371,9 +50514,9 @@
       </c>
     </row>
     <row r="23" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A23" s="427"/>
-      <c r="B23" s="428"/>
-      <c r="C23" s="430"/>
+      <c r="A23" s="432"/>
+      <c r="B23" s="433"/>
+      <c r="C23" s="444"/>
       <c r="D23" s="73" t="s">
         <v>106</v>
       </c>
@@ -50395,9 +50538,9 @@
       </c>
     </row>
     <row r="24" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A24" s="427"/>
-      <c r="B24" s="428"/>
-      <c r="C24" s="430"/>
+      <c r="A24" s="432"/>
+      <c r="B24" s="433"/>
+      <c r="C24" s="444"/>
       <c r="D24" s="73" t="s">
         <v>92</v>
       </c>
@@ -50419,9 +50562,9 @@
       </c>
     </row>
     <row r="25" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="420"/>
-      <c r="B25" s="422"/>
-      <c r="C25" s="430"/>
+      <c r="A25" s="436"/>
+      <c r="B25" s="438"/>
+      <c r="C25" s="444"/>
       <c r="D25" s="189" t="s">
         <v>94</v>
       </c>
@@ -50441,13 +50584,13 @@
       </c>
     </row>
     <row r="26" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A26" s="437" t="s">
+      <c r="A26" s="419" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="448" t="s">
+      <c r="B26" s="449" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="452" t="s">
+      <c r="C26" s="448" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="73" t="s">
@@ -50469,9 +50612,9 @@
       </c>
     </row>
     <row r="27" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A27" s="438"/>
-      <c r="B27" s="449"/>
-      <c r="C27" s="452"/>
+      <c r="A27" s="420"/>
+      <c r="B27" s="450"/>
+      <c r="C27" s="448"/>
       <c r="D27" s="73" t="s">
         <v>56</v>
       </c>
@@ -50493,9 +50636,9 @@
       </c>
     </row>
     <row r="28" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" s="438"/>
-      <c r="B28" s="449"/>
-      <c r="C28" s="452"/>
+      <c r="A28" s="420"/>
+      <c r="B28" s="450"/>
+      <c r="C28" s="448"/>
       <c r="D28" s="73" t="s">
         <v>61</v>
       </c>
@@ -50517,13 +50660,13 @@
       </c>
     </row>
     <row r="29" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="438"/>
-      <c r="B29" s="449"/>
-      <c r="C29" s="452"/>
-      <c r="D29" s="452" t="s">
+      <c r="A29" s="420"/>
+      <c r="B29" s="450"/>
+      <c r="C29" s="448"/>
+      <c r="D29" s="448" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="453" t="s">
+      <c r="E29" s="452" t="s">
         <v>77</v>
       </c>
       <c r="F29" s="73" t="s">
@@ -50539,11 +50682,11 @@
       </c>
     </row>
     <row r="30" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="438"/>
-      <c r="B30" s="449"/>
-      <c r="C30" s="452"/>
-      <c r="D30" s="452"/>
-      <c r="E30" s="454"/>
+      <c r="A30" s="420"/>
+      <c r="B30" s="450"/>
+      <c r="C30" s="448"/>
+      <c r="D30" s="448"/>
+      <c r="E30" s="453"/>
       <c r="F30" s="73" t="s">
         <v>113</v>
       </c>
@@ -50559,9 +50702,9 @@
       </c>
     </row>
     <row r="31" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A31" s="438"/>
-      <c r="B31" s="449"/>
-      <c r="C31" s="452"/>
+      <c r="A31" s="420"/>
+      <c r="B31" s="450"/>
+      <c r="C31" s="448"/>
       <c r="D31" s="73" t="s">
         <v>79</v>
       </c>
@@ -50583,9 +50726,9 @@
       </c>
     </row>
     <row r="32" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A32" s="438"/>
-      <c r="B32" s="449"/>
-      <c r="C32" s="452"/>
+      <c r="A32" s="420"/>
+      <c r="B32" s="450"/>
+      <c r="C32" s="448"/>
       <c r="D32" s="73" t="s">
         <v>83</v>
       </c>
@@ -50607,9 +50750,9 @@
       </c>
     </row>
     <row r="33" spans="1:133" s="47" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A33" s="438"/>
-      <c r="B33" s="449"/>
-      <c r="C33" s="452"/>
+      <c r="A33" s="420"/>
+      <c r="B33" s="450"/>
+      <c r="C33" s="448"/>
       <c r="D33" s="73" t="s">
         <v>114</v>
       </c>
@@ -50754,9 +50897,9 @@
       <c r="EC33" s="36"/>
     </row>
     <row r="34" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A34" s="438"/>
-      <c r="B34" s="449"/>
-      <c r="C34" s="452"/>
+      <c r="A34" s="420"/>
+      <c r="B34" s="450"/>
+      <c r="C34" s="448"/>
       <c r="D34" s="73" t="s">
         <v>92</v>
       </c>
@@ -50901,9 +51044,9 @@
       <c r="EC34" s="36"/>
     </row>
     <row r="35" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A35" s="439"/>
-      <c r="B35" s="450"/>
-      <c r="C35" s="452"/>
+      <c r="A35" s="421"/>
+      <c r="B35" s="451"/>
+      <c r="C35" s="448"/>
       <c r="D35" s="73" t="s">
         <v>94</v>
       </c>
@@ -50923,13 +51066,13 @@
       </c>
     </row>
     <row r="36" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A36" s="437" t="s">
+      <c r="A36" s="419" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="440" t="s">
+      <c r="B36" s="422" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="444" t="s">
+      <c r="C36" s="426" t="s">
         <v>117</v>
       </c>
       <c r="D36" s="206" t="s">
@@ -50953,9 +51096,9 @@
       </c>
     </row>
     <row r="37" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A37" s="438"/>
-      <c r="B37" s="441"/>
-      <c r="C37" s="444"/>
+      <c r="A37" s="420"/>
+      <c r="B37" s="423"/>
+      <c r="C37" s="426"/>
       <c r="D37" s="189" t="s">
         <v>122</v>
       </c>
@@ -50977,9 +51120,9 @@
       </c>
     </row>
     <row r="38" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A38" s="438"/>
-      <c r="B38" s="441"/>
-      <c r="C38" s="444"/>
+      <c r="A38" s="420"/>
+      <c r="B38" s="423"/>
+      <c r="C38" s="426"/>
       <c r="D38" s="73" t="s">
         <v>126</v>
       </c>
@@ -51001,9 +51144,9 @@
       </c>
     </row>
     <row r="39" spans="1:133" ht="84" x14ac:dyDescent="0.2">
-      <c r="A39" s="438"/>
-      <c r="B39" s="441"/>
-      <c r="C39" s="444"/>
+      <c r="A39" s="420"/>
+      <c r="B39" s="423"/>
+      <c r="C39" s="426"/>
       <c r="D39" s="73" t="s">
         <v>130</v>
       </c>
@@ -51025,9 +51168,9 @@
       </c>
     </row>
     <row r="40" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A40" s="438"/>
-      <c r="B40" s="441"/>
-      <c r="C40" s="444"/>
+      <c r="A40" s="420"/>
+      <c r="B40" s="423"/>
+      <c r="C40" s="426"/>
       <c r="D40" s="189" t="s">
         <v>134</v>
       </c>
@@ -51047,9 +51190,9 @@
       </c>
     </row>
     <row r="41" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A41" s="438"/>
-      <c r="B41" s="441"/>
-      <c r="C41" s="444"/>
+      <c r="A41" s="420"/>
+      <c r="B41" s="423"/>
+      <c r="C41" s="426"/>
       <c r="D41" s="73" t="s">
         <v>61</v>
       </c>
@@ -51071,9 +51214,9 @@
       </c>
     </row>
     <row r="42" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A42" s="438"/>
-      <c r="B42" s="441"/>
-      <c r="C42" s="444"/>
+      <c r="A42" s="420"/>
+      <c r="B42" s="423"/>
+      <c r="C42" s="426"/>
       <c r="D42" s="73" t="s">
         <v>76</v>
       </c>
@@ -51095,9 +51238,9 @@
       </c>
     </row>
     <row r="43" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A43" s="438"/>
-      <c r="B43" s="441"/>
-      <c r="C43" s="444"/>
+      <c r="A43" s="420"/>
+      <c r="B43" s="423"/>
+      <c r="C43" s="426"/>
       <c r="D43" s="261" t="s">
         <v>114</v>
       </c>
@@ -51119,9 +51262,9 @@
       </c>
     </row>
     <row r="44" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A44" s="438"/>
-      <c r="B44" s="441"/>
-      <c r="C44" s="444"/>
+      <c r="A44" s="420"/>
+      <c r="B44" s="423"/>
+      <c r="C44" s="426"/>
       <c r="D44" s="321" t="s">
         <v>92</v>
       </c>
@@ -51143,9 +51286,9 @@
       </c>
     </row>
     <row r="45" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A45" s="439"/>
-      <c r="B45" s="442"/>
-      <c r="C45" s="445"/>
+      <c r="A45" s="421"/>
+      <c r="B45" s="424"/>
+      <c r="C45" s="427"/>
       <c r="D45" s="73" t="s">
         <v>94</v>
       </c>
@@ -51181,13 +51324,13 @@
       <c r="J46" s="108"/>
     </row>
     <row r="47" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A47" s="427" t="s">
+      <c r="A47" s="432" t="s">
         <v>141</v>
       </c>
-      <c r="B47" s="428" t="s">
+      <c r="B47" s="433" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="452" t="s">
+      <c r="C47" s="448" t="s">
         <v>142</v>
       </c>
       <c r="D47" s="73" t="s">
@@ -51209,9 +51352,9 @@
       </c>
     </row>
     <row r="48" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A48" s="427"/>
-      <c r="B48" s="428"/>
-      <c r="C48" s="452"/>
+      <c r="A48" s="432"/>
+      <c r="B48" s="433"/>
+      <c r="C48" s="448"/>
       <c r="D48" s="73" t="s">
         <v>56</v>
       </c>
@@ -51231,9 +51374,9 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="24" x14ac:dyDescent="0.2">
-      <c r="A49" s="427"/>
-      <c r="B49" s="428"/>
-      <c r="C49" s="452"/>
+      <c r="A49" s="432"/>
+      <c r="B49" s="433"/>
+      <c r="C49" s="448"/>
       <c r="D49" s="73" t="s">
         <v>61</v>
       </c>
@@ -51253,9 +51396,9 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="427"/>
-      <c r="B50" s="428"/>
-      <c r="C50" s="452"/>
+      <c r="A50" s="432"/>
+      <c r="B50" s="433"/>
+      <c r="C50" s="448"/>
       <c r="D50" s="73" t="s">
         <v>63</v>
       </c>
@@ -51275,9 +51418,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="108" x14ac:dyDescent="0.2">
-      <c r="A51" s="427"/>
-      <c r="B51" s="428"/>
-      <c r="C51" s="452"/>
+      <c r="A51" s="432"/>
+      <c r="B51" s="433"/>
+      <c r="C51" s="448"/>
       <c r="D51" s="73" t="s">
         <v>68</v>
       </c>
@@ -51297,9 +51440,9 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A52" s="427"/>
-      <c r="B52" s="428"/>
-      <c r="C52" s="452"/>
+      <c r="A52" s="432"/>
+      <c r="B52" s="433"/>
+      <c r="C52" s="448"/>
       <c r="D52" s="73" t="s">
         <v>143</v>
       </c>
@@ -51319,9 +51462,9 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A53" s="427"/>
-      <c r="B53" s="428"/>
-      <c r="C53" s="452"/>
+      <c r="A53" s="432"/>
+      <c r="B53" s="433"/>
+      <c r="C53" s="448"/>
       <c r="D53" s="73" t="s">
         <v>76</v>
       </c>
@@ -51341,9 +51484,9 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="75" x14ac:dyDescent="0.2">
-      <c r="A54" s="427"/>
-      <c r="B54" s="428"/>
-      <c r="C54" s="452"/>
+      <c r="A54" s="432"/>
+      <c r="B54" s="433"/>
+      <c r="C54" s="448"/>
       <c r="D54" s="73" t="s">
         <v>79</v>
       </c>
@@ -51365,9 +51508,9 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A55" s="427"/>
-      <c r="B55" s="428"/>
-      <c r="C55" s="452"/>
+      <c r="A55" s="432"/>
+      <c r="B55" s="433"/>
+      <c r="C55" s="448"/>
       <c r="D55" s="73" t="s">
         <v>83</v>
       </c>
@@ -51389,9 +51532,9 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A56" s="427"/>
-      <c r="B56" s="428"/>
-      <c r="C56" s="452"/>
+      <c r="A56" s="432"/>
+      <c r="B56" s="433"/>
+      <c r="C56" s="448"/>
       <c r="D56" s="73" t="s">
         <v>106</v>
       </c>
@@ -51413,9 +51556,9 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A57" s="427"/>
-      <c r="B57" s="428"/>
-      <c r="C57" s="452"/>
+      <c r="A57" s="432"/>
+      <c r="B57" s="433"/>
+      <c r="C57" s="448"/>
       <c r="D57" s="73" t="s">
         <v>92</v>
       </c>
@@ -51437,9 +51580,9 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A58" s="427"/>
-      <c r="B58" s="428"/>
-      <c r="C58" s="452"/>
+      <c r="A58" s="432"/>
+      <c r="B58" s="433"/>
+      <c r="C58" s="448"/>
       <c r="D58" s="73" t="s">
         <v>94</v>
       </c>
@@ -51459,13 +51602,13 @@
       </c>
     </row>
     <row r="59" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A59" s="437" t="s">
+      <c r="A59" s="419" t="s">
         <v>108</v>
       </c>
-      <c r="B59" s="448" t="s">
+      <c r="B59" s="449" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="451" t="s">
+      <c r="C59" s="460" t="s">
         <v>188</v>
       </c>
       <c r="D59" s="73" t="s">
@@ -51487,9 +51630,9 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A60" s="438"/>
-      <c r="B60" s="449"/>
-      <c r="C60" s="451"/>
+      <c r="A60" s="420"/>
+      <c r="B60" s="450"/>
+      <c r="C60" s="460"/>
       <c r="D60" s="73" t="s">
         <v>56</v>
       </c>
@@ -51511,9 +51654,9 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A61" s="438"/>
-      <c r="B61" s="449"/>
-      <c r="C61" s="451"/>
+      <c r="A61" s="420"/>
+      <c r="B61" s="450"/>
+      <c r="C61" s="460"/>
       <c r="D61" s="73" t="s">
         <v>61</v>
       </c>
@@ -51535,13 +51678,13 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A62" s="438"/>
-      <c r="B62" s="449"/>
-      <c r="C62" s="451"/>
-      <c r="D62" s="452" t="s">
+      <c r="A62" s="420"/>
+      <c r="B62" s="450"/>
+      <c r="C62" s="460"/>
+      <c r="D62" s="448" t="s">
         <v>76</v>
       </c>
-      <c r="E62" s="453" t="s">
+      <c r="E62" s="452" t="s">
         <v>77</v>
       </c>
       <c r="F62" s="73" t="s">
@@ -51557,11 +51700,11 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A63" s="438"/>
-      <c r="B63" s="449"/>
-      <c r="C63" s="451"/>
-      <c r="D63" s="452"/>
-      <c r="E63" s="454"/>
+      <c r="A63" s="420"/>
+      <c r="B63" s="450"/>
+      <c r="C63" s="460"/>
+      <c r="D63" s="448"/>
+      <c r="E63" s="453"/>
       <c r="F63" s="73" t="s">
         <v>113</v>
       </c>
@@ -51577,9 +51720,9 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="75" x14ac:dyDescent="0.2">
-      <c r="A64" s="438"/>
-      <c r="B64" s="449"/>
-      <c r="C64" s="451"/>
+      <c r="A64" s="420"/>
+      <c r="B64" s="450"/>
+      <c r="C64" s="460"/>
       <c r="D64" s="73" t="s">
         <v>79</v>
       </c>
@@ -51601,9 +51744,9 @@
       </c>
     </row>
     <row r="65" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A65" s="438"/>
-      <c r="B65" s="449"/>
-      <c r="C65" s="451"/>
+      <c r="A65" s="420"/>
+      <c r="B65" s="450"/>
+      <c r="C65" s="460"/>
       <c r="D65" s="73" t="s">
         <v>83</v>
       </c>
@@ -51625,9 +51768,9 @@
       </c>
     </row>
     <row r="66" spans="1:133" s="47" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A66" s="438"/>
-      <c r="B66" s="449"/>
-      <c r="C66" s="451"/>
+      <c r="A66" s="420"/>
+      <c r="B66" s="450"/>
+      <c r="C66" s="460"/>
       <c r="D66" s="73" t="s">
         <v>114</v>
       </c>
@@ -51772,9 +51915,9 @@
       <c r="EC66" s="36"/>
     </row>
     <row r="67" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A67" s="438"/>
-      <c r="B67" s="449"/>
-      <c r="C67" s="451"/>
+      <c r="A67" s="420"/>
+      <c r="B67" s="450"/>
+      <c r="C67" s="460"/>
       <c r="D67" s="73" t="s">
         <v>92</v>
       </c>
@@ -51919,9 +52062,9 @@
       <c r="EC67" s="36"/>
     </row>
     <row r="68" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A68" s="439"/>
-      <c r="B68" s="450"/>
-      <c r="C68" s="451"/>
+      <c r="A68" s="421"/>
+      <c r="B68" s="451"/>
+      <c r="C68" s="460"/>
       <c r="D68" s="73" t="s">
         <v>94</v>
       </c>
@@ -51943,32 +52086,32 @@
   </sheetData>
   <autoFilter ref="A2:EC43" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="26">
+    <mergeCell ref="A59:A68"/>
+    <mergeCell ref="B59:B68"/>
+    <mergeCell ref="C59:C68"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="A16:A25"/>
+    <mergeCell ref="B16:B25"/>
+    <mergeCell ref="C16:C25"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A4:A15"/>
+    <mergeCell ref="B4:B15"/>
+    <mergeCell ref="C4:C15"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A36:A45"/>
+    <mergeCell ref="B36:B45"/>
+    <mergeCell ref="C36:C45"/>
     <mergeCell ref="A47:A58"/>
     <mergeCell ref="B47:B58"/>
     <mergeCell ref="C47:C58"/>
     <mergeCell ref="A26:A35"/>
     <mergeCell ref="B26:B35"/>
     <mergeCell ref="C26:C35"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A36:A45"/>
-    <mergeCell ref="B36:B45"/>
-    <mergeCell ref="C36:C45"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A4:A15"/>
-    <mergeCell ref="B4:B15"/>
-    <mergeCell ref="C4:C15"/>
-    <mergeCell ref="A16:A25"/>
-    <mergeCell ref="B16:B25"/>
-    <mergeCell ref="C16:C25"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="A59:A68"/>
-    <mergeCell ref="B59:B68"/>
-    <mergeCell ref="C59:C68"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="E62:E63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -52954,8 +53097,8 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="419"/>
-      <c r="J1" s="419"/>
+      <c r="I1" s="435"/>
+      <c r="J1" s="435"/>
       <c r="L1" s="30"/>
       <c r="M1" s="30"/>
     </row>
@@ -53140,13 +53283,13 @@
       <c r="EH3" s="36"/>
     </row>
     <row r="4" spans="1:138" ht="44.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="420">
+      <c r="A4" s="436">
         <v>1</v>
       </c>
-      <c r="B4" s="422" t="s">
+      <c r="B4" s="438" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="424" t="s">
+      <c r="C4" s="440" t="s">
         <v>51</v>
       </c>
       <c r="D4" s="73" t="s">
@@ -53174,9 +53317,9 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="30" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="421"/>
-      <c r="B5" s="423"/>
-      <c r="C5" s="425"/>
+      <c r="A5" s="437"/>
+      <c r="B5" s="439"/>
+      <c r="C5" s="441"/>
       <c r="D5" s="73" t="s">
         <v>56</v>
       </c>
@@ -53198,9 +53341,9 @@
       <c r="M5" s="76"/>
     </row>
     <row r="6" spans="1:138" ht="48" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="421"/>
-      <c r="B6" s="423"/>
-      <c r="C6" s="425"/>
+      <c r="A6" s="437"/>
+      <c r="B6" s="439"/>
+      <c r="C6" s="441"/>
       <c r="D6" s="73" t="s">
         <v>55</v>
       </c>
@@ -53225,9 +53368,9 @@
       </c>
     </row>
     <row r="7" spans="1:138" ht="144" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="421"/>
-      <c r="B7" s="423"/>
-      <c r="C7" s="425"/>
+      <c r="A7" s="437"/>
+      <c r="B7" s="439"/>
+      <c r="C7" s="441"/>
       <c r="D7" s="73" t="s">
         <v>63</v>
       </c>
@@ -53250,9 +53393,9 @@
       <c r="M7" s="76"/>
     </row>
     <row r="8" spans="1:138" ht="108" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="421"/>
-      <c r="B8" s="423"/>
-      <c r="C8" s="425"/>
+      <c r="A8" s="437"/>
+      <c r="B8" s="439"/>
+      <c r="C8" s="441"/>
       <c r="D8" s="73" t="s">
         <v>68</v>
       </c>
@@ -53274,9 +53417,9 @@
       <c r="M8" s="76"/>
     </row>
     <row r="9" spans="1:138" ht="36" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="421"/>
-      <c r="B9" s="423"/>
-      <c r="C9" s="425"/>
+      <c r="A9" s="437"/>
+      <c r="B9" s="439"/>
+      <c r="C9" s="441"/>
       <c r="D9" s="73" t="s">
         <v>72</v>
       </c>
@@ -53298,9 +53441,9 @@
       <c r="M9" s="76"/>
     </row>
     <row r="10" spans="1:138" ht="48" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="421"/>
-      <c r="B10" s="423"/>
-      <c r="C10" s="425"/>
+      <c r="A10" s="437"/>
+      <c r="B10" s="439"/>
+      <c r="C10" s="441"/>
       <c r="D10" s="73" t="s">
         <v>86</v>
       </c>
@@ -53324,9 +53467,9 @@
       <c r="M10" s="76"/>
     </row>
     <row r="11" spans="1:138" s="42" customFormat="1" ht="30" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="421"/>
-      <c r="B11" s="423"/>
-      <c r="C11" s="425"/>
+      <c r="A11" s="437"/>
+      <c r="B11" s="439"/>
+      <c r="C11" s="441"/>
       <c r="D11" s="73" t="s">
         <v>92</v>
       </c>
@@ -53476,9 +53619,9 @@
       <c r="EH11" s="41"/>
     </row>
     <row r="12" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="421"/>
-      <c r="B12" s="423"/>
-      <c r="C12" s="426"/>
+      <c r="A12" s="437"/>
+      <c r="B12" s="439"/>
+      <c r="C12" s="442"/>
       <c r="D12" s="73" t="s">
         <v>318</v>
       </c>
@@ -53500,13 +53643,13 @@
       <c r="M12" s="76"/>
     </row>
     <row r="13" spans="1:138" ht="45" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="427">
+      <c r="A13" s="432">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B13" s="428" t="s">
+      <c r="B13" s="433" t="s">
         <v>98</v>
       </c>
-      <c r="C13" s="429" t="s">
+      <c r="C13" s="443" t="s">
         <v>99</v>
       </c>
       <c r="D13" s="73" t="s">
@@ -53532,9 +53675,9 @@
       <c r="M13" s="76"/>
     </row>
     <row r="14" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="427"/>
-      <c r="B14" s="428"/>
-      <c r="C14" s="430"/>
+      <c r="A14" s="432"/>
+      <c r="B14" s="433"/>
+      <c r="C14" s="444"/>
       <c r="D14" s="73" t="s">
         <v>56</v>
       </c>
@@ -53560,9 +53703,9 @@
       <c r="M14" s="76"/>
     </row>
     <row r="15" spans="1:138" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="427"/>
-      <c r="B15" s="428"/>
-      <c r="C15" s="430"/>
+      <c r="A15" s="432"/>
+      <c r="B15" s="433"/>
+      <c r="C15" s="444"/>
       <c r="D15" s="73" t="s">
         <v>320</v>
       </c>
@@ -53609,9 +53752,9 @@
       <c r="M15" s="76"/>
     </row>
     <row r="16" spans="1:138" ht="30" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="427"/>
-      <c r="B16" s="428"/>
-      <c r="C16" s="430"/>
+      <c r="A16" s="432"/>
+      <c r="B16" s="433"/>
+      <c r="C16" s="444"/>
       <c r="D16" s="73" t="s">
         <v>322</v>
       </c>
@@ -53630,9 +53773,9 @@
       <c r="M16" s="76"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="427"/>
-      <c r="B17" s="428"/>
-      <c r="C17" s="430"/>
+      <c r="A17" s="432"/>
+      <c r="B17" s="433"/>
+      <c r="C17" s="444"/>
       <c r="D17" s="73" t="s">
         <v>106</v>
       </c>
@@ -53793,9 +53936,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" s="47" customFormat="1" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="427"/>
-      <c r="B18" s="428"/>
-      <c r="C18" s="430"/>
+      <c r="A18" s="432"/>
+      <c r="B18" s="433"/>
+      <c r="C18" s="444"/>
       <c r="D18" s="73" t="s">
         <v>92</v>
       </c>
@@ -53956,9 +54099,9 @@
       <c r="EH18" s="36"/>
     </row>
     <row r="19" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="420"/>
-      <c r="B19" s="422"/>
-      <c r="C19" s="430"/>
+      <c r="A19" s="436"/>
+      <c r="B19" s="438"/>
+      <c r="C19" s="444"/>
       <c r="D19" s="189" t="s">
         <v>318</v>
       </c>
@@ -54435,13 +54578,13 @@
       <c r="M26" s="76"/>
     </row>
     <row r="27" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="437">
+      <c r="A27" s="419">
         <v>2.1</v>
       </c>
-      <c r="B27" s="440" t="s">
+      <c r="B27" s="422" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="443" t="s">
+      <c r="C27" s="425" t="s">
         <v>117</v>
       </c>
       <c r="D27" s="73" t="s">
@@ -54467,9 +54610,9 @@
       <c r="M27" s="76"/>
     </row>
     <row r="28" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="438"/>
-      <c r="B28" s="441"/>
-      <c r="C28" s="444"/>
+      <c r="A28" s="420"/>
+      <c r="B28" s="423"/>
+      <c r="C28" s="426"/>
       <c r="D28" s="73" t="s">
         <v>122</v>
       </c>
@@ -54489,9 +54632,9 @@
       <c r="M28" s="76"/>
     </row>
     <row r="29" spans="1:138" ht="84" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="438"/>
-      <c r="B29" s="441"/>
-      <c r="C29" s="444"/>
+      <c r="A29" s="420"/>
+      <c r="B29" s="423"/>
+      <c r="C29" s="426"/>
       <c r="D29" s="73" t="s">
         <v>130</v>
       </c>
@@ -54515,9 +54658,9 @@
       <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="438"/>
-      <c r="B30" s="441"/>
-      <c r="C30" s="444"/>
+      <c r="A30" s="420"/>
+      <c r="B30" s="423"/>
+      <c r="C30" s="426"/>
       <c r="D30" s="189" t="s">
         <v>55</v>
       </c>
@@ -54541,9 +54684,9 @@
       <c r="M30" s="76"/>
     </row>
     <row r="31" spans="1:138" ht="36" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="438"/>
-      <c r="B31" s="441"/>
-      <c r="C31" s="444"/>
+      <c r="A31" s="420"/>
+      <c r="B31" s="423"/>
+      <c r="C31" s="426"/>
       <c r="D31" s="73" t="s">
         <v>134</v>
       </c>
@@ -54567,9 +54710,9 @@
       </c>
     </row>
     <row r="32" spans="1:138" ht="48" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="438"/>
-      <c r="B32" s="441"/>
-      <c r="C32" s="444"/>
+      <c r="A32" s="420"/>
+      <c r="B32" s="423"/>
+      <c r="C32" s="426"/>
       <c r="D32" s="267" t="s">
         <v>114</v>
       </c>
@@ -54593,9 +54736,9 @@
       <c r="M32" s="76"/>
     </row>
     <row r="33" spans="1:13" ht="30" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="438"/>
-      <c r="B33" s="441"/>
-      <c r="C33" s="444"/>
+      <c r="A33" s="420"/>
+      <c r="B33" s="423"/>
+      <c r="C33" s="426"/>
       <c r="D33" s="268" t="s">
         <v>92</v>
       </c>
@@ -54619,9 +54762,9 @@
       <c r="M33" s="76"/>
     </row>
     <row r="34" spans="1:13" ht="45" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="439"/>
-      <c r="B34" s="442"/>
-      <c r="C34" s="445"/>
+      <c r="A34" s="421"/>
+      <c r="B34" s="424"/>
+      <c r="C34" s="427"/>
       <c r="D34" s="73" t="s">
         <v>94</v>
       </c>
@@ -54661,10 +54804,10 @@
       <c r="M35" s="76"/>
     </row>
     <row r="36" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="420">
+      <c r="A36" s="436">
         <v>1</v>
       </c>
-      <c r="B36" s="422" t="s">
+      <c r="B36" s="438" t="s">
         <v>50</v>
       </c>
       <c r="C36" s="482" t="s">
@@ -54689,8 +54832,8 @@
       </c>
     </row>
     <row r="37" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A37" s="421"/>
-      <c r="B37" s="423"/>
+      <c r="A37" s="437"/>
+      <c r="B37" s="439"/>
       <c r="C37" s="483"/>
       <c r="D37" s="73" t="s">
         <v>56</v>
@@ -54711,8 +54854,8 @@
       </c>
     </row>
     <row r="38" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A38" s="421"/>
-      <c r="B38" s="423"/>
+      <c r="A38" s="437"/>
+      <c r="B38" s="439"/>
       <c r="C38" s="483"/>
       <c r="D38" s="73" t="s">
         <v>55</v>
@@ -54733,8 +54876,8 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="144" x14ac:dyDescent="0.2">
-      <c r="A39" s="421"/>
-      <c r="B39" s="423"/>
+      <c r="A39" s="437"/>
+      <c r="B39" s="439"/>
       <c r="C39" s="483"/>
       <c r="D39" s="73" t="s">
         <v>63</v>
@@ -54755,8 +54898,8 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="108" x14ac:dyDescent="0.2">
-      <c r="A40" s="421"/>
-      <c r="B40" s="423"/>
+      <c r="A40" s="437"/>
+      <c r="B40" s="439"/>
       <c r="C40" s="483"/>
       <c r="D40" s="73" t="s">
         <v>68</v>
@@ -54777,8 +54920,8 @@
       </c>
     </row>
     <row r="41" spans="1:13" ht="36" x14ac:dyDescent="0.2">
-      <c r="A41" s="421"/>
-      <c r="B41" s="423"/>
+      <c r="A41" s="437"/>
+      <c r="B41" s="439"/>
       <c r="C41" s="483"/>
       <c r="D41" s="73" t="s">
         <v>72</v>
@@ -54799,8 +54942,8 @@
       </c>
     </row>
     <row r="42" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A42" s="421"/>
-      <c r="B42" s="423"/>
+      <c r="A42" s="437"/>
+      <c r="B42" s="439"/>
       <c r="C42" s="483"/>
       <c r="D42" s="73" t="s">
         <v>86</v>
@@ -54823,8 +54966,8 @@
       </c>
     </row>
     <row r="43" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A43" s="421"/>
-      <c r="B43" s="423"/>
+      <c r="A43" s="437"/>
+      <c r="B43" s="439"/>
       <c r="C43" s="483"/>
       <c r="D43" s="73" t="s">
         <v>92</v>
@@ -54847,8 +54990,8 @@
       </c>
     </row>
     <row r="44" spans="1:13" ht="60" x14ac:dyDescent="0.2">
-      <c r="A44" s="421"/>
-      <c r="B44" s="423"/>
+      <c r="A44" s="437"/>
+      <c r="B44" s="439"/>
       <c r="C44" s="483"/>
       <c r="D44" s="73" t="s">
         <v>318</v>
@@ -54869,13 +55012,13 @@
       </c>
     </row>
     <row r="45" spans="1:13" ht="36" x14ac:dyDescent="0.2">
-      <c r="A45" s="427">
+      <c r="A45" s="432">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B45" s="428" t="s">
+      <c r="B45" s="433" t="s">
         <v>98</v>
       </c>
-      <c r="C45" s="429" t="s">
+      <c r="C45" s="443" t="s">
         <v>99</v>
       </c>
       <c r="D45" s="73" t="s">
@@ -54897,9 +55040,9 @@
       </c>
     </row>
     <row r="46" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A46" s="427"/>
-      <c r="B46" s="428"/>
-      <c r="C46" s="430"/>
+      <c r="A46" s="432"/>
+      <c r="B46" s="433"/>
+      <c r="C46" s="444"/>
       <c r="D46" s="73" t="s">
         <v>56</v>
       </c>
@@ -54921,9 +55064,9 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A47" s="427"/>
-      <c r="B47" s="428"/>
-      <c r="C47" s="430"/>
+      <c r="A47" s="432"/>
+      <c r="B47" s="433"/>
+      <c r="C47" s="444"/>
       <c r="D47" s="73" t="s">
         <v>320</v>
       </c>
@@ -54967,9 +55110,9 @@
       </c>
     </row>
     <row r="48" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A48" s="427"/>
-      <c r="B48" s="428"/>
-      <c r="C48" s="430"/>
+      <c r="A48" s="432"/>
+      <c r="B48" s="433"/>
+      <c r="C48" s="444"/>
       <c r="D48" s="73" t="s">
         <v>322</v>
       </c>
@@ -54985,9 +55128,9 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A49" s="427"/>
-      <c r="B49" s="428"/>
-      <c r="C49" s="430"/>
+      <c r="A49" s="432"/>
+      <c r="B49" s="433"/>
+      <c r="C49" s="444"/>
       <c r="D49" s="73" t="s">
         <v>106</v>
       </c>
@@ -55020,9 +55163,9 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A50" s="427"/>
-      <c r="B50" s="428"/>
-      <c r="C50" s="430"/>
+      <c r="A50" s="432"/>
+      <c r="B50" s="433"/>
+      <c r="C50" s="444"/>
       <c r="D50" s="73" t="s">
         <v>92</v>
       </c>
@@ -55055,9 +55198,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A51" s="420"/>
-      <c r="B51" s="422"/>
-      <c r="C51" s="430"/>
+      <c r="A51" s="436"/>
+      <c r="B51" s="438"/>
+      <c r="C51" s="444"/>
       <c r="D51" s="189" t="s">
         <v>318</v>
       </c>
@@ -55291,13 +55434,13 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A60" s="437">
+      <c r="A60" s="419">
         <v>2.1</v>
       </c>
-      <c r="B60" s="440" t="s">
+      <c r="B60" s="422" t="s">
         <v>116</v>
       </c>
-      <c r="C60" s="443" t="s">
+      <c r="C60" s="425" t="s">
         <v>117</v>
       </c>
       <c r="D60" s="73" t="s">
@@ -55319,9 +55462,9 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A61" s="438"/>
-      <c r="B61" s="441"/>
-      <c r="C61" s="444"/>
+      <c r="A61" s="420"/>
+      <c r="B61" s="423"/>
+      <c r="C61" s="426"/>
       <c r="D61" s="73" t="s">
         <v>122</v>
       </c>
@@ -55339,9 +55482,9 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="84" x14ac:dyDescent="0.2">
-      <c r="A62" s="438"/>
-      <c r="B62" s="441"/>
-      <c r="C62" s="444"/>
+      <c r="A62" s="420"/>
+      <c r="B62" s="423"/>
+      <c r="C62" s="426"/>
       <c r="D62" s="73" t="s">
         <v>130</v>
       </c>
@@ -55361,9 +55504,9 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A63" s="438"/>
-      <c r="B63" s="441"/>
-      <c r="C63" s="444"/>
+      <c r="A63" s="420"/>
+      <c r="B63" s="423"/>
+      <c r="C63" s="426"/>
       <c r="D63" s="189" t="s">
         <v>55</v>
       </c>
@@ -55385,9 +55528,9 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A64" s="438"/>
-      <c r="B64" s="441"/>
-      <c r="C64" s="444"/>
+      <c r="A64" s="420"/>
+      <c r="B64" s="423"/>
+      <c r="C64" s="426"/>
       <c r="D64" s="73" t="s">
         <v>134</v>
       </c>
@@ -55405,9 +55548,9 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="A65" s="438"/>
-      <c r="B65" s="441"/>
-      <c r="C65" s="444"/>
+      <c r="A65" s="420"/>
+      <c r="B65" s="423"/>
+      <c r="C65" s="426"/>
       <c r="D65" s="267" t="s">
         <v>114</v>
       </c>
@@ -55429,9 +55572,9 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A66" s="438"/>
-      <c r="B66" s="441"/>
-      <c r="C66" s="444"/>
+      <c r="A66" s="420"/>
+      <c r="B66" s="423"/>
+      <c r="C66" s="426"/>
       <c r="D66" s="268" t="s">
         <v>92</v>
       </c>
@@ -55453,9 +55596,9 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="45" x14ac:dyDescent="0.2">
-      <c r="A67" s="439"/>
-      <c r="B67" s="442"/>
-      <c r="C67" s="445"/>
+      <c r="A67" s="421"/>
+      <c r="B67" s="424"/>
+      <c r="C67" s="427"/>
       <c r="D67" s="73" t="s">
         <v>94</v>
       </c>
@@ -55477,24 +55620,6 @@
   </sheetData>
   <autoFilter ref="A2:EH34" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="25">
-    <mergeCell ref="A52:A59"/>
-    <mergeCell ref="B52:B59"/>
-    <mergeCell ref="C52:C59"/>
-    <mergeCell ref="A60:A67"/>
-    <mergeCell ref="B60:B67"/>
-    <mergeCell ref="C60:C67"/>
-    <mergeCell ref="A36:A44"/>
-    <mergeCell ref="B36:B44"/>
-    <mergeCell ref="C36:C44"/>
-    <mergeCell ref="A45:A51"/>
-    <mergeCell ref="B45:B51"/>
-    <mergeCell ref="C45:C51"/>
-    <mergeCell ref="A20:A26"/>
-    <mergeCell ref="B20:B26"/>
-    <mergeCell ref="C20:C26"/>
-    <mergeCell ref="A27:A34"/>
-    <mergeCell ref="B27:B34"/>
-    <mergeCell ref="C27:C34"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="A4:A12"/>
     <mergeCell ref="B4:B12"/>
@@ -55502,6 +55627,24 @@
     <mergeCell ref="A13:A19"/>
     <mergeCell ref="B13:B19"/>
     <mergeCell ref="C13:C19"/>
+    <mergeCell ref="A20:A26"/>
+    <mergeCell ref="B20:B26"/>
+    <mergeCell ref="C20:C26"/>
+    <mergeCell ref="A27:A34"/>
+    <mergeCell ref="B27:B34"/>
+    <mergeCell ref="C27:C34"/>
+    <mergeCell ref="A36:A44"/>
+    <mergeCell ref="B36:B44"/>
+    <mergeCell ref="C36:C44"/>
+    <mergeCell ref="A45:A51"/>
+    <mergeCell ref="B45:B51"/>
+    <mergeCell ref="C45:C51"/>
+    <mergeCell ref="A52:A59"/>
+    <mergeCell ref="B52:B59"/>
+    <mergeCell ref="C52:C59"/>
+    <mergeCell ref="A60:A67"/>
+    <mergeCell ref="B60:B67"/>
+    <mergeCell ref="C60:C67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -56207,12 +56350,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F52F3FC1CD8EC649B3AFADF3835D38B7" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="585bd31a01b77638b6ff73c684db7301">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
     <xsd:element name="properties">
@@ -56326,6 +56463,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEA3B3A7-4C5B-4FB5-B9FC-8D6E6D28CE9F}">
   <ds:schemaRefs>
@@ -56335,15 +56478,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB3A44B8-EE3C-49AF-BF49-698BCE2C5CA8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38A554B1-B6E8-4F95-B069-71B18B767B61}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -56359,6 +56493,15 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB3A44B8-EE3C-49AF-BF49-698BCE2C5CA8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{f01e930a-b52e-42b1-b70f-a8882b5d043b}" enabled="0" method="" siteId="{f01e930a-b52e-42b1-b70f-a8882b5d043b}" removed="1"/>
